--- a/capabilities/economic-research/model.xlsx
+++ b/capabilities/economic-research/model.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -192,18 +192,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -574,7 +573,7 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -1894,7 +1893,7 @@
   <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2044,7 +2043,7 @@
         <f>INDEX(WL_PATIENTS,1)*BENCH_DAYS</f>
         <v>86618.0</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="16">
         <f>INDEX(DAYS_PER_PT,1)-BENCH_DAYS</f>
         <v>-4.064651689025375</v>
       </c>
@@ -2060,7 +2059,7 @@
         <f>INDEX(WL_DAYS,1)-INDEX(EXCESS_DAYS,1)</f>
         <v>61470.0</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="18">
         <f>INDEX(EXCESS_DAYS,1)/INDEX(WL_DAYS,1)</f>
         <v>0.0</v>
       </c>
@@ -2080,31 +2079,31 @@
         <f>INDEX(REASON_NO_BED,1)+INDEX(REASON_BEHAVIOR,1)+INDEX(REASON_SPECIAL_CARE,1)+INDEX(REASON_FINANCIAL,1)+INDEX(REASON_GUARDIANSHIP,1)+INDEX(REASON_PASARR,1)+INDEX(REASON_OTHER,1)</f>
         <v>120.0</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="18">
         <f>INDEX(REASON_NO_BED,1)/INDEX(REASON_SUM,1)</f>
         <v>0.325</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="18">
         <f>INDEX(REASON_BEHAVIOR,1)/INDEX(REASON_SUM,1)</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="18">
         <f>INDEX(REASON_SPECIAL_CARE,1)/INDEX(REASON_SUM,1)</f>
         <v>0.19166666666666668</v>
       </c>
-      <c r="P4" s="19">
+      <c r="P4" s="18">
         <f>INDEX(REASON_FINANCIAL,1)/INDEX(REASON_SUM,1)</f>
         <v>0.15</v>
       </c>
-      <c r="Q4" s="19">
+      <c r="Q4" s="18">
         <f>INDEX(REASON_GUARDIANSHIP,1)/INDEX(REASON_SUM,1)</f>
         <v>0.09166666666666666</v>
       </c>
-      <c r="R4" s="19">
+      <c r="R4" s="18">
         <f>INDEX(REASON_PASARR,1)/INDEX(REASON_SUM,1)</f>
         <v>0.016666666666666666</v>
       </c>
-      <c r="S4" s="19">
+      <c r="S4" s="18">
         <f>INDEX(REASON_OTHER,1)/INDEX(REASON_SUM,1)</f>
         <v>0.09166666666666666</v>
       </c>
@@ -2130,7 +2129,7 @@
         <f>INDEX(WL_PATIENTS,2)*BENCH_DAYS</f>
         <v>74116.0</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="16">
         <f>INDEX(DAYS_PER_PT,2)-BENCH_DAYS</f>
         <v>-1.5158670192670947</v>
       </c>
@@ -2146,7 +2145,7 @@
         <f>INDEX(WL_DAYS,2)-INDEX(EXCESS_DAYS,2)</f>
         <v>66091.0</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="18">
         <f>INDEX(EXCESS_DAYS,2)/INDEX(WL_DAYS,2)</f>
         <v>0.0</v>
       </c>
@@ -2166,31 +2165,31 @@
         <f>INDEX(REASON_NO_BED,2)+INDEX(REASON_BEHAVIOR,2)+INDEX(REASON_SPECIAL_CARE,2)+INDEX(REASON_FINANCIAL,2)+INDEX(REASON_GUARDIANSHIP,2)+INDEX(REASON_PASARR,2)+INDEX(REASON_OTHER,2)</f>
         <v>171.0</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="18">
         <f>INDEX(REASON_NO_BED,2)/INDEX(REASON_SUM,2)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="18">
         <f>INDEX(REASON_BEHAVIOR,2)/INDEX(REASON_SUM,2)</f>
         <v>0.1695906432748538</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="18">
         <f>INDEX(REASON_SPECIAL_CARE,2)/INDEX(REASON_SUM,2)</f>
         <v>0.09941520467836257</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="18">
         <f>INDEX(REASON_FINANCIAL,2)/INDEX(REASON_SUM,2)</f>
         <v>0.18128654970760233</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="18">
         <f>INDEX(REASON_GUARDIANSHIP,2)/INDEX(REASON_SUM,2)</f>
         <v>0.10526315789473684</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="18">
         <f>INDEX(REASON_PASARR,2)/INDEX(REASON_SUM,2)</f>
         <v>0.011695906432748537</v>
       </c>
-      <c r="S5" s="19">
+      <c r="S5" s="18">
         <f>INDEX(REASON_OTHER,2)/INDEX(REASON_SUM,2)</f>
         <v>0.09941520467836257</v>
       </c>
@@ -2216,7 +2215,7 @@
         <f>INDEX(WL_PATIENTS,3)*BENCH_DAYS</f>
         <v>67060.0</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="16">
         <f>INDEX(DAYS_PER_PT,3)-BENCH_DAYS</f>
         <v>2.474112734864299</v>
       </c>
@@ -2232,7 +2231,7 @@
         <f>INDEX(WL_DAYS,3)-INDEX(EXCESS_DAYS,3)</f>
         <v>67060.0</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <f>INDEX(EXCESS_DAYS,3)/INDEX(WL_DAYS,3)</f>
         <v>0.1501818504391023</v>
       </c>
@@ -2252,31 +2251,31 @@
         <f>INDEX(REASON_NO_BED,3)+INDEX(REASON_BEHAVIOR,3)+INDEX(REASON_SPECIAL_CARE,3)+INDEX(REASON_FINANCIAL,3)+INDEX(REASON_GUARDIANSHIP,3)+INDEX(REASON_PASARR,3)+INDEX(REASON_OTHER,3)</f>
         <v>184.0</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="18">
         <f>INDEX(REASON_NO_BED,3)/INDEX(REASON_SUM,3)</f>
         <v>0.391304347826087</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="18">
         <f>INDEX(REASON_BEHAVIOR,3)/INDEX(REASON_SUM,3)</f>
         <v>0.14673913043478262</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="18">
         <f>INDEX(REASON_SPECIAL_CARE,3)/INDEX(REASON_SUM,3)</f>
         <v>0.11413043478260869</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="18">
         <f>INDEX(REASON_FINANCIAL,3)/INDEX(REASON_SUM,3)</f>
         <v>0.17391304347826086</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="Q6" s="18">
         <f>INDEX(REASON_GUARDIANSHIP,3)/INDEX(REASON_SUM,3)</f>
         <v>0.14130434782608695</v>
       </c>
-      <c r="R6" s="19">
+      <c r="R6" s="18">
         <f>INDEX(REASON_PASARR,3)/INDEX(REASON_SUM,3)</f>
         <v>0.0</v>
       </c>
-      <c r="S6" s="19">
+      <c r="S6" s="18">
         <f>INDEX(REASON_OTHER,3)/INDEX(REASON_SUM,3)</f>
         <v>0.03260869565217391</v>
       </c>
@@ -2302,7 +2301,7 @@
         <f>INDEX(WL_PATIENTS,4)*BENCH_DAYS</f>
         <v>63742.0</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="16">
         <f>INDEX(DAYS_PER_PT,4)-BENCH_DAYS</f>
         <v>-1.4155501866900941</v>
       </c>
@@ -2318,7 +2317,7 @@
         <f>INDEX(WL_DAYS,4)-INDEX(EXCESS_DAYS,4)</f>
         <v>57297.0</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="18">
         <f>INDEX(EXCESS_DAYS,4)/INDEX(WL_DAYS,4)</f>
         <v>0.0</v>
       </c>
@@ -2338,31 +2337,31 @@
         <f>INDEX(REASON_NO_BED,4)+INDEX(REASON_BEHAVIOR,4)+INDEX(REASON_SPECIAL_CARE,4)+INDEX(REASON_FINANCIAL,4)+INDEX(REASON_GUARDIANSHIP,4)+INDEX(REASON_PASARR,4)+INDEX(REASON_OTHER,4)</f>
         <v>144.0</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="18">
         <f>INDEX(REASON_NO_BED,4)/INDEX(REASON_SUM,4)</f>
         <v>0.2847222222222222</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="18">
         <f>INDEX(REASON_BEHAVIOR,4)/INDEX(REASON_SUM,4)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="18">
         <f>INDEX(REASON_SPECIAL_CARE,4)/INDEX(REASON_SUM,4)</f>
         <v>0.1527777777777778</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="18">
         <f>INDEX(REASON_FINANCIAL,4)/INDEX(REASON_SUM,4)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="18">
         <f>INDEX(REASON_GUARDIANSHIP,4)/INDEX(REASON_SUM,4)</f>
         <v>0.10416666666666667</v>
       </c>
-      <c r="R7" s="19">
+      <c r="R7" s="18">
         <f>INDEX(REASON_PASARR,4)/INDEX(REASON_SUM,4)</f>
         <v>0.0</v>
       </c>
-      <c r="S7" s="19">
+      <c r="S7" s="18">
         <f>INDEX(REASON_OTHER,4)/INDEX(REASON_SUM,4)</f>
         <v>0.08333333333333333</v>
       </c>
@@ -2388,7 +2387,7 @@
         <f>INDEX(WL_PATIENTS,5)*BENCH_DAYS</f>
         <v>68978.0</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="16">
         <f>INDEX(DAYS_PER_PT,5)-BENCH_DAYS</f>
         <v>-1.8120560178607672</v>
       </c>
@@ -2404,7 +2403,7 @@
         <f>INDEX(WL_DAYS,5)-INDEX(EXCESS_DAYS,5)</f>
         <v>60050.0</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="18">
         <f>INDEX(EXCESS_DAYS,5)/INDEX(WL_DAYS,5)</f>
         <v>0.0</v>
       </c>
@@ -2424,31 +2423,31 @@
         <f>INDEX(REASON_NO_BED,5)+INDEX(REASON_BEHAVIOR,5)+INDEX(REASON_SPECIAL_CARE,5)+INDEX(REASON_FINANCIAL,5)+INDEX(REASON_GUARDIANSHIP,5)+INDEX(REASON_PASARR,5)+INDEX(REASON_OTHER,5)</f>
         <v>189.0</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="18">
         <f>INDEX(REASON_NO_BED,5)/INDEX(REASON_SUM,5)</f>
         <v>0.26455026455026454</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="18">
         <f>INDEX(REASON_BEHAVIOR,5)/INDEX(REASON_SUM,5)</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="18">
         <f>INDEX(REASON_SPECIAL_CARE,5)/INDEX(REASON_SUM,5)</f>
         <v>0.1164021164021164</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="18">
         <f>INDEX(REASON_FINANCIAL,5)/INDEX(REASON_SUM,5)</f>
         <v>0.2275132275132275</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="Q8" s="18">
         <f>INDEX(REASON_GUARDIANSHIP,5)/INDEX(REASON_SUM,5)</f>
         <v>0.10582010582010581</v>
       </c>
-      <c r="R8" s="19">
+      <c r="R8" s="18">
         <f>INDEX(REASON_PASARR,5)/INDEX(REASON_SUM,5)</f>
         <v>0.0</v>
       </c>
-      <c r="S8" s="19">
+      <c r="S8" s="18">
         <f>INDEX(REASON_OTHER,5)/INDEX(REASON_SUM,5)</f>
         <v>0.09523809523809523</v>
       </c>
@@ -2474,7 +2473,7 @@
         <f>INDEX(WL_PATIENTS,6)*BENCH_DAYS</f>
         <v>51534.0</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="16">
         <f>INDEX(DAYS_PER_PT,6)-BENCH_DAYS</f>
         <v>7.342298288508559</v>
       </c>
@@ -2490,7 +2489,7 @@
         <f>INDEX(WL_DAYS,6)-INDEX(EXCESS_DAYS,6)</f>
         <v>51534.0</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="18">
         <f>INDEX(EXCESS_DAYS,6)/INDEX(WL_DAYS,6)</f>
         <v>0.3440256615878107</v>
       </c>
@@ -2510,31 +2509,31 @@
         <f>INDEX(REASON_NO_BED,6)+INDEX(REASON_BEHAVIOR,6)+INDEX(REASON_SPECIAL_CARE,6)+INDEX(REASON_FINANCIAL,6)+INDEX(REASON_GUARDIANSHIP,6)+INDEX(REASON_PASARR,6)+INDEX(REASON_OTHER,6)</f>
         <v>250.0</v>
       </c>
-      <c r="M9" s="19">
+      <c r="M9" s="18">
         <f>INDEX(REASON_NO_BED,6)/INDEX(REASON_SUM,6)</f>
         <v>0.228</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="18">
         <f>INDEX(REASON_BEHAVIOR,6)/INDEX(REASON_SUM,6)</f>
         <v>0.14</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="18">
         <f>INDEX(REASON_SPECIAL_CARE,6)/INDEX(REASON_SUM,6)</f>
         <v>0.156</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="18">
         <f>INDEX(REASON_FINANCIAL,6)/INDEX(REASON_SUM,6)</f>
         <v>0.3</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="Q9" s="18">
         <f>INDEX(REASON_GUARDIANSHIP,6)/INDEX(REASON_SUM,6)</f>
         <v>0.116</v>
       </c>
-      <c r="R9" s="19">
+      <c r="R9" s="18">
         <f>INDEX(REASON_PASARR,6)/INDEX(REASON_SUM,6)</f>
         <v>0.02</v>
       </c>
-      <c r="S9" s="19">
+      <c r="S9" s="18">
         <f>INDEX(REASON_OTHER,6)/INDEX(REASON_SUM,6)</f>
         <v>0.04</v>
       </c>
@@ -2560,7 +2559,7 @@
         <f>INDEX(WL_PATIENTS,7)*BENCH_DAYS</f>
         <v>50540.0</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="16">
         <f>INDEX(DAYS_PER_PT,7)-BENCH_DAYS</f>
         <v>9.018559556786702</v>
       </c>
@@ -2576,7 +2575,7 @@
         <f>INDEX(WL_DAYS,7)-INDEX(EXCESS_DAYS,7)</f>
         <v>50540.0</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="18">
         <f>INDEX(EXCESS_DAYS,7)/INDEX(WL_DAYS,7)</f>
         <v>0.3917951309914919</v>
       </c>
@@ -2596,31 +2595,31 @@
         <f>INDEX(REASON_NO_BED,7)+INDEX(REASON_BEHAVIOR,7)+INDEX(REASON_SPECIAL_CARE,7)+INDEX(REASON_FINANCIAL,7)+INDEX(REASON_GUARDIANSHIP,7)+INDEX(REASON_PASARR,7)+INDEX(REASON_OTHER,7)</f>
         <v>191.0</v>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="18">
         <f>INDEX(REASON_NO_BED,7)/INDEX(REASON_SUM,7)</f>
         <v>0.2198952879581152</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="18">
         <f>INDEX(REASON_BEHAVIOR,7)/INDEX(REASON_SUM,7)</f>
         <v>0.2513089005235602</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="18">
         <f>INDEX(REASON_SPECIAL_CARE,7)/INDEX(REASON_SUM,7)</f>
         <v>0.13612565445026178</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="18">
         <f>INDEX(REASON_FINANCIAL,7)/INDEX(REASON_SUM,7)</f>
         <v>0.2356020942408377</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="18">
         <f>INDEX(REASON_GUARDIANSHIP,7)/INDEX(REASON_SUM,7)</f>
         <v>0.14659685863874344</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="18">
         <f>INDEX(REASON_PASARR,7)/INDEX(REASON_SUM,7)</f>
         <v>0.005235602094240838</v>
       </c>
-      <c r="S10" s="19">
+      <c r="S10" s="18">
         <f>INDEX(REASON_OTHER,7)/INDEX(REASON_SUM,7)</f>
         <v>0.005235602094240838</v>
       </c>
@@ -2646,7 +2645,7 @@
         <f>INDEX(WL_PATIENTS,8)*BENCH_DAYS</f>
         <v>43722.0</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="16">
         <f>INDEX(DAYS_PER_PT,8)-BENCH_DAYS</f>
         <v>5.492795389048993</v>
       </c>
@@ -2662,7 +2661,7 @@
         <f>INDEX(WL_DAYS,8)-INDEX(EXCESS_DAYS,8)</f>
         <v>43722.0</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="18">
         <f>INDEX(EXCESS_DAYS,8)/INDEX(WL_DAYS,8)</f>
         <v>0.281785925487877</v>
       </c>
@@ -2682,31 +2681,31 @@
         <f>INDEX(REASON_NO_BED,8)+INDEX(REASON_BEHAVIOR,8)+INDEX(REASON_SPECIAL_CARE,8)+INDEX(REASON_FINANCIAL,8)+INDEX(REASON_GUARDIANSHIP,8)+INDEX(REASON_PASARR,8)+INDEX(REASON_OTHER,8)</f>
         <v>173.0</v>
       </c>
-      <c r="M11" s="19">
+      <c r="M11" s="18">
         <f>INDEX(REASON_NO_BED,8)/INDEX(REASON_SUM,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="18">
         <f>INDEX(REASON_BEHAVIOR,8)/INDEX(REASON_SUM,8)</f>
         <v>0.1676300578034682</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="18">
         <f>INDEX(REASON_SPECIAL_CARE,8)/INDEX(REASON_SUM,8)</f>
         <v>0.10404624277456648</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="18">
         <f>INDEX(REASON_FINANCIAL,8)/INDEX(REASON_SUM,8)</f>
         <v>0.3468208092485549</v>
       </c>
-      <c r="Q11" s="19">
+      <c r="Q11" s="18">
         <f>INDEX(REASON_GUARDIANSHIP,8)/INDEX(REASON_SUM,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="R11" s="19">
+      <c r="R11" s="18">
         <f>INDEX(REASON_PASARR,8)/INDEX(REASON_SUM,8)</f>
         <v>0.0</v>
       </c>
-      <c r="S11" s="19">
+      <c r="S11" s="18">
         <f>INDEX(REASON_OTHER,8)/INDEX(REASON_SUM,8)</f>
         <v>0.023121387283236993</v>
       </c>
@@ -2832,7 +2831,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Excess days</t>
         </is>
@@ -2856,7 +2855,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Waitlisted rate, January</t>
         </is>
@@ -2866,17 +2865,17 @@
           <t>USD per day</t>
         </is>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="20">
         <f>INDEX(WL_RATE_JAN,MATCH(2023,YEAR,0))</f>
         <v>283.6</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <f>INDEX(WL_RATE_JAN,MATCH(2024,YEAR,0))</f>
         <v>464.97</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Waitlisted rate, July</t>
         </is>
@@ -2886,17 +2885,17 @@
           <t>USD per day</t>
         </is>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="20">
         <f>INDEX(WL_RATE_JUL,MATCH(2023,YEAR,0))</f>
         <v>302.89</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <f>INDEX(WL_RATE_JUL,MATCH(2024,YEAR,0))</f>
         <v>455.59</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+    <row r="7" ht="31" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Average waitlisted rate (WL_RATE_AVG); Now = WL_RATE_2026</t>
         </is>
@@ -2906,21 +2905,21 @@
           <t>USD per day</t>
         </is>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="20">
         <f>(INDEX(WL_RATE_JAN,MATCH(2023,YEAR,0))+INDEX(WL_RATE_JUL,MATCH(2023,YEAR,0)))/2</f>
         <v>293.245</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="20">
         <f>(INDEX(WL_RATE_JAN,MATCH(2024,YEAR,0))+INDEX(WL_RATE_JUL,MATCH(2024,YEAR,0)))/2</f>
         <v>460.28</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="20">
         <f>WL_RATE_2026</f>
         <v>486.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Net cost per day, low (NET_COST_LO)</t>
         </is>
@@ -2930,21 +2929,21 @@
           <t>USD per day</t>
         </is>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="20">
         <f>AVOID_COST_LO-INDEX(WL_RATE_AVG,1)</f>
         <v>256.755</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="20">
         <f>AVOID_COST_LO-INDEX(WL_RATE_AVG,2)</f>
         <v>89.72000000000003</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <f>AVOID_COST_LO-WL_RATE_2026</f>
         <v>63.24000000000001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Net cost per day, high (NET_COST_HI)</t>
         </is>
@@ -2954,21 +2953,21 @@
           <t>USD per day</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="20">
         <f>AVOID_COST_HI-INDEX(WL_RATE_AVG,1)</f>
         <v>1176.755</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="20">
         <f>AVOID_COST_HI-INDEX(WL_RATE_AVG,2)</f>
         <v>1009.72</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <f>AVOID_COST_HI-WL_RATE_2026</f>
         <v>983.24</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Cost of excess days, low (EXCESS_COST_LO)</t>
         </is>
@@ -2978,21 +2977,21 @@
           <t>USD per year</t>
         </is>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="21">
         <f>INDEX(EXCESS_DAYS,MATCH(2023,YEAR,0))*INDEX(NET_COST_LO,1)</f>
         <v>8359172.535</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="21">
         <f>INDEX(EXCESS_DAYS,MATCH(2024,YEAR,0))*INDEX(NET_COST_LO,2)</f>
         <v>1539056.8800000004</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="21">
         <f>INDEX(EXCESS_DAYS,MATCH(2024,YEAR,0))*NET_COST_LO_NOW</f>
         <v>1084818.9600000002</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Cost of excess days, high (EXCESS_COST_HI)</t>
         </is>
@@ -3002,21 +3001,21 @@
           <t>USD per year</t>
         </is>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="21">
         <f>INDEX(EXCESS_DAYS,MATCH(2023,YEAR,0))*INDEX(NET_COST_HI,1)</f>
         <v>38311612.535000004</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="21">
         <f>INDEX(EXCESS_DAYS,MATCH(2024,YEAR,0))*INDEX(NET_COST_HI,2)</f>
         <v>17320736.88</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="21">
         <f>INDEX(EXCESS_DAYS,MATCH(2024,YEAR,0))*NET_COST_HI_NOW</f>
         <v>16866498.96</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+    <row r="12" ht="31" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Nursing-facility share of Dec 31 waitlist (NF_SHARE_DEC31), reported beside the result only</t>
         </is>
@@ -3026,17 +3025,17 @@
           <t>share</t>
         </is>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="18">
         <f>INDEX(DEC31_NF,MATCH(2023,YEAR,0))/INDEX(DEC31_TOTAL,MATCH(2023,YEAR,0))</f>
         <v>0.8219895287958116</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="18">
         <f>INDEX(DEC31_NF,MATCH(2024,YEAR,0))/INDEX(DEC31_TOTAL,MATCH(2024,YEAR,0))</f>
         <v>0.6936416184971098</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="14" ht="31" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Change in waitlist days, 2023 to 2024 (WL_DAYS_CHANGE_2024)</t>
         </is>
@@ -3046,7 +3045,7 @@
           <t>share</t>
         </is>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <f>INDEX(WL_DAYS,MATCH(2024,YEAR,0))/INDEX(WL_DAYS,MATCH(2023,YEAR,0))-1</f>
         <v>-0.26741037582584204</v>
       </c>
@@ -3062,7 +3061,7 @@
           <t>USD per day</t>
         </is>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <f>WL_RATE_LEAHI_2026</f>
         <v>480.19</v>
       </c>
@@ -3093,7 +3092,7 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -3130,7 +3129,7 @@
           <t>Financial share, Dec 31 2020</t>
         </is>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="18">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2020,YEAR,0))</f>
         <v>0.20833333333333334</v>
       </c>
@@ -3146,7 +3145,7 @@
           <t>Financial share, Dec 31 2021</t>
         </is>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="18">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2021,YEAR,0))</f>
         <v>0.2275132275132275</v>
       </c>
@@ -3162,7 +3161,7 @@
           <t>Drop, 2020 to 2021 (T1_DROP_2021; negative = rise)</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="18">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2020,YEAR,0))-INDEX(SHARE_FINANCIAL,MATCH(2021,YEAR,0))</f>
         <v>-0.019179894179894158</v>
       </c>
@@ -3194,7 +3193,7 @@
           <t>Financial share, Dec 31 2023</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="18">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2023,YEAR,0))</f>
         <v>0.2356020942408377</v>
       </c>
@@ -3205,7 +3204,7 @@
           <t>Financial share, Dec 31 2024</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="18">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2024,YEAR,0))</f>
         <v>0.3468208092485549</v>
       </c>
@@ -3216,7 +3215,7 @@
           <t>Drop, 2023 to 2024 (T1_DROP_2024; negative = rise)</t>
         </is>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="18">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2023,YEAR,0))-INDEX(SHARE_FINANCIAL,MATCH(2024,YEAR,0))</f>
         <v>-0.11121871500771721</v>
       </c>
@@ -3281,7 +3280,7 @@
           <t>Least-squares slope of days per patient, 2017 to 2023 (T2_SLOPE)</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="16">
         <f>SLOPE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7),INDEX(YEAR,1):INDEX(YEAR,7))</f>
         <v>1.8814212714379457</v>
       </c>
@@ -3633,11 +3632,11 @@
         <f>INDEX(CTY_DAYS,1,2)/INDEX(CTY_PATIENTS,1,2)</f>
         <v>27.74965612104539</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="18">
         <f>INDEX(CTY_DAYS,1,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.27933619745598515</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="18">
         <f>INDEX(CTY_DAYS,1,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.33139496681779357</v>
       </c>
@@ -3655,11 +3654,11 @@
         <f>INDEX(CTY_DAYS,2,2)/INDEX(CTY_PATIENTS,2,2)</f>
         <v>13.835270338554826</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="18">
         <f>INDEX(CTY_DAYS,2,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.4853003116839356</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="18">
         <f>INDEX(CTY_DAYS,2,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.4497667389447401</v>
       </c>
@@ -3677,11 +3676,11 @@
         <f>INDEX(CTY_DAYS,3,2)/INDEX(CTY_PATIENTS,3,2)</f>
         <v>30.109375</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <f>INDEX(CTY_DAYS,3,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.02069870151750364</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <f>INDEX(CTY_DAYS,3,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.031654510808857346</v>
       </c>
@@ -3699,11 +3698,11 @@
         <f>INDEX(CTY_DAYS,4,2)/INDEX(CTY_PATIENTS,4,2)</f>
         <v>32.28045325779037</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="18">
         <f>INDEX(CTY_DAYS,4,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.21466478934257555</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <f>INDEX(CTY_DAYS,4,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.18718378342860897</v>
       </c>
@@ -3714,11 +3713,11 @@
           <t>Total share</t>
         </is>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="18">
         <f>INDEX(CTY_DAY_SHARE,1,1)+INDEX(CTY_DAY_SHARE,2,1)+INDEX(CTY_DAY_SHARE,3,1)+INDEX(CTY_DAY_SHARE,4,1)</f>
         <v>1.0</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="18">
         <f>INDEX(CTY_DAY_SHARE,1,2)+INDEX(CTY_DAY_SHARE,2,2)+INDEX(CTY_DAY_SHARE,3,2)+INDEX(CTY_DAY_SHARE,4,2)</f>
         <v>1.0</v>
       </c>
@@ -3744,7 +3743,7 @@
   <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -3752,7 +3751,7 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3801,11 +3800,11 @@
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="22">
         <f>DATE(INDEX(YEAR,1),7,1)</f>
         <v>42917</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="16">
         <f>INDEX(DAYS_PER_PT,1)</f>
         <v>9.935348310974625</v>
       </c>
@@ -3823,11 +3822,11 @@
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="22">
         <f>DATE(INDEX(YEAR,2),7,1)</f>
         <v>43282</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="16">
         <f>INDEX(DAYS_PER_PT,2)</f>
         <v>12.484132980732905</v>
       </c>
@@ -3845,11 +3844,11 @@
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="22">
         <f>DATE(INDEX(YEAR,3),7,1)</f>
         <v>43647</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="16">
         <f>INDEX(DAYS_PER_PT,3)</f>
         <v>16.4741127348643</v>
       </c>
@@ -3867,11 +3866,11 @@
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="22">
         <f>DATE(INDEX(YEAR,4),7,1)</f>
         <v>44013</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="16">
         <f>INDEX(DAYS_PER_PT,4)</f>
         <v>12.584449813309906</v>
       </c>
@@ -3889,11 +3888,11 @@
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="22">
         <f>DATE(INDEX(YEAR,5),7,1)</f>
         <v>44378</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="16">
         <f>INDEX(DAYS_PER_PT,5)</f>
         <v>12.187943982139233</v>
       </c>
@@ -3911,11 +3910,11 @@
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="22">
         <f>DATE(INDEX(YEAR,6),7,1)</f>
         <v>44743</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="16">
         <f>INDEX(DAYS_PER_PT,6)</f>
         <v>21.34229828850856</v>
       </c>
@@ -3933,11 +3932,11 @@
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="22">
         <f>DATE(INDEX(YEAR,7),7,1)</f>
         <v>45108</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="16">
         <f>INDEX(DAYS_PER_PT,7)</f>
         <v>23.018559556786702</v>
       </c>
@@ -3955,11 +3954,11 @@
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="22">
         <f>DATE(INDEX(YEAR,8),7,1)</f>
         <v>45474</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="16">
         <f>INDEX(DAYS_PER_PT,8)</f>
         <v>19.492795389048993</v>
       </c>
@@ -3997,7 +3996,7 @@
           <t>12% adjustment for private homes</t>
         </is>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="22">
         <f>DATE_ADJ_2021</f>
         <v>44209</v>
       </c>
@@ -4008,7 +4007,7 @@
           <t>Rate reset</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="22">
         <f>DATE_RESET_2024</f>
         <v>45292</v>
       </c>
@@ -4072,31 +4071,31 @@
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <f>INDEX(SHARE_NO_BED,1)</f>
         <v>0.325</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="18">
         <f>INDEX(SHARE_BEHAVIOR,1)</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="18">
         <f>INDEX(SHARE_SPECIAL_CARE,1)</f>
         <v>0.19166666666666668</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="18">
         <f>INDEX(SHARE_FINANCIAL,1)</f>
         <v>0.15</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="18">
         <f>INDEX(SHARE_GUARDIANSHIP,1)</f>
         <v>0.09166666666666666</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="18">
         <f>INDEX(SHARE_PASARR,1)</f>
         <v>0.016666666666666666</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="18">
         <f>INDEX(SHARE_OTHER,1)</f>
         <v>0.09166666666666666</v>
       </c>
@@ -4110,31 +4109,31 @@
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="18">
         <f>INDEX(SHARE_NO_BED,2)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="18">
         <f>INDEX(SHARE_BEHAVIOR,2)</f>
         <v>0.1695906432748538</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="18">
         <f>INDEX(SHARE_SPECIAL_CARE,2)</f>
         <v>0.09941520467836257</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="18">
         <f>INDEX(SHARE_FINANCIAL,2)</f>
         <v>0.18128654970760233</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="18">
         <f>INDEX(SHARE_GUARDIANSHIP,2)</f>
         <v>0.10526315789473684</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="18">
         <f>INDEX(SHARE_PASARR,2)</f>
         <v>0.011695906432748537</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="18">
         <f>INDEX(SHARE_OTHER,2)</f>
         <v>0.09941520467836257</v>
       </c>
@@ -4148,31 +4147,31 @@
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="18">
         <f>INDEX(SHARE_NO_BED,3)</f>
         <v>0.391304347826087</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="18">
         <f>INDEX(SHARE_BEHAVIOR,3)</f>
         <v>0.14673913043478262</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="18">
         <f>INDEX(SHARE_SPECIAL_CARE,3)</f>
         <v>0.11413043478260869</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="18">
         <f>INDEX(SHARE_FINANCIAL,3)</f>
         <v>0.17391304347826086</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="18">
         <f>INDEX(SHARE_GUARDIANSHIP,3)</f>
         <v>0.14130434782608695</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="18">
         <f>INDEX(SHARE_PASARR,3)</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="18">
         <f>INDEX(SHARE_OTHER,3)</f>
         <v>0.03260869565217391</v>
       </c>
@@ -4186,31 +4185,31 @@
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="18">
         <f>INDEX(SHARE_NO_BED,4)</f>
         <v>0.2847222222222222</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="18">
         <f>INDEX(SHARE_BEHAVIOR,4)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="18">
         <f>INDEX(SHARE_SPECIAL_CARE,4)</f>
         <v>0.1527777777777778</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="18">
         <f>INDEX(SHARE_FINANCIAL,4)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="18">
         <f>INDEX(SHARE_GUARDIANSHIP,4)</f>
         <v>0.10416666666666667</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="18">
         <f>INDEX(SHARE_PASARR,4)</f>
         <v>0.0</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="18">
         <f>INDEX(SHARE_OTHER,4)</f>
         <v>0.08333333333333333</v>
       </c>
@@ -4224,31 +4223,31 @@
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="18">
         <f>INDEX(SHARE_NO_BED,5)</f>
         <v>0.26455026455026454</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="18">
         <f>INDEX(SHARE_BEHAVIOR,5)</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="18">
         <f>INDEX(SHARE_SPECIAL_CARE,5)</f>
         <v>0.1164021164021164</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="18">
         <f>INDEX(SHARE_FINANCIAL,5)</f>
         <v>0.2275132275132275</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="18">
         <f>INDEX(SHARE_GUARDIANSHIP,5)</f>
         <v>0.10582010582010581</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="18">
         <f>INDEX(SHARE_PASARR,5)</f>
         <v>0.0</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="18">
         <f>INDEX(SHARE_OTHER,5)</f>
         <v>0.09523809523809523</v>
       </c>
@@ -4262,31 +4261,31 @@
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="18">
         <f>INDEX(SHARE_NO_BED,6)</f>
         <v>0.228</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="18">
         <f>INDEX(SHARE_BEHAVIOR,6)</f>
         <v>0.14</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="18">
         <f>INDEX(SHARE_SPECIAL_CARE,6)</f>
         <v>0.156</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="18">
         <f>INDEX(SHARE_FINANCIAL,6)</f>
         <v>0.3</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="18">
         <f>INDEX(SHARE_GUARDIANSHIP,6)</f>
         <v>0.116</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="18">
         <f>INDEX(SHARE_PASARR,6)</f>
         <v>0.02</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="18">
         <f>INDEX(SHARE_OTHER,6)</f>
         <v>0.04</v>
       </c>
@@ -4300,31 +4299,31 @@
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="18">
         <f>INDEX(SHARE_NO_BED,7)</f>
         <v>0.2198952879581152</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="18">
         <f>INDEX(SHARE_BEHAVIOR,7)</f>
         <v>0.2513089005235602</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="18">
         <f>INDEX(SHARE_SPECIAL_CARE,7)</f>
         <v>0.13612565445026178</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="18">
         <f>INDEX(SHARE_FINANCIAL,7)</f>
         <v>0.2356020942408377</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="18">
         <f>INDEX(SHARE_GUARDIANSHIP,7)</f>
         <v>0.14659685863874344</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="18">
         <f>INDEX(SHARE_PASARR,7)</f>
         <v>0.005235602094240838</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="18">
         <f>INDEX(SHARE_OTHER,7)</f>
         <v>0.005235602094240838</v>
       </c>
@@ -4338,31 +4337,31 @@
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="18">
         <f>INDEX(SHARE_NO_BED,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="18">
         <f>INDEX(SHARE_BEHAVIOR,8)</f>
         <v>0.1676300578034682</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="18">
         <f>INDEX(SHARE_SPECIAL_CARE,8)</f>
         <v>0.10404624277456648</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="18">
         <f>INDEX(SHARE_FINANCIAL,8)</f>
         <v>0.3468208092485549</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="18">
         <f>INDEX(SHARE_GUARDIANSHIP,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="18">
         <f>INDEX(SHARE_PASARR,8)</f>
         <v>0.0</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="18">
         <f>INDEX(SHARE_OTHER,8)</f>
         <v>0.023121387283236993</v>
       </c>
@@ -4401,11 +4400,11 @@
           <t>Across the 12% adjustment</t>
         </is>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="23">
         <f>YEAR(DATE_ADJ_2021)-1</f>
         <v>2020.0</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="23">
         <f>YEAR(DATE_ADJ_2021)</f>
         <v>2021</v>
       </c>
@@ -4416,11 +4415,11 @@
           <t>Across the reset</t>
         </is>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="23">
         <f>YEAR(DATE_RESET_2024)-1</f>
         <v>2023.0</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="23">
         <f>YEAR(DATE_RESET_2024)</f>
         <v>2024</v>
       </c>
@@ -4454,7 +4453,7 @@
         <f>DATE(2016,1,1)</f>
         <v>42370</v>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="20">
         <f>IF(ISNA(MATCH(A37,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A37,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A37,RATE_DATE,0))))</f>
         <v>246.97</v>
       </c>
@@ -4468,7 +4467,7 @@
         <f>DATE(2016,7,1)</f>
         <v>42552</v>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="20">
         <f>IF(ISNA(MATCH(A38,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A38,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A38,RATE_DATE,0))))</f>
         <v>252.4</v>
       </c>
@@ -4482,7 +4481,7 @@
         <f>DATE(2017,1,1)</f>
         <v>42736</v>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="20">
         <f>IF(ISNA(MATCH(A39,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A39,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A39,RATE_DATE,0))))</f>
         <v>251.93</v>
       </c>
@@ -4496,7 +4495,7 @@
         <f>DATE(2017,7,1)</f>
         <v>42917</v>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="20">
         <f>IF(ISNA(MATCH(A40,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A40,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A40,RATE_DATE,0))))</f>
         <v>261.45</v>
       </c>
@@ -4510,7 +4509,7 @@
         <f>DATE(2018,1,1)</f>
         <v>43101</v>
       </c>
-      <c r="B41" s="21" t="str">
+      <c r="B41" s="20" t="str">
         <f>IF(ISNA(MATCH(A41,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A41,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A41,RATE_DATE,0))))</f>
         <v/>
       </c>
@@ -4524,7 +4523,7 @@
         <f>DATE(2018,7,1)</f>
         <v>43282</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="20">
         <f>IF(ISNA(MATCH(A42,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A42,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A42,RATE_DATE,0))))</f>
         <v>270.66</v>
       </c>
@@ -4538,7 +4537,7 @@
         <f>DATE(2019,1,1)</f>
         <v>43466</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="20">
         <f>IF(ISNA(MATCH(A43,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A43,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A43,RATE_DATE,0))))</f>
         <v>270.15</v>
       </c>
@@ -4552,7 +4551,7 @@
         <f>DATE(2019,7,1)</f>
         <v>43647</v>
       </c>
-      <c r="B44" s="21" t="str">
+      <c r="B44" s="20" t="str">
         <f>IF(ISNA(MATCH(A44,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A44,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A44,RATE_DATE,0))))</f>
         <v/>
       </c>
@@ -4566,7 +4565,7 @@
         <f>DATE(2020,1,1)</f>
         <v>43831</v>
       </c>
-      <c r="B45" s="21" t="str">
+      <c r="B45" s="20" t="str">
         <f>IF(ISNA(MATCH(A45,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A45,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A45,RATE_DATE,0))))</f>
         <v/>
       </c>
@@ -4580,7 +4579,7 @@
         <f>DATE(2020,7,1)</f>
         <v>44013</v>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="20">
         <f>IF(ISNA(MATCH(A46,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A46,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A46,RATE_DATE,0))))</f>
         <v>282.98</v>
       </c>
@@ -4594,7 +4593,7 @@
         <f>DATE(2021,1,1)</f>
         <v>44197</v>
       </c>
-      <c r="B47" s="21" t="str">
+      <c r="B47" s="20" t="str">
         <f>IF(ISNA(MATCH(A47,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A47,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A47,RATE_DATE,0))))</f>
         <v/>
       </c>
@@ -4608,7 +4607,7 @@
         <f>DATE(2021,7,1)</f>
         <v>44378</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="20">
         <f>IF(ISNA(MATCH(A48,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A48,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A48,RATE_DATE,0))))</f>
         <v>334.75</v>
       </c>
@@ -4622,7 +4621,7 @@
         <f>DATE(2022,1,1)</f>
         <v>44562</v>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="20">
         <f>IF(ISNA(MATCH(A49,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A49,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A49,RATE_DATE,0))))</f>
         <v>332.59</v>
       </c>
@@ -4636,7 +4635,7 @@
         <f>DATE(2022,7,1)</f>
         <v>44743</v>
       </c>
-      <c r="B50" s="21" t="str">
+      <c r="B50" s="20" t="str">
         <f>IF(ISNA(MATCH(A50,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A50,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A50,RATE_DATE,0))))</f>
         <v/>
       </c>
@@ -4650,7 +4649,7 @@
         <f>DATE(2023,1,1)</f>
         <v>44927</v>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="20">
         <f>IF(ISNA(MATCH(A51,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A51,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A51,RATE_DATE,0))))</f>
         <v>355.11</v>
       </c>
@@ -4664,7 +4663,7 @@
         <f>DATE(2023,7,1)</f>
         <v>45108</v>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="20">
         <f>IF(ISNA(MATCH(A52,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A52,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A52,RATE_DATE,0))))</f>
         <v>371.99</v>
       </c>
@@ -4678,7 +4677,7 @@
         <f>DATE(2024,1,1)</f>
         <v>45292</v>
       </c>
-      <c r="B53" s="21">
+      <c r="B53" s="20">
         <f>IF(ISNA(MATCH(A53,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A53,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A53,RATE_DATE,0))))</f>
         <v>481.83</v>
       </c>
@@ -4692,7 +4691,7 @@
         <f>DATE(2024,7,1)</f>
         <v>45474</v>
       </c>
-      <c r="B54" s="21">
+      <c r="B54" s="20">
         <f>IF(ISNA(MATCH(A54,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A54,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A54,RATE_DATE,0))))</f>
         <v>482.2</v>
       </c>
@@ -4706,7 +4705,7 @@
         <f>DATE(2025,1,1)</f>
         <v>45658</v>
       </c>
-      <c r="B55" s="21">
+      <c r="B55" s="20">
         <f>IF(ISNA(MATCH(A55,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A55,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A55,RATE_DATE,0))))</f>
         <v>509.69</v>
       </c>
@@ -4720,7 +4719,7 @@
         <f>DATE(2025,7,1)</f>
         <v>45839</v>
       </c>
-      <c r="B56" s="21">
+      <c r="B56" s="20">
         <f>IF(ISNA(MATCH(A56,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A56,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A56,RATE_DATE,0))))</f>
         <v>506.65</v>
       </c>
@@ -4734,7 +4733,7 @@
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
       </c>
-      <c r="B57" s="21">
+      <c r="B57" s="20">
         <f>IF(ISNA(MATCH(A57,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A57,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A57,RATE_DATE,0))))</f>
         <v>495.25</v>
       </c>
@@ -4777,15 +4776,15 @@
         <f>INDEX(COST_FY,1)</f>
         <v>2011</v>
       </c>
-      <c r="B61" s="25">
+      <c r="B61" s="22">
         <f>DATE(INDEX(COST_FY,1),7,1)</f>
         <v>40725</v>
       </c>
-      <c r="C61" s="21">
+      <c r="C61" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,1)</f>
         <v>287.76</v>
       </c>
-      <c r="D61" s="21">
+      <c r="D61" s="20">
         <f>INDEX(NF_COST_ALL,1)</f>
         <v>295.13</v>
       </c>
@@ -4795,15 +4794,15 @@
         <f>INDEX(COST_FY,2)</f>
         <v>2012</v>
       </c>
-      <c r="B62" s="25">
+      <c r="B62" s="22">
         <f>DATE(INDEX(COST_FY,2),7,1)</f>
         <v>41091</v>
       </c>
-      <c r="C62" s="21">
+      <c r="C62" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,2)</f>
         <v>311.89</v>
       </c>
-      <c r="D62" s="21">
+      <c r="D62" s="20">
         <f>INDEX(NF_COST_ALL,2)</f>
         <v>314.68</v>
       </c>
@@ -4813,15 +4812,15 @@
         <f>INDEX(COST_FY,3)</f>
         <v>2013</v>
       </c>
-      <c r="B63" s="25">
+      <c r="B63" s="22">
         <f>DATE(INDEX(COST_FY,3),7,1)</f>
         <v>41456</v>
       </c>
-      <c r="C63" s="21">
+      <c r="C63" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,3)</f>
         <v>322.2</v>
       </c>
-      <c r="D63" s="21">
+      <c r="D63" s="20">
         <f>INDEX(NF_COST_ALL,3)</f>
         <v>342.42</v>
       </c>
@@ -4831,15 +4830,15 @@
         <f>INDEX(COST_FY,4)</f>
         <v>2014</v>
       </c>
-      <c r="B64" s="25">
+      <c r="B64" s="22">
         <f>DATE(INDEX(COST_FY,4),7,1)</f>
         <v>41821</v>
       </c>
-      <c r="C64" s="21">
+      <c r="C64" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,4)</f>
         <v>322.2</v>
       </c>
-      <c r="D64" s="21">
+      <c r="D64" s="20">
         <f>INDEX(NF_COST_ALL,4)</f>
         <v>344.18</v>
       </c>
@@ -4849,15 +4848,15 @@
         <f>INDEX(COST_FY,5)</f>
         <v>2015</v>
       </c>
-      <c r="B65" s="25">
+      <c r="B65" s="22">
         <f>DATE(INDEX(COST_FY,5),7,1)</f>
         <v>42186</v>
       </c>
-      <c r="C65" s="21">
+      <c r="C65" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,5)</f>
         <v>322.11</v>
       </c>
-      <c r="D65" s="21">
+      <c r="D65" s="20">
         <f>INDEX(NF_COST_ALL,5)</f>
         <v>340.9</v>
       </c>
@@ -4867,15 +4866,15 @@
         <f>INDEX(COST_FY,6)</f>
         <v>2016</v>
       </c>
-      <c r="B66" s="25">
+      <c r="B66" s="22">
         <f>DATE(INDEX(COST_FY,6),7,1)</f>
         <v>42552</v>
       </c>
-      <c r="C66" s="21">
+      <c r="C66" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,6)</f>
         <v>344.38</v>
       </c>
-      <c r="D66" s="21">
+      <c r="D66" s="20">
         <f>INDEX(NF_COST_ALL,6)</f>
         <v>358.8</v>
       </c>
@@ -4885,15 +4884,15 @@
         <f>INDEX(COST_FY,7)</f>
         <v>2017</v>
       </c>
-      <c r="B67" s="25">
+      <c r="B67" s="22">
         <f>DATE(INDEX(COST_FY,7),7,1)</f>
         <v>42917</v>
       </c>
-      <c r="C67" s="21">
+      <c r="C67" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,7)</f>
         <v>356.1</v>
       </c>
-      <c r="D67" s="21">
+      <c r="D67" s="20">
         <f>INDEX(NF_COST_ALL,7)</f>
         <v>376.01</v>
       </c>
@@ -4903,15 +4902,15 @@
         <f>INDEX(COST_FY,8)</f>
         <v>2018</v>
       </c>
-      <c r="B68" s="25">
+      <c r="B68" s="22">
         <f>DATE(INDEX(COST_FY,8),7,1)</f>
         <v>43282</v>
       </c>
-      <c r="C68" s="21">
+      <c r="C68" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,8)</f>
         <v>365.93</v>
       </c>
-      <c r="D68" s="21">
+      <c r="D68" s="20">
         <f>INDEX(NF_COST_ALL,8)</f>
         <v>380.99</v>
       </c>
@@ -4921,15 +4920,15 @@
         <f>INDEX(COST_FY,9)</f>
         <v>2019</v>
       </c>
-      <c r="B69" s="25">
+      <c r="B69" s="22">
         <f>DATE(INDEX(COST_FY,9),7,1)</f>
         <v>43647</v>
       </c>
-      <c r="C69" s="21">
+      <c r="C69" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,9)</f>
         <v>373.25</v>
       </c>
-      <c r="D69" s="21">
+      <c r="D69" s="20">
         <f>INDEX(NF_COST_ALL,9)</f>
         <v>379.87</v>
       </c>
@@ -4939,15 +4938,15 @@
         <f>INDEX(COST_FY,10)</f>
         <v>2020</v>
       </c>
-      <c r="B70" s="25">
+      <c r="B70" s="22">
         <f>DATE(INDEX(COST_FY,10),7,1)</f>
         <v>44013</v>
       </c>
-      <c r="C70" s="21">
+      <c r="C70" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,10)</f>
         <v>398.33</v>
       </c>
-      <c r="D70" s="21">
+      <c r="D70" s="20">
         <f>INDEX(NF_COST_ALL,10)</f>
         <v>428.4</v>
       </c>
@@ -4957,15 +4956,15 @@
         <f>INDEX(COST_FY,11)</f>
         <v>2021</v>
       </c>
-      <c r="B71" s="25">
+      <c r="B71" s="22">
         <f>DATE(INDEX(COST_FY,11),7,1)</f>
         <v>44378</v>
       </c>
-      <c r="C71" s="21">
+      <c r="C71" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,11)</f>
         <v>423.44</v>
       </c>
-      <c r="D71" s="21">
+      <c r="D71" s="20">
         <f>INDEX(NF_COST_ALL,11)</f>
         <v>450.4</v>
       </c>
@@ -4975,15 +4974,15 @@
         <f>INDEX(COST_FY,12)</f>
         <v>2022</v>
       </c>
-      <c r="B72" s="25">
+      <c r="B72" s="22">
         <f>DATE(INDEX(COST_FY,12),7,1)</f>
         <v>44743</v>
       </c>
-      <c r="C72" s="21">
+      <c r="C72" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,12)</f>
         <v>435.63</v>
       </c>
-      <c r="D72" s="21">
+      <c r="D72" s="20">
         <f>INDEX(NF_COST_ALL,12)</f>
         <v>459.47</v>
       </c>
@@ -4993,15 +4992,15 @@
         <f>INDEX(COST_FY,13)</f>
         <v>2023</v>
       </c>
-      <c r="B73" s="25">
+      <c r="B73" s="22">
         <f>DATE(INDEX(COST_FY,13),7,1)</f>
         <v>45108</v>
       </c>
-      <c r="C73" s="21">
+      <c r="C73" s="20">
         <f>INDEX(NF_COST_MCD_HEAVY,13)</f>
         <v>461.78</v>
       </c>
-      <c r="D73" s="21">
+      <c r="D73" s="20">
         <f>INDEX(NF_COST_ALL,13)</f>
         <v>519.16</v>
       </c>
@@ -5201,10 +5200,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5248,7 +5247,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27">
+      <c r="A4" s="24">
         <f>1</f>
         <v>1</v>
       </c>
@@ -5257,11 +5256,11 @@
           <t>DAYS_PER_PT(2023)</t>
         </is>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="25">
         <f>INDEX(DAYS_PER_PT,MATCH(2023,YEAR,0))</f>
         <v>23.018559556786702</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="25">
         <f>23.02</f>
         <v>23.02</v>
       </c>
@@ -5275,7 +5274,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27">
+      <c r="A5" s="24">
         <f>2</f>
         <v>2</v>
       </c>
@@ -5284,11 +5283,11 @@
           <t>DAYS_PER_PT(2024)</t>
         </is>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="25">
         <f>INDEX(DAYS_PER_PT,MATCH(2024,YEAR,0))</f>
         <v>19.492795389048993</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="25">
         <f>19.49</f>
         <v>19.49</v>
       </c>
@@ -5302,7 +5301,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27">
+      <c r="A6" s="24">
         <f>3</f>
         <v>3</v>
       </c>
@@ -5329,7 +5328,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27">
+      <c r="A7" s="24">
         <f>4</f>
         <v>4</v>
       </c>
@@ -5356,7 +5355,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27">
+      <c r="A8" s="24">
         <f>5</f>
         <v>5</v>
       </c>
@@ -5383,7 +5382,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27">
+      <c r="A9" s="24">
         <f>6</f>
         <v>6</v>
       </c>
@@ -5410,7 +5409,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27">
+      <c r="A10" s="24">
         <f>7</f>
         <v>7</v>
       </c>
@@ -5437,7 +5436,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27">
+      <c r="A11" s="24">
         <f>8</f>
         <v>8</v>
       </c>
@@ -5446,11 +5445,11 @@
           <t>GAP_PER_PT(2017)</t>
         </is>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="25">
         <f>INDEX(GAP_PER_PT,MATCH(2017,YEAR,0))</f>
         <v>-4.064651689025375</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="25">
         <f>-4.06</f>
         <v>-4.06</v>
       </c>
@@ -5464,7 +5463,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27">
+      <c r="A12" s="24">
         <f>9</f>
         <v>9</v>
       </c>
@@ -5473,11 +5472,11 @@
           <t>GAP_PER_PT(2024)</t>
         </is>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="25">
         <f>INDEX(GAP_PER_PT,MATCH(2024,YEAR,0))</f>
         <v>5.492795389048993</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="25">
         <f>5.49</f>
         <v>5.49</v>
       </c>
@@ -5491,7 +5490,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27">
+      <c r="A13" s="24">
         <f>10</f>
         <v>10</v>
       </c>
@@ -5500,11 +5499,11 @@
           <t>WL_RATE_AVG(2023)</t>
         </is>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="26">
         <f>INDEX(WL_RATE_AVG,1)</f>
         <v>293.245</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="26">
         <f>293.245</f>
         <v>293.245</v>
       </c>
@@ -5518,7 +5517,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27">
+      <c r="A14" s="24">
         <f>11</f>
         <v>11</v>
       </c>
@@ -5527,11 +5526,11 @@
           <t>WL_RATE_AVG(2024)</t>
         </is>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="26">
         <f>INDEX(WL_RATE_AVG,2)</f>
         <v>460.28</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="26">
         <f>460.28</f>
         <v>460.28</v>
       </c>
@@ -5545,7 +5544,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27">
+      <c r="A15" s="24">
         <f>12</f>
         <v>12</v>
       </c>
@@ -5554,11 +5553,11 @@
           <t>NET_COST_LO(2024)</t>
         </is>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <f>INDEX(NET_COST_LO,2)</f>
         <v>89.72000000000003</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <f>89.72</f>
         <v>89.72</v>
       </c>
@@ -5572,7 +5571,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27">
+      <c r="A16" s="24">
         <f>13</f>
         <v>13</v>
       </c>
@@ -5581,11 +5580,11 @@
           <t>NET_COST_HI(2024)</t>
         </is>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <f>INDEX(NET_COST_HI,2)</f>
         <v>1009.72</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <f>1009.72</f>
         <v>1009.72</v>
       </c>
@@ -5599,7 +5598,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27">
+      <c r="A17" s="24">
         <f>14</f>
         <v>14</v>
       </c>
@@ -5608,11 +5607,11 @@
           <t>EXCESS_COST_LO(2024) (about)</t>
         </is>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="21">
         <f>INDEX(EXCESS_COST_LO,2)</f>
         <v>1539056.8800000004</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="21">
         <f>1539057</f>
         <v>1539057</v>
       </c>
@@ -5626,7 +5625,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27">
+      <c r="A18" s="24">
         <f>15</f>
         <v>15</v>
       </c>
@@ -5635,11 +5634,11 @@
           <t>EXCESS_COST_HI(2024) (about)</t>
         </is>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="21">
         <f>INDEX(EXCESS_COST_HI,2)</f>
         <v>17320736.88</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="21">
         <f>17320737</f>
         <v>17320737</v>
       </c>
@@ -5653,7 +5652,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27">
+      <c r="A19" s="24">
         <f>16</f>
         <v>16</v>
       </c>
@@ -5662,11 +5661,11 @@
           <t>NET_COST_LO_NOW</t>
         </is>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="20">
         <f>NET_COST_LO_NOW</f>
         <v>63.24000000000001</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="20">
         <f>63.24</f>
         <v>63.24</v>
       </c>
@@ -5680,7 +5679,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27">
+      <c r="A20" s="24">
         <f>17</f>
         <v>17</v>
       </c>
@@ -5689,11 +5688,11 @@
           <t>NET_COST_HI_NOW</t>
         </is>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="20">
         <f>NET_COST_HI_NOW</f>
         <v>983.24</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="20">
         <f>983.24</f>
         <v>983.24</v>
       </c>
@@ -5707,7 +5706,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27">
+      <c r="A21" s="24">
         <f>18</f>
         <v>18</v>
       </c>
@@ -5716,11 +5715,11 @@
           <t>WL_DAYS_CHANGE_2024</t>
         </is>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="18">
         <f>WL_DAYS_CHANGE_2024</f>
         <v>-0.26741037582584204</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="18">
         <f>-0.267</f>
         <v>-0.267</v>
       </c>
@@ -5734,7 +5733,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27">
+      <c r="A22" s="24">
         <f>19</f>
         <v>19</v>
       </c>
@@ -5743,11 +5742,11 @@
           <t>T1_DROP_2021 (points)</t>
         </is>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="25">
         <f>T1_DROP_2021*100</f>
         <v>-1.917989417989416</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="25">
         <f>-1.92</f>
         <v>-1.92</v>
       </c>
@@ -5761,7 +5760,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27">
+      <c r="A23" s="24">
         <f>20</f>
         <v>20</v>
       </c>
@@ -5770,11 +5769,11 @@
           <t>T1_DROP_2024 (points)</t>
         </is>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="25">
         <f>T1_DROP_2024*100</f>
         <v>-11.121871500771721</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="25">
         <f>-11.12</f>
         <v>-11.12</v>
       </c>
@@ -5788,7 +5787,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27">
+      <c r="A24" s="24">
         <f>21</f>
         <v>21</v>
       </c>
@@ -5797,11 +5796,11 @@
           <t>T2_SLOPE (about)</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="25">
         <f>T2_SLOPE</f>
         <v>1.8814212714379457</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="25">
         <f>1.88</f>
         <v>1.88</v>
       </c>
@@ -5815,7 +5814,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27">
+      <c r="A25" s="24">
         <f>22</f>
         <v>22</v>
       </c>
@@ -5842,7 +5841,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27">
+      <c r="A26" s="24">
         <f>23</f>
         <v>23</v>
       </c>
@@ -5869,7 +5868,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27">
+      <c r="A27" s="24">
         <f>24</f>
         <v>24</v>
       </c>
@@ -5896,7 +5895,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27">
+      <c r="A28" s="24">
         <f>25</f>
         <v>25</v>
       </c>
@@ -5923,7 +5922,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27">
+      <c r="A29" s="24">
         <f>26</f>
         <v>26</v>
       </c>
@@ -5950,7 +5949,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27">
+      <c r="A30" s="24">
         <f>27</f>
         <v>27</v>
       </c>
@@ -5977,7 +5976,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27">
+      <c r="A31" s="24">
         <f>28</f>
         <v>28</v>
       </c>
@@ -6004,7 +6003,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27">
+      <c r="A32" s="24">
         <f>29</f>
         <v>29</v>
       </c>
@@ -6013,11 +6012,11 @@
           <t>KFF_COST_DAY x 0.15</t>
         </is>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="20">
         <f>KFF_COST_DAY*0.15</f>
         <v>549.6</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32" s="20">
         <f>549.6</f>
         <v>549.6</v>
       </c>
@@ -6031,7 +6030,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27">
+      <c r="A33" s="24">
         <f>30</f>
         <v>30</v>
       </c>
@@ -6040,11 +6039,11 @@
           <t>KFF_COST_DAY x 0.40</t>
         </is>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="20">
         <f>KFF_COST_DAY*0.4</f>
         <v>1465.6000000000001</v>
       </c>
-      <c r="D33" s="21">
+      <c r="D33" s="20">
         <f>1465.6</f>
         <v>1465.6</v>
       </c>
@@ -6058,7 +6057,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27">
+      <c r="A34" s="24">
         <f>31</f>
         <v>31</v>
       </c>
@@ -6067,11 +6066,11 @@
           <t>KFF_COST_DAY x 0.15 within rounding (to $10) of AVOID_COST_LO</t>
         </is>
       </c>
-      <c r="C34" s="21">
+      <c r="C34" s="20">
         <f>KFF_COST_DAY*0.15</f>
         <v>549.6</v>
       </c>
-      <c r="D34" s="21">
+      <c r="D34" s="20">
         <f>AVOID_COST_LO</f>
         <v>550</v>
       </c>
@@ -6085,7 +6084,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27">
+      <c r="A35" s="24">
         <f>32</f>
         <v>32</v>
       </c>
@@ -6094,11 +6093,11 @@
           <t>KFF_COST_DAY x 0.40 within rounding (to $10) of AVOID_COST_HI</t>
         </is>
       </c>
-      <c r="C35" s="21">
+      <c r="C35" s="20">
         <f>KFF_COST_DAY*0.4</f>
         <v>1465.6000000000001</v>
       </c>
-      <c r="D35" s="21">
+      <c r="D35" s="20">
         <f>AVOID_COST_HI</f>
         <v>1470</v>
       </c>

--- a/capabilities/economic-research/model.xlsx
+++ b/capabilities/economic-research/model.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SPA HI-23-0014: 12% adjustment for private homes (first seen in the July 2021 memo)</t>
+          <t>SPA HI-23-0014, Attachment 4.19-D p. 38: 12% adjustment for private homes (first seen in the January 2021 memo, QI-2041)</t>
         </is>
       </c>
       <c r="P13" s="8" t="n"/>
@@ -1468,7 +1468,7 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Reason columns F to L; 2017 reasons sum to 120 against 157 by level of care (37 with no recorded reason). DEC31_NF and the waitlisted rates exist for 2023 and 2024 only (blank, not inputs, in other years).</t>
+          <t>Reason columns F to L; 2017 reasons sum to 120 against 157 by level of care (Maui Memorial records reasons for 6 of 47 patients; Queen's Punchbowl's reasons sum to 43 against 39). DEC31_NF and the waitlisted rates exist for 2023 and 2024 only (blank, not inputs, in other years).</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>No median in this memo (left blank)</t>
+          <t>Left blank: QI-1911B, the controlling July 2019 memo, lists but omits its acuity rate table</t>
         </is>
       </c>
       <c r="P47" s="8" t="n"/>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>495.25</v>
+        <v>495.26</v>
       </c>
       <c r="P57" s="8" t="n"/>
       <c r="Q57" s="8" t="n"/>
@@ -2009,7 +2009,7 @@
         <v>2014</v>
       </c>
       <c r="B64" s="11" t="n">
-        <v>344.18</v>
+        <v>344.19</v>
       </c>
       <c r="C64" s="11" t="n">
         <v>322.2</v>
@@ -2026,7 +2026,7 @@
         <v>340.9</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>322.11</v>
+        <v>322.1</v>
       </c>
       <c r="P65" s="8" t="n"/>
       <c r="Q65" s="8" t="n"/>
@@ -2138,7 +2138,7 @@
         <v>519.16</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>461.78</v>
+        <v>461.79</v>
       </c>
       <c r="P73" s="8" t="n"/>
       <c r="Q73" s="8" t="n"/>
@@ -2147,7 +2147,7 @@
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t>Medicaid-heavy = at least 50% Medicaid days, excluding complex-care Kulana Malama and Islands Skilled (research notes; rule to verify against the extract). All facilities = every Hawaii facility in the file.</t>
+          <t>Medicaid-heavy = Medicaid (Title XIX) days at least 50% of total days, excluding complex-care Kulana Malama (CCN 125057) and Islands Skilled Nursing and Rehab (CCN 125067). All facilities = every Hawaii facility in the file. Medians on unrounded values, half up to the cent.</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t>Values from my decision tree v4; to verify. A national Medicare index standing in for Hawaii nursing-home cost growth.</t>
+          <t>CMS SNF PPS final rule fact sheets, FY2024 to FY2027. A national Medicare index standing in for Hawaii nursing-home cost growth.</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="D41" s="25">
         <f>RATE_GROWTH_2024_2026</f>
-        <v>0.013830433071925885</v>
+        <v>0.013840668562237424</v>
       </c>
       <c r="E41" s="25">
         <f>0.0138</f>
@@ -3536,11 +3536,11 @@
       </c>
       <c r="D42" s="21">
         <f>INDEX(COST_FWD,3)</f>
-        <v>506.06918126599993</v>
+        <v>506.080140363</v>
       </c>
       <c r="E42" s="21">
-        <f>506.07</f>
-        <v>506.07</v>
+        <f>506.08</f>
+        <v>506.08</v>
       </c>
       <c r="F42">
         <f>0.005</f>
@@ -3568,11 +3568,11 @@
       </c>
       <c r="D43" s="21">
         <f>INDEX(COST_FWD,4)</f>
-        <v>522.7694642477779</v>
+        <v>522.780784994979</v>
       </c>
       <c r="E43" s="21">
-        <f>522.77</f>
-        <v>522.77</v>
+        <f>522.78</f>
+        <v>522.78</v>
       </c>
       <c r="F43">
         <f>0.005</f>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="D44" s="25">
         <f>INDEX(COND_A_GAP,1)</f>
-        <v>0.021378858200640227</v>
+        <v>0.021380290392819967</v>
       </c>
       <c r="E44" s="25">
         <f>0.0214</f>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="D45" s="25">
         <f>INDEX(COND_A_GAP,2)</f>
-        <v>0.039539306869518454</v>
+        <v>0.039531015821562265</v>
       </c>
       <c r="E45" s="25">
         <f>0.0395</f>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C4" s="21">
         <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2023,COST_FY,0))</f>
-        <v>461.78</v>
+        <v>461.79</v>
       </c>
     </row>
     <row r="5">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="C5" s="21">
         <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2023,COST_FY,0))*(1+INDEX(MB_GROSS,1))</f>
-        <v>475.6334</v>
+        <v>475.6437</v>
       </c>
     </row>
     <row r="6">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="C6" s="21">
         <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2023,COST_FY,0))*(1+INDEX(MB_GROSS,1))*(1+INDEX(MB_GROSS,2))</f>
-        <v>489.902402</v>
+        <v>489.91301100000004</v>
       </c>
     </row>
     <row r="7">
@@ -6657,15 +6657,15 @@
       </c>
       <c r="C7" s="21">
         <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2023,COST_FY,0))*(1+INDEX(MB_GROSS,1))*(1+INDEX(MB_GROSS,2))*(1+INDEX(MB_GROSS,3))</f>
-        <v>506.06918126599993</v>
+        <v>506.080140363</v>
       </c>
       <c r="D7" s="21">
         <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2026,1,1),RATE_DATE,0))</f>
-        <v>495.25</v>
+        <v>495.26</v>
       </c>
       <c r="E7" s="25">
         <f>1-INDEX(RATE_FWD,1)/INDEX(COST_FWD,3)</f>
-        <v>0.021378858200640227</v>
+        <v>0.021380290392819967</v>
       </c>
     </row>
     <row r="8">
@@ -6680,15 +6680,15 @@
       </c>
       <c r="C8" s="21">
         <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2023,COST_FY,0))*(1+INDEX(MB_GROSS,1))*(1+INDEX(MB_GROSS,2))*(1+INDEX(MB_GROSS,3))*(1+INDEX(MB_GROSS,4))</f>
-        <v>522.7694642477779</v>
+        <v>522.780784994979</v>
       </c>
       <c r="D8" s="21">
         <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2026,1,1),RATE_DATE,0))*(1+RATE_GROWTH_2024_2026)</f>
-        <v>502.0995219788713</v>
+        <v>502.1147295121337</v>
       </c>
       <c r="E8" s="25">
         <f>1-INDEX(RATE_FWD,2)/INDEX(COST_FWD,4)</f>
-        <v>0.039539306869518454</v>
+        <v>0.039531015821562265</v>
       </c>
     </row>
     <row r="10">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B10" s="25">
         <f>(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2026,1,1),RATE_DATE,0))/INDEX(NF_RATE_MEDIAN,MATCH(DATE(2024,1,1),RATE_DATE,0)))^(1/2)-1</f>
-        <v>0.013830433071925885</v>
+        <v>0.013840668562237424</v>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>The market basket is a national Medicare index standing in for Hawaii nursing-home cost growth (values to verify).</t>
+          <t>The market basket is a national Medicare index standing in for Hawaii nursing-home cost growth.</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="B57" s="21">
         <f>IF(ISNA(MATCH(A57,RATE_DATE,0)),"",IF(INDEX(NF_RATE_MEDIAN,MATCH(A57,RATE_DATE,0))="","",INDEX(NF_RATE_MEDIAN,MATCH(A57,RATE_DATE,0))))</f>
-        <v>495.25</v>
+        <v>495.26</v>
       </c>
       <c r="C57" t="str">
         <f>IF(ISNA(MATCH(A57,RATE_DATE,0)),"missing memo",IF(INDEX(NF_RATE_MEDIAN,MATCH(A57,RATE_DATE,0))="","no median",""))</f>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="D64" s="21">
         <f>INDEX(NF_COST_ALL,4)</f>
-        <v>344.18</v>
+        <v>344.19</v>
       </c>
     </row>
     <row r="65">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="C65" s="21">
         <f>INDEX(NF_COST_MCD_HEAVY,5)</f>
-        <v>322.11</v>
+        <v>322.1</v>
       </c>
       <c r="D65" s="21">
         <f>INDEX(NF_COST_ALL,5)</f>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="C73" s="21">
         <f>INDEX(NF_COST_MCD_HEAVY,13)</f>
-        <v>461.78</v>
+        <v>461.79</v>
       </c>
       <c r="D73" s="21">
         <f>INDEX(NF_COST_ALL,13)</f>

--- a/capabilities/economic-research/model.xlsx
+++ b/capabilities/economic-research/model.xlsx
@@ -29,31 +29,33 @@
     <definedName name="DATE_ADJ_2021">'Inputs'!$B$13</definedName>
     <definedName name="DATE_RESET_2024">'Inputs'!$B$14</definedName>
     <definedName name="T1_MIN_DROP_PTS">'Inputs'!$B$15</definedName>
-    <definedName name="COVID_YEARS">'Inputs'!$B$16:$B$17</definedName>
-    <definedName name="YEAR">'Inputs'!$A$22:$A$29</definedName>
-    <definedName name="WL_PATIENTS">'Inputs'!$B$22:$B$29</definedName>
-    <definedName name="WL_DAYS">'Inputs'!$C$22:$C$29</definedName>
-    <definedName name="REASON_NO_BED">'Inputs'!$D$22:$D$29</definedName>
-    <definedName name="REASON_BEHAVIOR">'Inputs'!$E$22:$E$29</definedName>
-    <definedName name="REASON_SPECIAL_CARE">'Inputs'!$F$22:$F$29</definedName>
-    <definedName name="REASON_FINANCIAL">'Inputs'!$G$22:$G$29</definedName>
-    <definedName name="REASON_GUARDIANSHIP">'Inputs'!$H$22:$H$29</definedName>
-    <definedName name="REASON_PASARR">'Inputs'!$I$22:$I$29</definedName>
-    <definedName name="REASON_OTHER">'Inputs'!$J$22:$J$29</definedName>
-    <definedName name="DEC31_TOTAL">'Inputs'!$K$22:$K$29</definedName>
-    <definedName name="DEC31_NF">'Inputs'!$L$22:$L$29</definedName>
-    <definedName name="LTC_UNSTAFFED">'Inputs'!$M$22:$M$29</definedName>
-    <definedName name="WL_RATE_JAN">'Inputs'!$N$22:$N$29</definedName>
-    <definedName name="WL_RATE_JUL">'Inputs'!$O$22:$O$29</definedName>
-    <definedName name="COUNTY">'Inputs'!$A$34:$A$37</definedName>
-    <definedName name="CTY_PATIENTS">'Inputs'!$B$34:$C$37</definedName>
-    <definedName name="CTY_DAYS">'Inputs'!$D$34:$E$37</definedName>
-    <definedName name="RATE_DATE">'Inputs'!$A$41:$A$57</definedName>
-    <definedName name="NF_RATE_MEDIAN">'Inputs'!$C$41:$C$57</definedName>
-    <definedName name="COST_FY">'Inputs'!$A$61:$A$73</definedName>
-    <definedName name="NF_COST_ALL">'Inputs'!$B$61:$B$73</definedName>
-    <definedName name="NF_COST_MCD_HEAVY">'Inputs'!$C$61:$C$73</definedName>
-    <definedName name="MB_GROSS">'Inputs'!$B$78:$B$81</definedName>
+    <definedName name="ADMIT_WINDOW_DAYS">'Inputs'!$B$16</definedName>
+    <definedName name="MEDIAN_MCD_LOS">'Inputs'!$B$17</definedName>
+    <definedName name="COVID_YEARS">'Inputs'!$B$18:$B$19</definedName>
+    <definedName name="YEAR">'Inputs'!$A$24:$A$31</definedName>
+    <definedName name="WL_PATIENTS">'Inputs'!$B$24:$B$31</definedName>
+    <definedName name="WL_DAYS">'Inputs'!$C$24:$C$31</definedName>
+    <definedName name="REASON_NO_BED">'Inputs'!$D$24:$D$31</definedName>
+    <definedName name="REASON_BEHAVIOR">'Inputs'!$E$24:$E$31</definedName>
+    <definedName name="REASON_SPECIAL_CARE">'Inputs'!$F$24:$F$31</definedName>
+    <definedName name="REASON_FINANCIAL">'Inputs'!$G$24:$G$31</definedName>
+    <definedName name="REASON_GUARDIANSHIP">'Inputs'!$H$24:$H$31</definedName>
+    <definedName name="REASON_PASARR">'Inputs'!$I$24:$I$31</definedName>
+    <definedName name="REASON_OTHER">'Inputs'!$J$24:$J$31</definedName>
+    <definedName name="DEC31_TOTAL">'Inputs'!$K$24:$K$31</definedName>
+    <definedName name="DEC31_NF">'Inputs'!$L$24:$L$31</definedName>
+    <definedName name="LTC_UNSTAFFED">'Inputs'!$M$24:$M$31</definedName>
+    <definedName name="WL_RATE_JAN">'Inputs'!$N$24:$N$31</definedName>
+    <definedName name="WL_RATE_JUL">'Inputs'!$O$24:$O$31</definedName>
+    <definedName name="COUNTY">'Inputs'!$A$36:$A$39</definedName>
+    <definedName name="CTY_PATIENTS">'Inputs'!$B$36:$C$39</definedName>
+    <definedName name="CTY_DAYS">'Inputs'!$D$36:$E$39</definedName>
+    <definedName name="RATE_DATE">'Inputs'!$A$43:$A$59</definedName>
+    <definedName name="NF_RATE_MEDIAN">'Inputs'!$C$43:$C$59</definedName>
+    <definedName name="COST_FY">'Inputs'!$A$63:$A$75</definedName>
+    <definedName name="NF_COST_ALL">'Inputs'!$B$63:$B$75</definedName>
+    <definedName name="NF_COST_MCD_HEAVY">'Inputs'!$C$63:$C$75</definedName>
+    <definedName name="MB_GROSS">'Inputs'!$B$80:$B$83</definedName>
     <definedName name="DAYS_PER_PT">'Waitlist'!$B$4:$B$11</definedName>
     <definedName name="BENCH_TOTAL">'Waitlist'!$C$4:$C$11</definedName>
     <definedName name="GAP_PER_PT">'Waitlist'!$D$4:$D$11</definedName>
@@ -83,9 +85,10 @@
     <definedName name="EXCESS_COST_HI">'Cost'!$C$11:$D$11</definedName>
     <definedName name="EXCESS_COST_HI_NOW">'Cost'!$E$11</definedName>
     <definedName name="NF_SHARE_DEC31">'Cost'!$C$12:$D$12</definedName>
-    <definedName name="CEIL_PER_PT_LO">'Cost'!$E$13</definedName>
-    <definedName name="CEIL_PER_PT_HI">'Cost'!$E$14</definedName>
-    <definedName name="WL_DAYS_CHANGE_2024">'Cost'!$C$16</definedName>
+    <definedName name="DAYS_SAVED_PER_PT">'Cost'!$E$13</definedName>
+    <definedName name="CEIL_PER_PT_LO">'Cost'!$E$14</definedName>
+    <definedName name="CEIL_PER_PT_HI">'Cost'!$E$15</definedName>
+    <definedName name="WL_DAYS_CHANGE_2024">'Cost'!$C$17</definedName>
     <definedName name="T1_DROP_2021">'Tests'!$B$6</definedName>
     <definedName name="T1_PASS_2021">'Tests'!$B$7</definedName>
     <definedName name="T1_DROP_2024">'Tests'!$B$10</definedName>
@@ -108,6 +111,7 @@
     <definedName name="RATE_FWD">'Conditions'!$D$7:$D$8</definedName>
     <definedName name="COND_A_GAP">'Conditions'!$E$7:$E$8</definedName>
     <definedName name="RATE_GROWTH_2024_2026">'Conditions'!$B$10</definedName>
+    <definedName name="STAY_SHORTFALL">'Conditions'!$B$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -200,6 +204,7 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,12 +220,11 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -595,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R82"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="7" min="1" max="1"/>
@@ -632,12 +636,12 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>COUNT(R6:R17,R22:R29,R34:R37,R41:R57,R61:R73,R78:R81)</f>
+        <f>COUNT(R6:R19,R24:R31,R36:R39,R43:R59,R63:R75,R80:R83)</f>
         <v>57</v>
       </c>
       <c r="C2" t="str">
-        <f>"of "&amp;(ROWS(R6:R17)+ROWS(R22:R29)+ROWS(R34:R37)+ROWS(R41:R57)+ROWS(R61:R73)+ROWS(R78:R81))</f>
-        <v>of 58</v>
+        <f>"of "&amp;(ROWS(R6:R19)+ROWS(R24:R31)+ROWS(R36:R39)+ROWS(R43:R59)+ROWS(R63:R75)+ROWS(R80:R83))</f>
+        <v>of 60</v>
       </c>
     </row>
     <row r="3"/>
@@ -1018,378 +1022,322 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>COVID_YEARS</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>2020</v>
+          <t>ADMIT_WINDOW_DAYS</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Brief</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>Brief line 79</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R16" s="31" t="n">
-        <v>46294</v>
-      </c>
+          <t>My judgment (2026-10-01): the time within which a home giving the guarantee must admit. Set equal to the benchmark</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="34" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>MEDIAN_MCD_LOS</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>542.83</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CMS SNF cost reports, FY2023 file, "SNF Average Length of Stay Title XIX", each Hawaii home's latest report: median of the 31 homes reporting a value (range 8.26 to 1,680.75). Rounded to 543 in the paper</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="34" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>COVID_YEARS</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Brief</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>Brief line 79</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R18" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>(COVID_YEARS, 2nd)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>2021</v>
       </c>
-      <c r="P17" s="8" t="inlineStr">
+      <c r="P19" s="8" t="inlineStr">
         <is>
           <t>Brief line 79</t>
         </is>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="Q19" s="8" t="inlineStr">
         <is>
           <t>MK</t>
         </is>
       </c>
-      <c r="R17" s="31" t="n">
+      <c r="R19" s="31" t="n">
         <v>46294</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Year table (SHPDA Table 18 statewide; Table 16 statewide; Med-QUEST waitlisted rates)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1" s="7">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="22" ht="32" customHeight="1" s="7">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>WL_PATIENTS</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>WL_DAYS</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>REASON_NO_BED</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>REASON_BEHAVIOR</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>REASON_SPECIAL_CARE</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>REASON_FINANCIAL</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>REASON_GUARDIANSHIP</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>REASON_PASARR</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>REASON_OTHER</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>DEC31_TOTAL</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>DEC31_NF</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>LTC_UNSTAFFED</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>WL_RATE_JAN</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>WL_RATE_JUL</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="inlineStr">
+      <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R20" s="5" t="inlineStr">
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" s="7">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23" ht="30" customHeight="1" s="7">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>T18 total</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>T18 total</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>T18 reason F</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>T18 reason G</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>T18 reason H</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>T18 reason I</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>T18 reason J</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>T18 reason K</t>
         </is>
       </c>
-      <c r="J21" s="13" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>T18 reason L</t>
         </is>
       </c>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>T18 by level of care</t>
         </is>
       </c>
-      <c r="L21" s="13" t="inlineStr">
+      <c r="L23" s="14" t="inlineStr">
         <is>
           <t>T18 type A</t>
         </is>
       </c>
-      <c r="M21" s="13" t="inlineStr">
+      <c r="M23" s="14" t="inlineStr">
         <is>
           <t>T16 statewide</t>
         </is>
       </c>
-      <c r="N21" s="13" t="inlineStr">
+      <c r="N23" s="14" t="inlineStr">
         <is>
           <t>QI-2225, QI-2342</t>
         </is>
       </c>
-      <c r="O21" s="13" t="inlineStr">
+      <c r="O23" s="14" t="inlineStr">
         <is>
           <t>QI-2326, QI-2413</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="n">
+    <row r="24">
+      <c r="A24" s="15" t="n">
         <v>2017</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B24" s="6" t="n">
         <v>6187</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C24" s="6" t="n">
         <v>61470</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D24" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E24" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F24" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G24" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H24" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>157</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M24" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="P24" s="8" t="inlineStr">
         <is>
           <t>T18 2017 p. 72; T16 2017 p. 69</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R22" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>5294</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>66091</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>171</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>160</v>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>T18 2018 p. 82; T16 p. 79</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R23" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>4790</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>78911</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>184</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>248</v>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>T18 2019 p. 82; T16 p. 79</t>
         </is>
       </c>
       <c r="Q24" s="8" t="inlineStr">
@@ -1402,45 +1350,45 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
-        <v>2020</v>
+      <c r="A25" s="15" t="n">
+        <v>2018</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>4553</v>
+        <v>5294</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>57297</v>
+        <v>66091</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>462</v>
+        <v>160</v>
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>T18 2020 p. 85; T16 p. 81</t>
+          <t>T18 2018 p. 82; T16 p. 79</t>
         </is>
       </c>
       <c r="Q25" s="8" t="inlineStr">
@@ -1453,45 +1401,45 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="n">
-        <v>2021</v>
+      <c r="A26" s="15" t="n">
+        <v>2019</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>4927</v>
+        <v>4790</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>60050</v>
+        <v>78911</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>614</v>
+        <v>248</v>
       </c>
       <c r="P26" s="8" t="inlineStr">
         <is>
-          <t>T18 2021 p. 87; T16 p. 83</t>
+          <t>T18 2019 p. 82; T16 p. 79</t>
         </is>
       </c>
       <c r="Q26" s="8" t="inlineStr">
@@ -1504,45 +1452,45 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="n">
-        <v>2022</v>
+      <c r="A27" s="15" t="n">
+        <v>2020</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>3681</v>
+        <v>4553</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>78561</v>
+        <v>57297</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>661</v>
+        <v>462</v>
       </c>
       <c r="P27" s="8" t="inlineStr">
         <is>
-          <t>T18 2022 p. 86; T16 p. 82</t>
+          <t>T18 2020 p. 85; T16 p. 81</t>
         </is>
       </c>
       <c r="Q27" s="8" t="inlineStr">
@@ -1555,54 +1503,45 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="n">
-        <v>2023</v>
+      <c r="A28" s="15" t="n">
+        <v>2021</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3610</v>
+        <v>4927</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>83097</v>
+        <v>60050</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>191</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="N28" s="33" t="n">
-        <v>283.6</v>
-      </c>
-      <c r="O28" s="33" t="n">
-        <v>302.89</v>
+        <v>614</v>
       </c>
       <c r="P28" s="8" t="inlineStr">
         <is>
-          <t>T18 2023 p. 86; T16 p. 82; QI-2225 p. 2; QI-2326 p. 2</t>
+          <t>T18 2021 p. 87; T16 p. 83</t>
         </is>
       </c>
       <c r="Q28" s="8" t="inlineStr">
@@ -1615,54 +1554,45 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="n">
-        <v>2024</v>
+      <c r="A29" s="15" t="n">
+        <v>2022</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3123</v>
+        <v>3681</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>60876</v>
+        <v>78561</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E29" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="H29" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="F29" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>31</v>
-      </c>
       <c r="I29" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>173</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>548</v>
-      </c>
-      <c r="N29" s="33" t="n">
-        <v>464.97</v>
-      </c>
-      <c r="O29" s="33" t="n">
-        <v>455.59</v>
+        <v>661</v>
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>T18 2024 p. 86; T16 p. 82; QI-2342 p. 2; QI-2413 p. 2</t>
+          <t>T18 2022 p. 86; T16 p. 82</t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
@@ -1675,143 +1605,199 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3610</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>83097</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="N30" s="33" t="n">
+        <v>283.6</v>
+      </c>
+      <c r="O30" s="33" t="n">
+        <v>302.89</v>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>T18 2023 p. 86; T16 p. 82; QI-2225 p. 2; QI-2326 p. 2</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R30" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>3123</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>60876</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>548</v>
+      </c>
+      <c r="N31" s="33" t="n">
+        <v>464.97</v>
+      </c>
+      <c r="O31" s="33" t="n">
+        <v>455.59</v>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>T18 2024 p. 86; T16 p. 82; QI-2342 p. 2; QI-2413 p. 2</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R31" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Reason columns F to L; 2017 reasons sum to 120 against 157 by level of care (Maui Memorial records reasons for 6 of 47 patients; Queen's Punchbowl's reasons sum to 43 against 39). DEC31_NF and the waitlisted rates exist for 2023 and 2024 only (blank, not inputs, in other years).</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>County table (Table 18 hospital rows summed by county, shpda-table18-by-hospital-2023-2024.csv)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1" s="7">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="35" ht="32" customHeight="1" s="7">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>COUNTY</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>CTY_PATIENTS 2023</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>CTY_PATIENTS 2024</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>CTY_DAYS 2023</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>CTY_DAYS 2024</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="P35" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="inlineStr">
+      <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R33" s="5" t="inlineStr">
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>869</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>727</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>23212</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>20174</v>
-      </c>
-      <c r="P34" s="8" t="inlineStr">
-        <is>
-          <t>T18 2023 and 2024, pp. 85-86 (hospital rows summed; county totals)</t>
-        </is>
-      </c>
-      <c r="Q34" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R34" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Honolulu</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n">
-        <v>2255</v>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>1979</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>40327</v>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>27380</v>
-      </c>
-      <c r="P35" s="8" t="inlineStr">
-        <is>
-          <t>T18 2023 and 2024, pp. 85-86 (hospital rows summed; county totals)</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R35" s="31" t="n">
-        <v>46294</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Kauai</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>86</v>
+        <v>869</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>64</v>
+        <v>727</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1720</v>
+        <v>23212</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1927</v>
+        <v>20174</v>
       </c>
       <c r="P36" s="8" t="inlineStr">
         <is>
@@ -1830,20 +1816,20 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Maui</t>
+          <t>Honolulu</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>400</v>
+        <v>2255</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>353</v>
+        <v>1979</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>17838</v>
+        <v>40327</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>11395</v>
+        <v>27380</v>
       </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
@@ -1859,113 +1845,125 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="38"/>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>1720</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>1927</v>
+      </c>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>T18 2023 and 2024, pp. 85-86 (hospital rows summed; county totals)</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R38" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>353</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>17838</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>11395</v>
+      </c>
+      <c r="P39" s="8" t="inlineStr">
+        <is>
+          <t>T18 2023 and 2024, pp. 85-86 (hospital rows summed; county totals)</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R39" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Median nursing-facility rate by memo (Med-QUEST memos, hi-medicaid-rate-series-2016-2026.csv)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1" s="7">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="42" ht="32" customHeight="1" s="7">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>RATE_DATE (effective month)</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Memo</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>NF_RATE_MEDIAN</t>
         </is>
       </c>
-      <c r="P40" s="5" t="inlineStr">
+      <c r="P42" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q40" s="5" t="inlineStr">
+      <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R40" s="5" t="inlineStr">
+      <c r="R42" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="16" t="n">
+    <row r="43">
+      <c r="A43" s="17" t="n">
         <v>42370</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>QI-1521</t>
         </is>
       </c>
-      <c r="C41" s="33" t="n">
+      <c r="C43" s="33" t="n">
         <v>246.97</v>
       </c>
-      <c r="P41" s="8" t="inlineStr">
+      <c r="P43" s="8" t="inlineStr">
         <is>
           <t>QI-1521 p. 2</t>
-        </is>
-      </c>
-      <c r="Q41" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R41" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="n">
-        <v>42552</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>QI-1607</t>
-        </is>
-      </c>
-      <c r="C42" s="33" t="n">
-        <v>252.4</v>
-      </c>
-      <c r="P42" s="8" t="inlineStr">
-        <is>
-          <t>QI-1607 p. 5</t>
-        </is>
-      </c>
-      <c r="Q42" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R42" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="n">
-        <v>42736</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>QI-1622</t>
-        </is>
-      </c>
-      <c r="C43" s="33" t="n">
-        <v>251.93</v>
-      </c>
-      <c r="P43" s="8" t="inlineStr">
-        <is>
-          <t>QI-1622 p. 2</t>
         </is>
       </c>
       <c r="Q43" s="8" t="inlineStr">
@@ -1978,20 +1976,20 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n">
-        <v>42917</v>
+      <c r="A44" s="17" t="n">
+        <v>42552</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>QI-1710</t>
+          <t>QI-1607</t>
         </is>
       </c>
       <c r="C44" s="33" t="n">
-        <v>261.45</v>
+        <v>252.4</v>
       </c>
       <c r="P44" s="8" t="inlineStr">
         <is>
-          <t>QI-1710 p. 8</t>
+          <t>QI-1607 p. 5</t>
         </is>
       </c>
       <c r="Q44" s="8" t="inlineStr">
@@ -2004,20 +2002,20 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n">
-        <v>43282</v>
+      <c r="A45" s="17" t="n">
+        <v>42736</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>QI-1809</t>
+          <t>QI-1622</t>
         </is>
       </c>
       <c r="C45" s="33" t="n">
-        <v>270.66</v>
+        <v>251.93</v>
       </c>
       <c r="P45" s="8" t="inlineStr">
         <is>
-          <t>QI-1809 p. 9</t>
+          <t>QI-1622 p. 2</t>
         </is>
       </c>
       <c r="Q45" s="8" t="inlineStr">
@@ -2030,20 +2028,20 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n">
-        <v>43466</v>
+      <c r="A46" s="17" t="n">
+        <v>42917</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>QI-1820</t>
+          <t>QI-1710</t>
         </is>
       </c>
       <c r="C46" s="33" t="n">
-        <v>270.15</v>
+        <v>261.45</v>
       </c>
       <c r="P46" s="8" t="inlineStr">
         <is>
-          <t>QI-1820 p. 5</t>
+          <t>QI-1710 p. 8</t>
         </is>
       </c>
       <c r="Q46" s="8" t="inlineStr">
@@ -2056,23 +2054,20 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n">
-        <v>43647</v>
+      <c r="A47" s="17" t="n">
+        <v>43282</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>QI-1911B</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>Left blank: QI-1911B, the controlling July 2019 memo, lists but omits its acuity rate table</t>
-        </is>
+          <t>QI-1809</t>
+        </is>
+      </c>
+      <c r="C47" s="33" t="n">
+        <v>270.66</v>
       </c>
       <c r="P47" s="8" t="inlineStr">
         <is>
-          <t>Blank by decision: QI-1911B omits Att. H</t>
+          <t>QI-1809 p. 9</t>
         </is>
       </c>
       <c r="Q47" s="8" t="inlineStr">
@@ -2080,23 +2075,25 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="R47" s="34" t="n"/>
+      <c r="R47" s="31" t="n">
+        <v>46294</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n">
-        <v>44013</v>
+      <c r="A48" s="17" t="n">
+        <v>43466</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>QI-2022</t>
+          <t>QI-1820</t>
         </is>
       </c>
       <c r="C48" s="33" t="n">
-        <v>282.98</v>
+        <v>270.15</v>
       </c>
       <c r="P48" s="8" t="inlineStr">
         <is>
-          <t>QI-2022 p. 11</t>
+          <t>QI-1820 p. 5</t>
         </is>
       </c>
       <c r="Q48" s="8" t="inlineStr">
@@ -2109,20 +2106,23 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n">
-        <v>44378</v>
+      <c r="A49" s="17" t="n">
+        <v>43647</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>QI-2113B</t>
-        </is>
-      </c>
-      <c r="C49" s="33" t="n">
-        <v>334.75</v>
+          <t>QI-1911B</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Left blank: QI-1911B, the controlling July 2019 memo, lists but omits its acuity rate table</t>
+        </is>
       </c>
       <c r="P49" s="8" t="inlineStr">
         <is>
-          <t>QI-2113B p. 11</t>
+          <t>Blank by decision: QI-1911B omits Att. H</t>
         </is>
       </c>
       <c r="Q49" s="8" t="inlineStr">
@@ -2130,25 +2130,23 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="R49" s="31" t="n">
-        <v>46294</v>
-      </c>
+      <c r="R49" s="34" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n">
-        <v>44562</v>
+      <c r="A50" s="17" t="n">
+        <v>44013</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>QI-2166</t>
+          <t>QI-2022</t>
         </is>
       </c>
       <c r="C50" s="33" t="n">
-        <v>332.59</v>
+        <v>282.98</v>
       </c>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>QI-2166 p. 7</t>
+          <t>QI-2022 p. 11</t>
         </is>
       </c>
       <c r="Q50" s="8" t="inlineStr">
@@ -2161,20 +2159,20 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n">
-        <v>44927</v>
+      <c r="A51" s="17" t="n">
+        <v>44378</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>QI-2225</t>
+          <t>QI-2113B</t>
         </is>
       </c>
       <c r="C51" s="33" t="n">
-        <v>355.11</v>
+        <v>334.75</v>
       </c>
       <c r="P51" s="8" t="inlineStr">
         <is>
-          <t>QI-2225 p. 3</t>
+          <t>QI-2113B p. 11</t>
         </is>
       </c>
       <c r="Q51" s="8" t="inlineStr">
@@ -2187,20 +2185,20 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n">
-        <v>45108</v>
+      <c r="A52" s="17" t="n">
+        <v>44562</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>QI-2326</t>
+          <t>QI-2166</t>
         </is>
       </c>
       <c r="C52" s="33" t="n">
-        <v>371.99</v>
+        <v>332.59</v>
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>QI-2326 p. 3</t>
+          <t>QI-2166 p. 7</t>
         </is>
       </c>
       <c r="Q52" s="8" t="inlineStr">
@@ -2213,20 +2211,20 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n">
-        <v>45292</v>
+      <c r="A53" s="17" t="n">
+        <v>44927</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>QI-2342</t>
+          <t>QI-2225</t>
         </is>
       </c>
       <c r="C53" s="33" t="n">
-        <v>481.83</v>
+        <v>355.11</v>
       </c>
       <c r="P53" s="8" t="inlineStr">
         <is>
-          <t>QI-2342 p. 3</t>
+          <t>QI-2225 p. 3</t>
         </is>
       </c>
       <c r="Q53" s="8" t="inlineStr">
@@ -2239,20 +2237,20 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n">
-        <v>45474</v>
+      <c r="A54" s="17" t="n">
+        <v>45108</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>QI-2413</t>
+          <t>QI-2326</t>
         </is>
       </c>
       <c r="C54" s="33" t="n">
-        <v>482.2</v>
+        <v>371.99</v>
       </c>
       <c r="P54" s="8" t="inlineStr">
         <is>
-          <t>QI-2413 p. 3</t>
+          <t>QI-2326 p. 3</t>
         </is>
       </c>
       <c r="Q54" s="8" t="inlineStr">
@@ -2265,20 +2263,20 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n">
-        <v>45658</v>
+      <c r="A55" s="17" t="n">
+        <v>45292</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>QI-2427</t>
+          <t>QI-2342</t>
         </is>
       </c>
       <c r="C55" s="33" t="n">
-        <v>509.69</v>
+        <v>481.83</v>
       </c>
       <c r="P55" s="8" t="inlineStr">
         <is>
-          <t>QI-2427 p. 3</t>
+          <t>QI-2342 p. 3</t>
         </is>
       </c>
       <c r="Q55" s="8" t="inlineStr">
@@ -2291,20 +2289,20 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n">
-        <v>45839</v>
+      <c r="A56" s="17" t="n">
+        <v>45474</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>QI-2515</t>
+          <t>QI-2413</t>
         </is>
       </c>
       <c r="C56" s="33" t="n">
-        <v>506.65</v>
+        <v>482.2</v>
       </c>
       <c r="P56" s="8" t="inlineStr">
         <is>
-          <t>QI-2515 p. 3</t>
+          <t>QI-2413 p. 3</t>
         </is>
       </c>
       <c r="Q56" s="8" t="inlineStr">
@@ -2317,20 +2315,20 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n">
-        <v>46023</v>
+      <c r="A57" s="17" t="n">
+        <v>45658</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>QI-2532</t>
+          <t>QI-2427</t>
         </is>
       </c>
       <c r="C57" s="33" t="n">
-        <v>495.26</v>
+        <v>509.69</v>
       </c>
       <c r="P57" s="8" t="inlineStr">
         <is>
-          <t>QI-2532 p. 3 (median 495.255, rounded half up)</t>
+          <t>QI-2427 p. 3</t>
         </is>
       </c>
       <c r="Q57" s="8" t="inlineStr">
@@ -2342,103 +2340,107 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="58"/>
+    <row r="58">
+      <c r="A58" s="17" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>QI-2515</t>
+        </is>
+      </c>
+      <c r="C58" s="33" t="n">
+        <v>506.65</v>
+      </c>
+      <c r="P58" s="8" t="inlineStr">
+        <is>
+          <t>QI-2515 p. 3</t>
+        </is>
+      </c>
+      <c r="Q58" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R58" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="17" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>QI-2532</t>
+        </is>
+      </c>
+      <c r="C59" s="33" t="n">
+        <v>495.26</v>
+      </c>
+      <c r="P59" s="8" t="inlineStr">
+        <is>
+          <t>QI-2532 p. 3 (median 495.255, rounded half up)</t>
+        </is>
+      </c>
+      <c r="Q59" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R59" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Median nursing-home cost per patient day (CMS SNF cost reports, hi-snf-cost-per-day-series-2011-2023.csv)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="32" customHeight="1" s="7">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="62" ht="32" customHeight="1" s="7">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>COST_FY</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>NF_COST_ALL</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>NF_COST_MCD_HEAVY</t>
         </is>
       </c>
-      <c r="P60" s="5" t="inlineStr">
+      <c r="P62" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q60" s="5" t="inlineStr">
+      <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R60" s="5" t="inlineStr">
+      <c r="R62" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="14" t="n">
+    <row r="63">
+      <c r="A63" s="15" t="n">
         <v>2011</v>
       </c>
-      <c r="B61" s="33" t="n">
+      <c r="B63" s="33" t="n">
         <v>295.13</v>
       </c>
-      <c r="C61" s="33" t="n">
+      <c r="C63" s="33" t="n">
         <v>287.76</v>
-      </c>
-      <c r="P61" s="8" t="inlineStr">
-        <is>
-          <t>CMS SNF cost report FY20xx (data.cms.gov), Worksheet A; median re-derived</t>
-        </is>
-      </c>
-      <c r="Q61" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R61" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B62" s="33" t="n">
-        <v>314.68</v>
-      </c>
-      <c r="C62" s="33" t="n">
-        <v>311.89</v>
-      </c>
-      <c r="P62" s="8" t="inlineStr">
-        <is>
-          <t>CMS SNF cost report FY20xx (data.cms.gov), Worksheet A; median re-derived</t>
-        </is>
-      </c>
-      <c r="Q62" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R62" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="14" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B63" s="33" t="n">
-        <v>342.42</v>
-      </c>
-      <c r="C63" s="33" t="n">
-        <v>322.2</v>
       </c>
       <c r="P63" s="8" t="inlineStr">
         <is>
@@ -2455,14 +2457,14 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14" t="n">
-        <v>2014</v>
+      <c r="A64" s="15" t="n">
+        <v>2012</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>344.19</v>
+        <v>314.68</v>
       </c>
       <c r="C64" s="33" t="n">
-        <v>322.2</v>
+        <v>311.89</v>
       </c>
       <c r="P64" s="8" t="inlineStr">
         <is>
@@ -2479,14 +2481,14 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="n">
-        <v>2015</v>
+      <c r="A65" s="15" t="n">
+        <v>2013</v>
       </c>
       <c r="B65" s="33" t="n">
-        <v>340.9</v>
+        <v>342.42</v>
       </c>
       <c r="C65" s="33" t="n">
-        <v>322.1</v>
+        <v>322.2</v>
       </c>
       <c r="P65" s="8" t="inlineStr">
         <is>
@@ -2503,14 +2505,14 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="n">
-        <v>2016</v>
+      <c r="A66" s="15" t="n">
+        <v>2014</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>358.8</v>
+        <v>344.19</v>
       </c>
       <c r="C66" s="33" t="n">
-        <v>344.38</v>
+        <v>322.2</v>
       </c>
       <c r="P66" s="8" t="inlineStr">
         <is>
@@ -2527,14 +2529,14 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="n">
-        <v>2017</v>
+      <c r="A67" s="15" t="n">
+        <v>2015</v>
       </c>
       <c r="B67" s="33" t="n">
-        <v>376.01</v>
+        <v>340.9</v>
       </c>
       <c r="C67" s="33" t="n">
-        <v>356.1</v>
+        <v>322.1</v>
       </c>
       <c r="P67" s="8" t="inlineStr">
         <is>
@@ -2551,14 +2553,14 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="14" t="n">
-        <v>2018</v>
+      <c r="A68" s="15" t="n">
+        <v>2016</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>380.99</v>
+        <v>358.8</v>
       </c>
       <c r="C68" s="33" t="n">
-        <v>365.93</v>
+        <v>344.38</v>
       </c>
       <c r="P68" s="8" t="inlineStr">
         <is>
@@ -2575,14 +2577,14 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="14" t="n">
-        <v>2019</v>
+      <c r="A69" s="15" t="n">
+        <v>2017</v>
       </c>
       <c r="B69" s="33" t="n">
-        <v>379.87</v>
+        <v>376.01</v>
       </c>
       <c r="C69" s="33" t="n">
-        <v>373.25</v>
+        <v>356.1</v>
       </c>
       <c r="P69" s="8" t="inlineStr">
         <is>
@@ -2599,14 +2601,14 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="14" t="n">
-        <v>2020</v>
+      <c r="A70" s="15" t="n">
+        <v>2018</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>428.4</v>
+        <v>380.99</v>
       </c>
       <c r="C70" s="33" t="n">
-        <v>398.33</v>
+        <v>365.93</v>
       </c>
       <c r="P70" s="8" t="inlineStr">
         <is>
@@ -2623,14 +2625,14 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="14" t="n">
-        <v>2021</v>
+      <c r="A71" s="15" t="n">
+        <v>2019</v>
       </c>
       <c r="B71" s="33" t="n">
-        <v>450.4</v>
+        <v>379.87</v>
       </c>
       <c r="C71" s="33" t="n">
-        <v>423.44</v>
+        <v>373.25</v>
       </c>
       <c r="P71" s="8" t="inlineStr">
         <is>
@@ -2647,14 +2649,14 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="14" t="n">
-        <v>2022</v>
+      <c r="A72" s="15" t="n">
+        <v>2020</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>459.47</v>
+        <v>428.4</v>
       </c>
       <c r="C72" s="33" t="n">
-        <v>435.63</v>
+        <v>398.33</v>
       </c>
       <c r="P72" s="8" t="inlineStr">
         <is>
@@ -2671,14 +2673,14 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="14" t="n">
-        <v>2023</v>
+      <c r="A73" s="15" t="n">
+        <v>2021</v>
       </c>
       <c r="B73" s="33" t="n">
-        <v>519.16</v>
+        <v>450.4</v>
       </c>
       <c r="C73" s="33" t="n">
-        <v>461.79</v>
+        <v>423.44</v>
       </c>
       <c r="P73" s="8" t="inlineStr">
         <is>
@@ -2695,119 +2697,115 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="15" t="inlineStr">
+      <c r="A74" s="15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B74" s="33" t="n">
+        <v>459.47</v>
+      </c>
+      <c r="C74" s="33" t="n">
+        <v>435.63</v>
+      </c>
+      <c r="P74" s="8" t="inlineStr">
+        <is>
+          <t>CMS SNF cost report FY20xx (data.cms.gov), Worksheet A; median re-derived</t>
+        </is>
+      </c>
+      <c r="Q74" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R74" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B75" s="33" t="n">
+        <v>519.16</v>
+      </c>
+      <c r="C75" s="33" t="n">
+        <v>461.79</v>
+      </c>
+      <c r="P75" s="8" t="inlineStr">
+        <is>
+          <t>CMS SNF cost report FY20xx (data.cms.gov), Worksheet A; median re-derived</t>
+        </is>
+      </c>
+      <c r="Q75" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R75" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>Medicaid-heavy = Medicaid (Title XIX) days at least 50% of total days, excluding complex-care Kulana Malama (CCN 125057) and Islands Skilled Nursing and Rehab (CCN 125067). All facilities = every Hawaii facility in the file. Medians on unrounded values, half up to the cent.</t>
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Market basket for condition (a) (CMS SNF PPS final rules, FY2024 to FY2027)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Fiscal year</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>MB_GROSS</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="P77" s="5" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q77" s="5" t="inlineStr">
+      <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R77" s="5" t="inlineStr">
+      <c r="R79" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="14" t="n">
+    <row r="80">
+      <c r="A80" s="15" t="n">
         <v>2024</v>
       </c>
-      <c r="B78" s="17" t="n">
+      <c r="B80" s="18" t="n">
         <v>0.03</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>CMS SNF PPS final rule FY2024: market basket before the forecast-error and productivity adjustments</t>
         </is>
       </c>
-      <c r="P78" s="8" t="inlineStr">
+      <c r="P80" s="8" t="inlineStr">
         <is>
           <t>CMS-1779-F fact sheet (FY2024)</t>
-        </is>
-      </c>
-      <c r="Q78" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R78" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B79" s="17" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>CMS SNF PPS final rule FY2025: market basket before the forecast-error and productivity adjustments</t>
-        </is>
-      </c>
-      <c r="P79" s="8" t="inlineStr">
-        <is>
-          <t>CMS-1802-F fact sheet (FY2025)</t>
-        </is>
-      </c>
-      <c r="Q79" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R79" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B80" s="17" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>CMS SNF PPS final rule FY2026: market basket before the forecast-error and productivity adjustments</t>
-        </is>
-      </c>
-      <c r="P80" s="8" t="inlineStr">
-        <is>
-          <t>CMS-1827-F fact sheet (FY2026)</t>
         </is>
       </c>
       <c r="Q80" s="8" t="inlineStr">
@@ -2820,20 +2818,20 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="14" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B81" s="17" t="n">
-        <v>0.033</v>
+      <c r="A81" s="15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B81" s="18" t="n">
+        <v>0.03</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CMS SNF PPS final rule FY2027: market basket before the forecast-error and productivity adjustments</t>
+          <t>CMS SNF PPS final rule FY2025: market basket before the forecast-error and productivity adjustments</t>
         </is>
       </c>
       <c r="P81" s="8" t="inlineStr">
         <is>
-          <t>CMS-1843-F fact sheet (FY2027)</t>
+          <t>CMS-1802-F fact sheet (FY2025)</t>
         </is>
       </c>
       <c r="Q81" s="8" t="inlineStr">
@@ -2846,7 +2844,59 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="15" t="inlineStr">
+      <c r="A82" s="15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B82" s="18" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CMS SNF PPS final rule FY2026: market basket before the forecast-error and productivity adjustments</t>
+        </is>
+      </c>
+      <c r="P82" s="8" t="inlineStr">
+        <is>
+          <t>CMS-1827-F fact sheet (FY2026)</t>
+        </is>
+      </c>
+      <c r="Q82" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R82" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B83" s="18" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CMS SNF PPS final rule FY2027: market basket before the forecast-error and productivity adjustments</t>
+        </is>
+      </c>
+      <c r="P83" s="8" t="inlineStr">
+        <is>
+          <t>CMS-1843-F fact sheet (FY2027)</t>
+        </is>
+      </c>
+      <c r="Q83" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R83" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>CMS SNF PPS final rule fact sheets, FY2024 to FY2027. A national Medicare index standing in for Hawaii nursing-home cost growth.</t>
         </is>
@@ -2863,7 +2913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="7" min="1" max="1"/>
@@ -3069,11 +3119,11 @@
           <t>EXCESS_BEDS(2023) (365 days)</t>
         </is>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>INDEX(EXCESS_BEDS,MATCH(2023,YEAR,0))</f>
         <v>89.1972602739726</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>89.2</f>
         <v>89.2</v>
       </c>
@@ -3101,11 +3151,11 @@
           <t>EXCESS_BEDS(2024) (366 days)</t>
         </is>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>INDEX(EXCESS_BEDS,MATCH(2024,YEAR,0))</f>
         <v>46.868852459016395</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>46.9</f>
         <v>46.9</v>
       </c>
@@ -3482,16 +3532,16 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CEIL_PER_PT_LO</t>
-        </is>
-      </c>
-      <c r="D22" s="35">
-        <f>CEIL_PER_PT_LO</f>
-        <v>1232.7243804034586</v>
-      </c>
-      <c r="E22" s="35">
-        <f>1232.72</f>
-        <v>1232.72</v>
+          <t>DAYS_SAVED_PER_PT</t>
+        </is>
+      </c>
+      <c r="D22" s="24">
+        <f>DAYS_SAVED_PER_PT</f>
+        <v>5.492795389048993</v>
+      </c>
+      <c r="E22" s="24">
+        <f>5.49</f>
+        <v>5.49</v>
       </c>
       <c r="F22">
         <f>0.005</f>
@@ -3514,16 +3564,16 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CEIL_PER_PT_HI</t>
+          <t>CEIL_PER_PT_LO</t>
         </is>
       </c>
       <c r="D23" s="35">
-        <f>CEIL_PER_PT_HI</f>
-        <v>19166.096138328532</v>
+        <f>CEIL_PER_PT_LO</f>
+        <v>347.36438040345837</v>
       </c>
       <c r="E23" s="35">
-        <f>19166.10</f>
-        <v>19166.1</v>
+        <f>347.36</f>
+        <v>347.36</v>
       </c>
       <c r="F23">
         <f>0.005</f>
@@ -3546,20 +3596,20 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>WL_DAYS_CHANGE_2024</t>
-        </is>
-      </c>
-      <c r="D24" s="19">
-        <f>WL_DAYS_CHANGE_2024</f>
-        <v>-0.26741037582584204</v>
-      </c>
-      <c r="E24" s="19">
-        <f>-0.267</f>
-        <v>-0.267</v>
+          <t>CEIL_PER_PT_HI</t>
+        </is>
+      </c>
+      <c r="D24" s="35">
+        <f>CEIL_PER_PT_HI</f>
+        <v>5400.736138328532</v>
+      </c>
+      <c r="E24" s="35">
+        <f>5400.74</f>
+        <v>5400.74</v>
       </c>
       <c r="F24">
-        <f>0.0005</f>
-        <v>0.0005</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G24" t="str">
         <f>IF(AND(ISNUMBER(D24),ISNUMBER(E24)),IF(ABS(D24-E24)&lt;=F24,"PASS","FAIL"),"FAIL")</f>
@@ -3578,20 +3628,20 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>T1_DROP_2021 (points)</t>
-        </is>
-      </c>
-      <c r="D25" s="24">
-        <f>T1_DROP_2021*100</f>
-        <v>-1.917989417989416</v>
-      </c>
-      <c r="E25" s="24">
-        <f>-1.92</f>
-        <v>-1.92</v>
+          <t>WL_DAYS_CHANGE_2024</t>
+        </is>
+      </c>
+      <c r="D25" s="20">
+        <f>WL_DAYS_CHANGE_2024</f>
+        <v>-0.26741037582584204</v>
+      </c>
+      <c r="E25" s="20">
+        <f>-0.267</f>
+        <v>-0.267</v>
       </c>
       <c r="F25">
-        <f>0.005</f>
-        <v>0.005</v>
+        <f>0.0005</f>
+        <v>0.0005</v>
       </c>
       <c r="G25" t="str">
         <f>IF(AND(ISNUMBER(D25),ISNUMBER(E25)),IF(ABS(D25-E25)&lt;=F25,"PASS","FAIL"),"FAIL")</f>
@@ -3610,16 +3660,16 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>T1_DROP_2024 (points)</t>
+          <t>T1_DROP_2021 (points)</t>
         </is>
       </c>
       <c r="D26" s="24">
-        <f>T1_DROP_2024*100</f>
-        <v>-11.121871500771721</v>
+        <f>T1_DROP_2021*100</f>
+        <v>-1.917989417989416</v>
       </c>
       <c r="E26" s="24">
-        <f>-11.12</f>
-        <v>-11.12</v>
+        <f>-1.92</f>
+        <v>-1.92</v>
       </c>
       <c r="F26">
         <f>0.005</f>
@@ -3642,16 +3692,16 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>T2_SLOPE (about)</t>
+          <t>T1_DROP_2024 (points)</t>
         </is>
       </c>
       <c r="D27" s="24">
-        <f>T2_SLOPE</f>
-        <v>1.8814212714379457</v>
+        <f>T1_DROP_2024*100</f>
+        <v>-11.121871500771721</v>
       </c>
       <c r="E27" s="24">
-        <f>1.88</f>
-        <v>1.88</v>
+        <f>-11.12</f>
+        <v>-11.12</v>
       </c>
       <c r="F27">
         <f>0.005</f>
@@ -3674,20 +3724,20 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>T3_YEARS</t>
-        </is>
-      </c>
-      <c r="D28" s="3">
-        <f>T3_YEARS</f>
-        <v>5</v>
-      </c>
-      <c r="E28" s="3">
-        <f>5</f>
-        <v>5</v>
+          <t>T2_SLOPE (about)</t>
+        </is>
+      </c>
+      <c r="D28" s="24">
+        <f>T2_SLOPE</f>
+        <v>1.8814212714379457</v>
+      </c>
+      <c r="E28" s="24">
+        <f>1.88</f>
+        <v>1.88</v>
       </c>
       <c r="F28">
-        <f>0</f>
-        <v>0</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G28" t="str">
         <f>IF(AND(ISNUMBER(D28),ISNUMBER(E28)),IF(ABS(D28-E28)&lt;=F28,"PASS","FAIL"),"FAIL")</f>
@@ -3706,23 +3756,23 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>T3: no bed largest in each of 2017 to 2021</t>
-        </is>
-      </c>
-      <c r="D29" t="b">
-        <f>AND(INDEX(LARGEST_REASON,MATCH(2017,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2018,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2019,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2020,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2021,YEAR,0))="No bed")</f>
-        <v>1</v>
-      </c>
-      <c r="E29" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F29" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
+          <t>T3_YEARS</t>
+        </is>
+      </c>
+      <c r="D29" s="3">
+        <f>T3_YEARS</f>
+        <v>5</v>
+      </c>
+      <c r="E29" s="3">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="F29">
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="G29" t="str">
-        <f>IF(D29=E29,"PASS","FAIL")</f>
+        <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29)),IF(ABS(D29-E29)&lt;=F29,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -3738,11 +3788,11 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>REASON_SUM(y) = DEC31_TOTAL(y), 2018 to 2024</t>
+          <t>T3: no bed largest in each of 2017 to 2021</t>
         </is>
       </c>
       <c r="D30" t="b">
-        <f>AND(INDEX(REASON_SUM,2)=INDEX(DEC31_TOTAL,2),INDEX(REASON_SUM,3)=INDEX(DEC31_TOTAL,3),INDEX(REASON_SUM,4)=INDEX(DEC31_TOTAL,4),INDEX(REASON_SUM,5)=INDEX(DEC31_TOTAL,5),INDEX(REASON_SUM,6)=INDEX(DEC31_TOTAL,6),INDEX(REASON_SUM,7)=INDEX(DEC31_TOTAL,7),INDEX(REASON_SUM,8)=INDEX(DEC31_TOTAL,8))</f>
+        <f>AND(INDEX(LARGEST_REASON,MATCH(2017,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2018,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2019,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2020,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2021,YEAR,0))="No bed")</f>
         <v>1</v>
       </c>
       <c r="E30" t="b">
@@ -3770,23 +3820,23 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>REASON_SUM(2017)</t>
-        </is>
-      </c>
-      <c r="D31" s="3">
-        <f>INDEX(REASON_SUM,MATCH(2017,YEAR,0))</f>
-        <v>120.0</v>
-      </c>
-      <c r="E31" s="3">
-        <f>120</f>
-        <v>120</v>
-      </c>
-      <c r="F31">
-        <f>0</f>
-        <v>0</v>
+          <t>REASON_SUM(y) = DEC31_TOTAL(y), 2018 to 2024</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <f>AND(INDEX(REASON_SUM,2)=INDEX(DEC31_TOTAL,2),INDEX(REASON_SUM,3)=INDEX(DEC31_TOTAL,3),INDEX(REASON_SUM,4)=INDEX(DEC31_TOTAL,4),INDEX(REASON_SUM,5)=INDEX(DEC31_TOTAL,5),INDEX(REASON_SUM,6)=INDEX(DEC31_TOTAL,6),INDEX(REASON_SUM,7)=INDEX(DEC31_TOTAL,7),INDEX(REASON_SUM,8)=INDEX(DEC31_TOTAL,8))</f>
+        <v>1</v>
+      </c>
+      <c r="E31" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F31" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
       </c>
       <c r="G31" t="str">
-        <f>IF(AND(ISNUMBER(D31),ISNUMBER(E31)),IF(ABS(D31-E31)&lt;=F31,"PASS","FAIL"),"FAIL")</f>
+        <f>IF(D31=E31,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -3802,16 +3852,16 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DEC31_TOTAL(2017)</t>
+          <t>REASON_SUM(2017)</t>
         </is>
       </c>
       <c r="D32" s="3">
-        <f>INDEX(DEC31_TOTAL,MATCH(2017,YEAR,0))</f>
-        <v>157</v>
+        <f>INDEX(REASON_SUM,MATCH(2017,YEAR,0))</f>
+        <v>120.0</v>
       </c>
       <c r="E32" s="3">
-        <f>157</f>
-        <v>157</v>
+        <f>120</f>
+        <v>120</v>
       </c>
       <c r="F32">
         <f>0</f>
@@ -3834,20 +3884,20 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>KFF_COST_DAY x 0.15 (arithmetic on the input)</t>
-        </is>
-      </c>
-      <c r="D33" s="35">
-        <f>KFF_COST_DAY*0.15</f>
-        <v>549.6</v>
-      </c>
-      <c r="E33" s="35">
-        <f>549.6</f>
-        <v>549.6</v>
+          <t>DEC31_TOTAL(2017)</t>
+        </is>
+      </c>
+      <c r="D33" s="3">
+        <f>INDEX(DEC31_TOTAL,MATCH(2017,YEAR,0))</f>
+        <v>157</v>
+      </c>
+      <c r="E33" s="3">
+        <f>157</f>
+        <v>157</v>
       </c>
       <c r="F33">
-        <f>0.005</f>
-        <v>0.005</v>
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="G33" t="str">
         <f>IF(AND(ISNUMBER(D33),ISNUMBER(E33)),IF(ABS(D33-E33)&lt;=F33,"PASS","FAIL"),"FAIL")</f>
@@ -3866,16 +3916,16 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>KFF_COST_DAY x 0.40 (arithmetic on the input)</t>
+          <t>KFF_COST_DAY x 0.15 (arithmetic on the input)</t>
         </is>
       </c>
       <c r="D34" s="35">
-        <f>KFF_COST_DAY*0.4</f>
-        <v>1465.6000000000001</v>
+        <f>KFF_COST_DAY*0.15</f>
+        <v>549.6</v>
       </c>
       <c r="E34" s="35">
-        <f>1465.6</f>
-        <v>1465.6</v>
+        <f>549.6</f>
+        <v>549.6</v>
       </c>
       <c r="F34">
         <f>0.005</f>
@@ -3898,20 +3948,20 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>KFF_COST_DAY x 0.15 within rounding (to $10) of AVOID_COST_LO</t>
+          <t>KFF_COST_DAY x 0.40 (arithmetic on the input)</t>
         </is>
       </c>
       <c r="D35" s="35">
-        <f>KFF_COST_DAY*0.15</f>
-        <v>549.6</v>
+        <f>KFF_COST_DAY*0.4</f>
+        <v>1465.6000000000001</v>
       </c>
       <c r="E35" s="35">
-        <f>AVOID_COST_LO</f>
-        <v>550</v>
+        <f>1465.6</f>
+        <v>1465.6</v>
       </c>
       <c r="F35">
-        <f>5</f>
-        <v>5</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G35" t="str">
         <f>IF(AND(ISNUMBER(D35),ISNUMBER(E35)),IF(ABS(D35-E35)&lt;=F35,"PASS","FAIL"),"FAIL")</f>
@@ -3930,16 +3980,16 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>KFF_COST_DAY x 0.40 within rounding (to $10) of AVOID_COST_HI</t>
+          <t>KFF_COST_DAY x 0.15 within rounding (to $10) of AVOID_COST_LO</t>
         </is>
       </c>
       <c r="D36" s="35">
-        <f>KFF_COST_DAY*0.4</f>
-        <v>1465.6000000000001</v>
+        <f>KFF_COST_DAY*0.15</f>
+        <v>549.6</v>
       </c>
       <c r="E36" s="35">
-        <f>AVOID_COST_HI</f>
-        <v>1470</v>
+        <f>AVOID_COST_LO</f>
+        <v>550</v>
       </c>
       <c r="F36">
         <f>5</f>
@@ -3962,20 +4012,20 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CAP_RATIO(2024)</t>
-        </is>
-      </c>
-      <c r="D37" s="24">
-        <f>INDEX(CAP_RATIO,MATCH(2024,YEAR,0))</f>
-        <v>11.692200069954529</v>
-      </c>
-      <c r="E37" s="24">
-        <f>11.69</f>
-        <v>11.69</v>
+          <t>KFF_COST_DAY x 0.40 within rounding (to $10) of AVOID_COST_HI</t>
+        </is>
+      </c>
+      <c r="D37" s="35">
+        <f>KFF_COST_DAY*0.4</f>
+        <v>1465.6000000000001</v>
+      </c>
+      <c r="E37" s="35">
+        <f>AVOID_COST_HI</f>
+        <v>1470</v>
       </c>
       <c r="F37">
-        <f>0.005</f>
-        <v>0.005</v>
+        <f>5</f>
+        <v>5</v>
       </c>
       <c r="G37" t="str">
         <f>IF(AND(ISNUMBER(D37),ISNUMBER(E37)),IF(ABS(D37-E37)&lt;=F37,"PASS","FAIL"),"FAIL")</f>
@@ -3994,16 +4044,16 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CAP_RATIO_STAFF_2024</t>
+          <t>CAP_RATIO(2024)</t>
         </is>
       </c>
       <c r="D38" s="24">
-        <f>CAP_RATIO_STAFF_2024</f>
-        <v>7.531654424623994</v>
+        <f>INDEX(CAP_RATIO,MATCH(2024,YEAR,0))</f>
+        <v>11.692200069954529</v>
       </c>
       <c r="E38" s="24">
-        <f>7.53</f>
-        <v>7.53</v>
+        <f>11.69</f>
+        <v>11.69</v>
       </c>
       <c r="F38">
         <f>0.005</f>
@@ -4026,20 +4076,20 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>T1_FIN_CHANGE_2021</t>
-        </is>
-      </c>
-      <c r="D39" s="3">
-        <f>T1_FIN_CHANGE_2021</f>
-        <v>13.0</v>
-      </c>
-      <c r="E39" s="3">
-        <f>13</f>
-        <v>13</v>
+          <t>CAP_RATIO_STAFF_2024</t>
+        </is>
+      </c>
+      <c r="D39" s="24">
+        <f>CAP_RATIO_STAFF_2024</f>
+        <v>7.531654424623994</v>
+      </c>
+      <c r="E39" s="24">
+        <f>7.53</f>
+        <v>7.53</v>
       </c>
       <c r="F39">
-        <f>0</f>
-        <v>0</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G39" t="str">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(E39)),IF(ABS(D39-E39)&lt;=F39,"PASS","FAIL"),"FAIL")</f>
@@ -4058,16 +4108,16 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>T1_OTHER_CHANGE_2021</t>
+          <t>T1_FIN_CHANGE_2021</t>
         </is>
       </c>
       <c r="D40" s="3">
-        <f>T1_OTHER_CHANGE_2021</f>
-        <v>32.0</v>
+        <f>T1_FIN_CHANGE_2021</f>
+        <v>13.0</v>
       </c>
       <c r="E40" s="3">
-        <f>32</f>
-        <v>32</v>
+        <f>13</f>
+        <v>13</v>
       </c>
       <c r="F40">
         <f>0</f>
@@ -4090,16 +4140,16 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>T1_FIN_CHANGE_2024</t>
+          <t>T1_OTHER_CHANGE_2021</t>
         </is>
       </c>
       <c r="D41" s="3">
-        <f>T1_FIN_CHANGE_2024</f>
-        <v>15.0</v>
+        <f>T1_OTHER_CHANGE_2021</f>
+        <v>32.0</v>
       </c>
       <c r="E41" s="3">
-        <f>15</f>
-        <v>15</v>
+        <f>32</f>
+        <v>32</v>
       </c>
       <c r="F41">
         <f>0</f>
@@ -4122,16 +4172,16 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>T1_OTHER_CHANGE_2024</t>
+          <t>T1_FIN_CHANGE_2024</t>
         </is>
       </c>
       <c r="D42" s="3">
-        <f>T1_OTHER_CHANGE_2024</f>
-        <v>-33.0</v>
+        <f>T1_FIN_CHANGE_2024</f>
+        <v>15.0</v>
       </c>
       <c r="E42" s="3">
-        <f>-33</f>
-        <v>-33.0</v>
+        <f>15</f>
+        <v>15</v>
       </c>
       <c r="F42">
         <f>0</f>
@@ -4154,20 +4204,20 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>RATE_GROWTH_2024_2026</t>
-        </is>
-      </c>
-      <c r="D43" s="25">
-        <f>RATE_GROWTH_2024_2026</f>
-        <v>0.013840668562237424</v>
-      </c>
-      <c r="E43" s="25">
-        <f>0.0138</f>
-        <v>0.0138</v>
+          <t>T1_OTHER_CHANGE_2024</t>
+        </is>
+      </c>
+      <c r="D43" s="3">
+        <f>T1_OTHER_CHANGE_2024</f>
+        <v>-33.0</v>
+      </c>
+      <c r="E43" s="3">
+        <f>-33</f>
+        <v>-33.0</v>
       </c>
       <c r="F43">
-        <f>5e-05</f>
-        <v>5e-05</v>
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="G43" t="str">
         <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43)),IF(ABS(D43-E43)&lt;=F43,"PASS","FAIL"),"FAIL")</f>
@@ -4186,20 +4236,20 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COST_FWD(2026)</t>
-        </is>
-      </c>
-      <c r="D44" s="35">
-        <f>INDEX(COST_FWD,3)</f>
-        <v>506.080140363</v>
-      </c>
-      <c r="E44" s="35">
-        <f>506.08</f>
-        <v>506.08</v>
+          <t>RATE_GROWTH_2024_2026</t>
+        </is>
+      </c>
+      <c r="D44" s="26">
+        <f>RATE_GROWTH_2024_2026</f>
+        <v>0.013840668562237424</v>
+      </c>
+      <c r="E44" s="26">
+        <f>0.0138</f>
+        <v>0.0138</v>
       </c>
       <c r="F44">
-        <f>0.005</f>
-        <v>0.005</v>
+        <f>5e-05</f>
+        <v>5e-05</v>
       </c>
       <c r="G44" t="str">
         <f>IF(AND(ISNUMBER(D44),ISNUMBER(E44)),IF(ABS(D44-E44)&lt;=F44,"PASS","FAIL"),"FAIL")</f>
@@ -4218,16 +4268,16 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COST_FWD(2027)</t>
+          <t>COST_FWD(2026)</t>
         </is>
       </c>
       <c r="D45" s="35">
-        <f>INDEX(COST_FWD,4)</f>
-        <v>522.780784994979</v>
+        <f>INDEX(COST_FWD,3)</f>
+        <v>506.080140363</v>
       </c>
       <c r="E45" s="35">
-        <f>522.78</f>
-        <v>522.78</v>
+        <f>506.08</f>
+        <v>506.08</v>
       </c>
       <c r="F45">
         <f>0.005</f>
@@ -4250,20 +4300,20 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COND_A_GAP(2026)</t>
-        </is>
-      </c>
-      <c r="D46" s="25">
-        <f>INDEX(COND_A_GAP,1)</f>
-        <v>0.021380290392819967</v>
-      </c>
-      <c r="E46" s="25">
-        <f>0.0214</f>
-        <v>0.0214</v>
+          <t>COST_FWD(2027)</t>
+        </is>
+      </c>
+      <c r="D46" s="35">
+        <f>INDEX(COST_FWD,4)</f>
+        <v>522.780784994979</v>
+      </c>
+      <c r="E46" s="35">
+        <f>522.78</f>
+        <v>522.78</v>
       </c>
       <c r="F46">
-        <f>5e-05</f>
-        <v>5e-05</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G46" t="str">
         <f>IF(AND(ISNUMBER(D46),ISNUMBER(E46)),IF(ABS(D46-E46)&lt;=F46,"PASS","FAIL"),"FAIL")</f>
@@ -4282,16 +4332,16 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COND_A_GAP(2027)</t>
-        </is>
-      </c>
-      <c r="D47" s="25">
-        <f>INDEX(COND_A_GAP,2)</f>
-        <v>0.039531015821562265</v>
-      </c>
-      <c r="E47" s="25">
-        <f>0.0395</f>
-        <v>0.0395</v>
+          <t>COND_A_GAP(2026)</t>
+        </is>
+      </c>
+      <c r="D47" s="26">
+        <f>INDEX(COND_A_GAP,1)</f>
+        <v>0.021380290392819967</v>
+      </c>
+      <c r="E47" s="26">
+        <f>0.0214</f>
+        <v>0.0214</v>
       </c>
       <c r="F47">
         <f>5e-05</f>
@@ -4302,131 +4352,131 @@
         <v>PASS</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="29">
+        <f>44</f>
+        <v>44</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>COND_A_GAP(2027)</t>
+        </is>
+      </c>
+      <c r="D48" s="26">
+        <f>INDEX(COND_A_GAP,2)</f>
+        <v>0.039531015821562265</v>
+      </c>
+      <c r="E48" s="26">
+        <f>0.0395</f>
+        <v>0.0395</v>
+      </c>
+      <c r="F48">
+        <f>5e-05</f>
+        <v>5e-05</v>
+      </c>
+      <c r="G48" t="str">
+        <f>IF(AND(ISNUMBER(D48),ISNUMBER(E48)),IF(ABS(D48-E48)&lt;=F48,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="29">
+        <f>45</f>
+        <v>45</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>STAY_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="D49" s="35">
+        <f>STAY_SHORTFALL</f>
+        <v>5873.496793247295</v>
+      </c>
+      <c r="E49" s="35">
+        <f>5873.50</f>
+        <v>5873.5</v>
+      </c>
+      <c r="F49">
+        <f>0.005</f>
+        <v>0.005</v>
+      </c>
+      <c r="G49" t="str">
+        <f>IF(AND(ISNUMBER(D49),ISNUMBER(E49)),IF(ABS(D49-E49)&lt;=F49,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Invariants (must pass for any inputs; part of ALL CHECKS)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Computed</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="29">
+    <row r="53">
+      <c r="A53" s="29">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>I1</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>The seven SHARE_ values sum to 1, every year</t>
         </is>
       </c>
-      <c r="D51" t="b">
+      <c r="D53" t="b">
         <f>AND(ABS(INDEX(SHARE_NO_BED,1)+INDEX(SHARE_BEHAVIOR,1)+INDEX(SHARE_SPECIAL_CARE,1)+INDEX(SHARE_FINANCIAL,1)+INDEX(SHARE_GUARDIANSHIP,1)+INDEX(SHARE_PASARR,1)+INDEX(SHARE_OTHER,1)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,2)+INDEX(SHARE_BEHAVIOR,2)+INDEX(SHARE_SPECIAL_CARE,2)+INDEX(SHARE_FINANCIAL,2)+INDEX(SHARE_GUARDIANSHIP,2)+INDEX(SHARE_PASARR,2)+INDEX(SHARE_OTHER,2)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,3)+INDEX(SHARE_BEHAVIOR,3)+INDEX(SHARE_SPECIAL_CARE,3)+INDEX(SHARE_FINANCIAL,3)+INDEX(SHARE_GUARDIANSHIP,3)+INDEX(SHARE_PASARR,3)+INDEX(SHARE_OTHER,3)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,4)+INDEX(SHARE_BEHAVIOR,4)+INDEX(SHARE_SPECIAL_CARE,4)+INDEX(SHARE_FINANCIAL,4)+INDEX(SHARE_GUARDIANSHIP,4)+INDEX(SHARE_PASARR,4)+INDEX(SHARE_OTHER,4)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,5)+INDEX(SHARE_BEHAVIOR,5)+INDEX(SHARE_SPECIAL_CARE,5)+INDEX(SHARE_FINANCIAL,5)+INDEX(SHARE_GUARDIANSHIP,5)+INDEX(SHARE_PASARR,5)+INDEX(SHARE_OTHER,5)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,6)+INDEX(SHARE_BEHAVIOR,6)+INDEX(SHARE_SPECIAL_CARE,6)+INDEX(SHARE_FINANCIAL,6)+INDEX(SHARE_GUARDIANSHIP,6)+INDEX(SHARE_PASARR,6)+INDEX(SHARE_OTHER,6)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,7)+INDEX(SHARE_BEHAVIOR,7)+INDEX(SHARE_SPECIAL_CARE,7)+INDEX(SHARE_FINANCIAL,7)+INDEX(SHARE_GUARDIANSHIP,7)+INDEX(SHARE_PASARR,7)+INDEX(SHARE_OTHER,7)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,8)+INDEX(SHARE_BEHAVIOR,8)+INDEX(SHARE_SPECIAL_CARE,8)+INDEX(SHARE_FINANCIAL,8)+INDEX(SHARE_GUARDIANSHIP,8)+INDEX(SHARE_PASARR,8)+INDEX(SHARE_OTHER,8)-1)&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E51" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F51" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G51" t="str">
-        <f>IF(D51=E51,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="29">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>WITHIN_DAYS + EXCESS_DAYS = WL_DAYS, every year</t>
-        </is>
-      </c>
-      <c r="D52" t="b">
-        <f>AND(ABS(INDEX(WITHIN_DAYS,1)+INDEX(EXCESS_DAYS,1)-INDEX(WL_DAYS,1))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,2)+INDEX(EXCESS_DAYS,2)-INDEX(WL_DAYS,2))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,3)+INDEX(EXCESS_DAYS,3)-INDEX(WL_DAYS,3))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,4)+INDEX(EXCESS_DAYS,4)-INDEX(WL_DAYS,4))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,5)+INDEX(EXCESS_DAYS,5)-INDEX(WL_DAYS,5))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,6)+INDEX(EXCESS_DAYS,6)-INDEX(WL_DAYS,6))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,7)+INDEX(EXCESS_DAYS,7)-INDEX(WL_DAYS,7))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,8)+INDEX(EXCESS_DAYS,8)-INDEX(WL_DAYS,8))&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E52" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F52" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G52" t="str">
-        <f>IF(D52=E52,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="29">
-        <f>3</f>
-        <v>3</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>I3</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>EXCESS_DAYS = MAX(0, GAP_PER_PT x WL_PATIENTS), every year (covers 2019 and 2022)</t>
-        </is>
-      </c>
-      <c r="D53" t="b">
-        <f>AND(ABS(INDEX(EXCESS_DAYS,1)-MAX(0,INDEX(GAP_PER_PT,1)*INDEX(WL_PATIENTS,1)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,2)-MAX(0,INDEX(GAP_PER_PT,2)*INDEX(WL_PATIENTS,2)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,3)-MAX(0,INDEX(GAP_PER_PT,3)*INDEX(WL_PATIENTS,3)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,4)-MAX(0,INDEX(GAP_PER_PT,4)*INDEX(WL_PATIENTS,4)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,5)-MAX(0,INDEX(GAP_PER_PT,5)*INDEX(WL_PATIENTS,5)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,6)-MAX(0,INDEX(GAP_PER_PT,6)*INDEX(WL_PATIENTS,6)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,7)-MAX(0,INDEX(GAP_PER_PT,7)*INDEX(WL_PATIENTS,7)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,8)-MAX(0,INDEX(GAP_PER_PT,8)*INDEX(WL_PATIENTS,8)))&lt;=1e-06)</f>
         <v>1</v>
       </c>
       <c r="E53" t="b">
@@ -4444,21 +4494,21 @@
     </row>
     <row r="54">
       <c r="A54" s="29">
-        <f>4</f>
-        <v>4</v>
+        <f>2</f>
+        <v>2</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>County CTY_DAYS sum to WL_DAYS, 2023 and 2024</t>
+          <t>WITHIN_DAYS + EXCESS_DAYS = WL_DAYS, every year</t>
         </is>
       </c>
       <c r="D54" t="b">
-        <f>AND(ABS(INDEX(CTY_DAYS,1,1)+INDEX(CTY_DAYS,2,1)+INDEX(CTY_DAYS,3,1)+INDEX(CTY_DAYS,4,1)-INDEX(WL_DAYS,MATCH(2023,YEAR,0)))&lt;=1e-06,ABS(INDEX(CTY_DAYS,1,2)+INDEX(CTY_DAYS,2,2)+INDEX(CTY_DAYS,3,2)+INDEX(CTY_DAYS,4,2)-INDEX(WL_DAYS,MATCH(2024,YEAR,0)))&lt;=1e-06)</f>
+        <f>AND(ABS(INDEX(WITHIN_DAYS,1)+INDEX(EXCESS_DAYS,1)-INDEX(WL_DAYS,1))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,2)+INDEX(EXCESS_DAYS,2)-INDEX(WL_DAYS,2))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,3)+INDEX(EXCESS_DAYS,3)-INDEX(WL_DAYS,3))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,4)+INDEX(EXCESS_DAYS,4)-INDEX(WL_DAYS,4))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,5)+INDEX(EXCESS_DAYS,5)-INDEX(WL_DAYS,5))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,6)+INDEX(EXCESS_DAYS,6)-INDEX(WL_DAYS,6))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,7)+INDEX(EXCESS_DAYS,7)-INDEX(WL_DAYS,7))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,8)+INDEX(EXCESS_DAYS,8)-INDEX(WL_DAYS,8))&lt;=1e-06)</f>
         <v>1</v>
       </c>
       <c r="E54" t="b">
@@ -4476,21 +4526,21 @@
     </row>
     <row r="55">
       <c r="A55" s="29">
-        <f>5</f>
-        <v>5</v>
+        <f>3</f>
+        <v>3</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>I5</t>
+          <t>I3</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>County CTY_DAY_SHARE sum to 1, 2023 and 2024</t>
+          <t>EXCESS_DAYS = MAX(0, GAP_PER_PT x WL_PATIENTS), every year (covers 2019 and 2022)</t>
         </is>
       </c>
       <c r="D55" t="b">
-        <f>AND(ABS(INDEX(CTY_DAY_SHARE,1,1)+INDEX(CTY_DAY_SHARE,2,1)+INDEX(CTY_DAY_SHARE,3,1)+INDEX(CTY_DAY_SHARE,4,1)-1)&lt;=1e-06,ABS(INDEX(CTY_DAY_SHARE,1,2)+INDEX(CTY_DAY_SHARE,2,2)+INDEX(CTY_DAY_SHARE,3,2)+INDEX(CTY_DAY_SHARE,4,2)-1)&lt;=1e-06)</f>
+        <f>AND(ABS(INDEX(EXCESS_DAYS,1)-MAX(0,INDEX(GAP_PER_PT,1)*INDEX(WL_PATIENTS,1)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,2)-MAX(0,INDEX(GAP_PER_PT,2)*INDEX(WL_PATIENTS,2)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,3)-MAX(0,INDEX(GAP_PER_PT,3)*INDEX(WL_PATIENTS,3)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,4)-MAX(0,INDEX(GAP_PER_PT,4)*INDEX(WL_PATIENTS,4)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,5)-MAX(0,INDEX(GAP_PER_PT,5)*INDEX(WL_PATIENTS,5)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,6)-MAX(0,INDEX(GAP_PER_PT,6)*INDEX(WL_PATIENTS,6)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,7)-MAX(0,INDEX(GAP_PER_PT,7)*INDEX(WL_PATIENTS,7)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,8)-MAX(0,INDEX(GAP_PER_PT,8)*INDEX(WL_PATIENTS,8)))&lt;=1e-06)</f>
         <v>1</v>
       </c>
       <c r="E55" t="b">
@@ -4508,122 +4558,122 @@
     </row>
     <row r="56">
       <c r="A56" s="29">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>County CTY_DAYS sum to WL_DAYS, 2023 and 2024</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <f>AND(ABS(INDEX(CTY_DAYS,1,1)+INDEX(CTY_DAYS,2,1)+INDEX(CTY_DAYS,3,1)+INDEX(CTY_DAYS,4,1)-INDEX(WL_DAYS,MATCH(2023,YEAR,0)))&lt;=1e-06,ABS(INDEX(CTY_DAYS,1,2)+INDEX(CTY_DAYS,2,2)+INDEX(CTY_DAYS,3,2)+INDEX(CTY_DAYS,4,2)-INDEX(WL_DAYS,MATCH(2024,YEAR,0)))&lt;=1e-06)</f>
+        <v>1</v>
+      </c>
+      <c r="E56" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F56" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
+      </c>
+      <c r="G56" t="str">
+        <f>IF(D56=E56,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>County CTY_DAY_SHARE sum to 1, 2023 and 2024</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <f>AND(ABS(INDEX(CTY_DAY_SHARE,1,1)+INDEX(CTY_DAY_SHARE,2,1)+INDEX(CTY_DAY_SHARE,3,1)+INDEX(CTY_DAY_SHARE,4,1)-1)&lt;=1e-06,ABS(INDEX(CTY_DAY_SHARE,1,2)+INDEX(CTY_DAY_SHARE,2,2)+INDEX(CTY_DAY_SHARE,3,2)+INDEX(CTY_DAY_SHARE,4,2)-1)&lt;=1e-06)</f>
+        <v>1</v>
+      </c>
+      <c r="E57" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F57" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
+      </c>
+      <c r="G57" t="str">
+        <f>IF(D57=E57,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>I6</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>T2_SLOPE = least-squares slope written out by hand, 2017 to 2023</t>
         </is>
       </c>
-      <c r="D56" s="24">
+      <c r="D58" s="24">
         <f>((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,1)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,2)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,3)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,4)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,5)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,6)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,7)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7))))/((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2)</f>
         <v>1.8814212714379457</v>
       </c>
-      <c r="E56" s="24">
+      <c r="E58" s="24">
         <f>T2_SLOPE</f>
         <v>1.8814212714379457</v>
       </c>
-      <c r="F56">
+      <c r="F58">
         <f>1e-06</f>
         <v>1e-06</v>
       </c>
-      <c r="G56" t="str">
-        <f>IF(AND(ISNUMBER(D56),ISNUMBER(E56)),IF(ABS(D56-E56)&lt;=F56,"PASS","FAIL"),"FAIL")</f>
+      <c r="G58" t="str">
+        <f>IF(AND(ISNUMBER(D58),ISNUMBER(E58)),IF(ABS(D58-E58)&lt;=F58,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="29">
+    <row r="59">
+      <c r="A59" s="29">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>I7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>T3_YEARS recomputed from the counts (no bed above each other reason)</t>
         </is>
       </c>
-      <c r="D57" s="3">
+      <c r="D59" s="3">
         <f>IF(AND(INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_BEHAVIOR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_SPECIAL_CARE,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_FINANCIAL,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_GUARDIANSHIP,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_PASARR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_OTHER,1)),1,0)+IF(AND(INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_BEHAVIOR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_SPECIAL_CARE,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_FINANCIAL,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_GUARDIANSHIP,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_PASARR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_OTHER,2)),1,0)+IF(AND(INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_BEHAVIOR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_SPECIAL_CARE,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_FINANCIAL,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_GUARDIANSHIP,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_PASARR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_OTHER,3)),1,0)+IF(AND(INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_BEHAVIOR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_SPECIAL_CARE,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_FINANCIAL,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_GUARDIANSHIP,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_PASARR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_OTHER,4)),1,0)+IF(AND(INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_BEHAVIOR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_SPECIAL_CARE,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_FINANCIAL,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_GUARDIANSHIP,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_PASARR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_OTHER,5)),1,0)+IF(AND(INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_BEHAVIOR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_SPECIAL_CARE,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_FINANCIAL,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_GUARDIANSHIP,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_PASARR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_OTHER,6)),1,0)+IF(AND(INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_BEHAVIOR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_SPECIAL_CARE,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_FINANCIAL,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_GUARDIANSHIP,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_PASARR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_OTHER,7)),1,0)+IF(AND(INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_BEHAVIOR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_SPECIAL_CARE,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_FINANCIAL,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_GUARDIANSHIP,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_PASARR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_OTHER,8)),1,0)</f>
         <v>5.0</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E59" s="3">
         <f>T3_YEARS</f>
         <v>5</v>
-      </c>
-      <c r="F57">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G57" t="str">
-        <f>IF(AND(ISNUMBER(D57),ISNUMBER(E57)),IF(ABS(D57-E57)&lt;=F57,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="29">
-        <f>8</f>
-        <v>8</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>I8</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>MEETS_BENCH is TRUE exactly when GAP_PER_PT &lt;= 0, every year</t>
-        </is>
-      </c>
-      <c r="D58" t="b">
-        <f>AND(INDEX(MEETS_BENCH,1)=(INDEX(GAP_PER_PT,1)&lt;=0),INDEX(MEETS_BENCH,2)=(INDEX(GAP_PER_PT,2)&lt;=0),INDEX(MEETS_BENCH,3)=(INDEX(GAP_PER_PT,3)&lt;=0),INDEX(MEETS_BENCH,4)=(INDEX(GAP_PER_PT,4)&lt;=0),INDEX(MEETS_BENCH,5)=(INDEX(GAP_PER_PT,5)&lt;=0),INDEX(MEETS_BENCH,6)=(INDEX(GAP_PER_PT,6)&lt;=0),INDEX(MEETS_BENCH,7)=(INDEX(GAP_PER_PT,7)&lt;=0),INDEX(MEETS_BENCH,8)=(INDEX(GAP_PER_PT,8)&lt;=0))</f>
-        <v>1</v>
-      </c>
-      <c r="E58" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F58" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G58" t="str">
-        <f>IF(D58=E58,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="29">
-        <f>9</f>
-        <v>9</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>I9</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Every WorkedExample row reads "match"</t>
-        </is>
-      </c>
-      <c r="D59" s="3">
-        <f>COUNTIF(WorkedExample!E29:E57,"match")</f>
-        <v>29</v>
-      </c>
-      <c r="E59" s="3">
-        <f>ROWS(WorkedExample!E29:E57)</f>
-        <v>29</v>
       </c>
       <c r="F59">
         <f>0</f>
@@ -4634,131 +4684,131 @@
         <v>PASS</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="29">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>I8</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>MEETS_BENCH is TRUE exactly when GAP_PER_PT &lt;= 0, every year</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <f>AND(INDEX(MEETS_BENCH,1)=(INDEX(GAP_PER_PT,1)&lt;=0),INDEX(MEETS_BENCH,2)=(INDEX(GAP_PER_PT,2)&lt;=0),INDEX(MEETS_BENCH,3)=(INDEX(GAP_PER_PT,3)&lt;=0),INDEX(MEETS_BENCH,4)=(INDEX(GAP_PER_PT,4)&lt;=0),INDEX(MEETS_BENCH,5)=(INDEX(GAP_PER_PT,5)&lt;=0),INDEX(MEETS_BENCH,6)=(INDEX(GAP_PER_PT,6)&lt;=0),INDEX(MEETS_BENCH,7)=(INDEX(GAP_PER_PT,7)&lt;=0),INDEX(MEETS_BENCH,8)=(INDEX(GAP_PER_PT,8)&lt;=0))</f>
+        <v>1</v>
+      </c>
+      <c r="E60" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F60" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
+      </c>
+      <c r="G60" t="str">
+        <f>IF(D60=E60,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="29">
+        <f>9</f>
+        <v>9</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>I9</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Every WorkedExample row reads "match"</t>
+        </is>
+      </c>
+      <c r="D61" s="3">
+        <f>COUNTIF(WorkedExample!E29:E57,"match")</f>
+        <v>29</v>
+      </c>
+      <c r="E61" s="3">
+        <f>ROWS(WorkedExample!E29:E57)</f>
+        <v>29</v>
+      </c>
+      <c r="F61">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G61" t="str">
+        <f>IF(AND(ISNUMBER(D61),ISNUMBER(E61)),IF(ABS(D61-E61)&lt;=F61,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Error scans (count of error values in each sheet's used range; part of ALL CHECKS)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Computed</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="29">
+    <row r="65">
+      <c r="A65" s="29">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Error scan</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>No error values: Inputs (A1:S84)</t>
-        </is>
-      </c>
-      <c r="D63" s="3">
-        <f>SUMPRODUCT(--ISERROR(Inputs!A1:S84))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E63" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G63" t="str">
-        <f>IF(AND(ISNUMBER(D63),ISNUMBER(E63)),IF(ABS(D63-E63)&lt;=F63,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="29">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>No error values: Waitlist (A1:V19)</t>
-        </is>
-      </c>
-      <c r="D64" s="3">
-        <f>SUMPRODUCT(--ISERROR(Waitlist!A1:V19))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E64" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G64" t="str">
-        <f>IF(AND(ISNUMBER(D64),ISNUMBER(E64)),IF(ABS(D64-E64)&lt;=F64,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="29">
-        <f>3</f>
-        <v>3</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>No error values: Cost (A1:F21)</t>
+          <t>No error values: Inputs (A1:S86)</t>
         </is>
       </c>
       <c r="D65" s="3">
-        <f>SUMPRODUCT(--ISERROR(Cost!A1:F21))</f>
+        <f>SUMPRODUCT(--ISERROR(Inputs!A1:S86))</f>
         <v>0.0</v>
       </c>
       <c r="E65" s="3">
@@ -4776,8 +4826,8 @@
     </row>
     <row r="66">
       <c r="A66" s="29">
-        <f>4</f>
-        <v>4</v>
+        <f>2</f>
+        <v>2</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
@@ -4786,11 +4836,11 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>No error values: Tests (A1:F41)</t>
+          <t>No error values: Waitlist (A1:V19)</t>
         </is>
       </c>
       <c r="D66" s="3">
-        <f>SUMPRODUCT(--ISERROR(Tests!A1:F41))</f>
+        <f>SUMPRODUCT(--ISERROR(Waitlist!A1:V19))</f>
         <v>0.0</v>
       </c>
       <c r="E66" s="3">
@@ -4808,8 +4858,8 @@
     </row>
     <row r="67">
       <c r="A67" s="29">
-        <f>5</f>
-        <v>5</v>
+        <f>3</f>
+        <v>3</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
@@ -4818,11 +4868,11 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>No error values: County (A1:F12)</t>
+          <t>No error values: Cost (A1:F22)</t>
         </is>
       </c>
       <c r="D67" s="3">
-        <f>SUMPRODUCT(--ISERROR(County!A1:F12))</f>
+        <f>SUMPRODUCT(--ISERROR(Cost!A1:F22))</f>
         <v>0.0</v>
       </c>
       <c r="E67" s="3">
@@ -4840,8 +4890,8 @@
     </row>
     <row r="68">
       <c r="A68" s="29">
-        <f>6</f>
-        <v>6</v>
+        <f>4</f>
+        <v>4</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
@@ -4850,11 +4900,11 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>No error values: Capacity (A1:E22)</t>
+          <t>No error values: Tests (A1:F41)</t>
         </is>
       </c>
       <c r="D68" s="3">
-        <f>SUMPRODUCT(--ISERROR(Capacity!A1:E22))</f>
+        <f>SUMPRODUCT(--ISERROR(Tests!A1:F41))</f>
         <v>0.0</v>
       </c>
       <c r="E68" s="3">
@@ -4872,8 +4922,8 @@
     </row>
     <row r="69">
       <c r="A69" s="29">
-        <f>7</f>
-        <v>7</v>
+        <f>5</f>
+        <v>5</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
@@ -4882,11 +4932,11 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>No error values: Conditions (A1:F17)</t>
+          <t>No error values: County (A1:F12)</t>
         </is>
       </c>
       <c r="D69" s="3">
-        <f>SUMPRODUCT(--ISERROR(Conditions!A1:F17))</f>
+        <f>SUMPRODUCT(--ISERROR(County!A1:F12))</f>
         <v>0.0</v>
       </c>
       <c r="E69" s="3">
@@ -4904,8 +4954,8 @@
     </row>
     <row r="70">
       <c r="A70" s="29">
-        <f>8</f>
-        <v>8</v>
+        <f>6</f>
+        <v>6</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
@@ -4914,11 +4964,11 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>No error values: FigureData (A1:J88)</t>
+          <t>No error values: Capacity (A1:E22)</t>
         </is>
       </c>
       <c r="D70" s="3">
-        <f>SUMPRODUCT(--ISERROR(FigureData!A1:J88))</f>
+        <f>SUMPRODUCT(--ISERROR(Capacity!A1:E22))</f>
         <v>0.0</v>
       </c>
       <c r="E70" s="3">
@@ -4936,8 +4986,8 @@
     </row>
     <row r="71">
       <c r="A71" s="29">
-        <f>9</f>
-        <v>9</v>
+        <f>7</f>
+        <v>7</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
@@ -4946,11 +4996,11 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>No error values: WorkedExample (A1:G62)</t>
+          <t>No error values: Conditions (A1:F17)</t>
         </is>
       </c>
       <c r="D71" s="3">
-        <f>SUMPRODUCT(--ISERROR(WorkedExample!A1:G62))</f>
+        <f>SUMPRODUCT(--ISERROR(Conditions!A1:F17))</f>
         <v>0.0</v>
       </c>
       <c r="E71" s="3">
@@ -4968,8 +5018,8 @@
     </row>
     <row r="72">
       <c r="A72" s="29">
-        <f>10</f>
-        <v>10</v>
+        <f>8</f>
+        <v>8</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
@@ -4978,11 +5028,11 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>No error values: Checks (rows 1 to 71, above this row)</t>
+          <t>No error values: FigureData (A1:J88)</t>
         </is>
       </c>
       <c r="D72" s="3">
-        <f>SUMPRODUCT(--ISERROR(A1:G71))</f>
+        <f>SUMPRODUCT(--ISERROR(FigureData!A1:J88))</f>
         <v>0.0</v>
       </c>
       <c r="E72" s="3">
@@ -4998,34 +5048,98 @@
         <v>PASS</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="29">
+        <f>9</f>
+        <v>9</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>No error values: WorkedExample (A1:G62)</t>
+        </is>
+      </c>
+      <c r="D73" s="3">
+        <f>SUMPRODUCT(--ISERROR(WorkedExample!A1:G62))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E73" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G73" t="str">
+        <f>IF(AND(ISNUMBER(D73),ISNUMBER(E73)),IF(ABS(D73-E73)&lt;=F73,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
     <row r="74">
+      <c r="A74" s="29">
+        <f>10</f>
+        <v>10</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>No error values: Checks (rows 1 to 73, above this row)</t>
+        </is>
+      </c>
+      <c r="D74" s="3">
+        <f>SUMPRODUCT(--ISERROR(A1:G73))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E74" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G74" t="str">
+        <f>IF(AND(ISNUMBER(D74),ISNUMBER(E74)),IF(ABS(D74-E74)&lt;=F74,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
           <t>ALL CHECKS (invariants and error scans)</t>
         </is>
       </c>
-      <c r="D74" s="4" t="str">
-        <f>IF(AND(COUNTIF(G51:G59,"FAIL")+COUNTIF(G63:G72,"FAIL")=0,COUNTIF(G51:G59,"PASS")+COUNTIF(G63:G72,"PASS")=19),"ALL PASS","REVIEW")</f>
+      <c r="D76" s="4" t="str">
+        <f>IF(AND(COUNTIF(G53:G61,"FAIL")+COUNTIF(G65:G74,"FAIL")=0,COUNTIF(G53:G61,"PASS")+COUNTIF(G65:G74,"PASS")=19),"ALL PASS","REVIEW")</f>
         <v>ALL PASS</v>
       </c>
     </row>
-    <row r="75">
-      <c r="C75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Anchors matching</t>
         </is>
       </c>
-      <c r="D75" s="3">
-        <f>COUNTIF(G5:G47,"PASS")</f>
-        <v>43</v>
-      </c>
-      <c r="E75" t="str">
-        <f>"of "&amp;ROWS(G5:G47)</f>
-        <v>of 43</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="15" t="inlineStr">
+      <c r="D77" s="3">
+        <f>COUNTIF(G5:G49,"PASS")</f>
+        <v>45</v>
+      </c>
+      <c r="E77" t="str">
+        <f>"of "&amp;ROWS(G5:G49)</f>
+        <v>of 45</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
         <is>
           <t>Anchor tolerance = half a unit of the spec's shown precision; invariant tolerance 1e-6. Checked outside the workbook by script (spec Audit findings): every calculated cell is a formula; every spec name exists as an absolute defined name and no others; every input cell is yellow and no calculated cell is.</t>
         </is>
@@ -5183,11 +5297,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14">
+      <c r="A4" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <f>INDEX(WL_DAYS,1)/INDEX(WL_PATIENTS,1)</f>
         <v>9.935348310974625</v>
       </c>
@@ -5195,7 +5309,7 @@
         <f>INDEX(WL_PATIENTS,1)*BENCH_DAYS</f>
         <v>86618.0</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="19">
         <f>INDEX(DAYS_PER_PT,1)-BENCH_DAYS</f>
         <v>-4.064651689025375</v>
       </c>
@@ -5211,7 +5325,7 @@
         <f>INDEX(WL_DAYS,1)-INDEX(EXCESS_DAYS,1)</f>
         <v>61470.0</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="20">
         <f>INDEX(EXCESS_DAYS,1)/INDEX(WL_DAYS,1)</f>
         <v>0.0</v>
       </c>
@@ -5219,7 +5333,7 @@
         <f>DATE(INDEX(YEAR,1)+1,1,1)-DATE(INDEX(YEAR,1),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="19">
         <f>INDEX(EXCESS_DAYS,1)/INDEX(DAYS_IN_YEAR,1)</f>
         <v>0.0</v>
       </c>
@@ -5231,31 +5345,31 @@
         <f>INDEX(REASON_NO_BED,1)+INDEX(REASON_BEHAVIOR,1)+INDEX(REASON_SPECIAL_CARE,1)+INDEX(REASON_FINANCIAL,1)+INDEX(REASON_GUARDIANSHIP,1)+INDEX(REASON_PASARR,1)+INDEX(REASON_OTHER,1)</f>
         <v>120.0</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="20">
         <f>INDEX(REASON_NO_BED,1)/INDEX(REASON_SUM,1)</f>
         <v>0.325</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="20">
         <f>INDEX(REASON_BEHAVIOR,1)/INDEX(REASON_SUM,1)</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,1)/INDEX(REASON_SUM,1)</f>
         <v>0.19166666666666668</v>
       </c>
-      <c r="P4" s="19">
+      <c r="P4" s="20">
         <f>INDEX(REASON_FINANCIAL,1)/INDEX(REASON_SUM,1)</f>
         <v>0.15</v>
       </c>
-      <c r="Q4" s="19">
+      <c r="Q4" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,1)/INDEX(REASON_SUM,1)</f>
         <v>0.09166666666666666</v>
       </c>
-      <c r="R4" s="19">
+      <c r="R4" s="20">
         <f>INDEX(REASON_PASARR,1)/INDEX(REASON_SUM,1)</f>
         <v>0.016666666666666666</v>
       </c>
-      <c r="S4" s="19">
+      <c r="S4" s="20">
         <f>INDEX(REASON_OTHER,1)/INDEX(REASON_SUM,1)</f>
         <v>0.09166666666666666</v>
       </c>
@@ -5269,11 +5383,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>INDEX(WL_DAYS,2)/INDEX(WL_PATIENTS,2)</f>
         <v>12.484132980732905</v>
       </c>
@@ -5281,7 +5395,7 @@
         <f>INDEX(WL_PATIENTS,2)*BENCH_DAYS</f>
         <v>74116.0</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>INDEX(DAYS_PER_PT,2)-BENCH_DAYS</f>
         <v>-1.5158670192670947</v>
       </c>
@@ -5297,7 +5411,7 @@
         <f>INDEX(WL_DAYS,2)-INDEX(EXCESS_DAYS,2)</f>
         <v>66091.0</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="20">
         <f>INDEX(EXCESS_DAYS,2)/INDEX(WL_DAYS,2)</f>
         <v>0.0</v>
       </c>
@@ -5305,7 +5419,7 @@
         <f>DATE(INDEX(YEAR,2)+1,1,1)-DATE(INDEX(YEAR,2),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="19">
         <f>INDEX(EXCESS_DAYS,2)/INDEX(DAYS_IN_YEAR,2)</f>
         <v>0.0</v>
       </c>
@@ -5317,31 +5431,31 @@
         <f>INDEX(REASON_NO_BED,2)+INDEX(REASON_BEHAVIOR,2)+INDEX(REASON_SPECIAL_CARE,2)+INDEX(REASON_FINANCIAL,2)+INDEX(REASON_GUARDIANSHIP,2)+INDEX(REASON_PASARR,2)+INDEX(REASON_OTHER,2)</f>
         <v>171.0</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="20">
         <f>INDEX(REASON_NO_BED,2)/INDEX(REASON_SUM,2)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="20">
         <f>INDEX(REASON_BEHAVIOR,2)/INDEX(REASON_SUM,2)</f>
         <v>0.1695906432748538</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,2)/INDEX(REASON_SUM,2)</f>
         <v>0.09941520467836257</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="20">
         <f>INDEX(REASON_FINANCIAL,2)/INDEX(REASON_SUM,2)</f>
         <v>0.18128654970760233</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,2)/INDEX(REASON_SUM,2)</f>
         <v>0.10526315789473684</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="20">
         <f>INDEX(REASON_PASARR,2)/INDEX(REASON_SUM,2)</f>
         <v>0.011695906432748537</v>
       </c>
-      <c r="S5" s="19">
+      <c r="S5" s="20">
         <f>INDEX(REASON_OTHER,2)/INDEX(REASON_SUM,2)</f>
         <v>0.09941520467836257</v>
       </c>
@@ -5355,11 +5469,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>INDEX(WL_DAYS,3)/INDEX(WL_PATIENTS,3)</f>
         <v>16.4741127348643</v>
       </c>
@@ -5367,7 +5481,7 @@
         <f>INDEX(WL_PATIENTS,3)*BENCH_DAYS</f>
         <v>67060.0</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <f>INDEX(DAYS_PER_PT,3)-BENCH_DAYS</f>
         <v>2.474112734864299</v>
       </c>
@@ -5383,7 +5497,7 @@
         <f>INDEX(WL_DAYS,3)-INDEX(EXCESS_DAYS,3)</f>
         <v>67060.0</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <f>INDEX(EXCESS_DAYS,3)/INDEX(WL_DAYS,3)</f>
         <v>0.1501818504391023</v>
       </c>
@@ -5391,7 +5505,7 @@
         <f>DATE(INDEX(YEAR,3)+1,1,1)-DATE(INDEX(YEAR,3),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="19">
         <f>INDEX(EXCESS_DAYS,3)/INDEX(DAYS_IN_YEAR,3)</f>
         <v>32.46849315068493</v>
       </c>
@@ -5403,31 +5517,31 @@
         <f>INDEX(REASON_NO_BED,3)+INDEX(REASON_BEHAVIOR,3)+INDEX(REASON_SPECIAL_CARE,3)+INDEX(REASON_FINANCIAL,3)+INDEX(REASON_GUARDIANSHIP,3)+INDEX(REASON_PASARR,3)+INDEX(REASON_OTHER,3)</f>
         <v>184.0</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="20">
         <f>INDEX(REASON_NO_BED,3)/INDEX(REASON_SUM,3)</f>
         <v>0.391304347826087</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="20">
         <f>INDEX(REASON_BEHAVIOR,3)/INDEX(REASON_SUM,3)</f>
         <v>0.14673913043478262</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,3)/INDEX(REASON_SUM,3)</f>
         <v>0.11413043478260869</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="20">
         <f>INDEX(REASON_FINANCIAL,3)/INDEX(REASON_SUM,3)</f>
         <v>0.17391304347826086</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="Q6" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,3)/INDEX(REASON_SUM,3)</f>
         <v>0.14130434782608695</v>
       </c>
-      <c r="R6" s="19">
+      <c r="R6" s="20">
         <f>INDEX(REASON_PASARR,3)/INDEX(REASON_SUM,3)</f>
         <v>0.0</v>
       </c>
-      <c r="S6" s="19">
+      <c r="S6" s="20">
         <f>INDEX(REASON_OTHER,3)/INDEX(REASON_SUM,3)</f>
         <v>0.03260869565217391</v>
       </c>
@@ -5441,11 +5555,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>INDEX(WL_DAYS,4)/INDEX(WL_PATIENTS,4)</f>
         <v>12.584449813309906</v>
       </c>
@@ -5453,7 +5567,7 @@
         <f>INDEX(WL_PATIENTS,4)*BENCH_DAYS</f>
         <v>63742.0</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>INDEX(DAYS_PER_PT,4)-BENCH_DAYS</f>
         <v>-1.4155501866900941</v>
       </c>
@@ -5469,7 +5583,7 @@
         <f>INDEX(WL_DAYS,4)-INDEX(EXCESS_DAYS,4)</f>
         <v>57297.0</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="20">
         <f>INDEX(EXCESS_DAYS,4)/INDEX(WL_DAYS,4)</f>
         <v>0.0</v>
       </c>
@@ -5477,7 +5591,7 @@
         <f>DATE(INDEX(YEAR,4)+1,1,1)-DATE(INDEX(YEAR,4),1,1)</f>
         <v>366.0</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="19">
         <f>INDEX(EXCESS_DAYS,4)/INDEX(DAYS_IN_YEAR,4)</f>
         <v>0.0</v>
       </c>
@@ -5489,31 +5603,31 @@
         <f>INDEX(REASON_NO_BED,4)+INDEX(REASON_BEHAVIOR,4)+INDEX(REASON_SPECIAL_CARE,4)+INDEX(REASON_FINANCIAL,4)+INDEX(REASON_GUARDIANSHIP,4)+INDEX(REASON_PASARR,4)+INDEX(REASON_OTHER,4)</f>
         <v>144.0</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="20">
         <f>INDEX(REASON_NO_BED,4)/INDEX(REASON_SUM,4)</f>
         <v>0.2847222222222222</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="20">
         <f>INDEX(REASON_BEHAVIOR,4)/INDEX(REASON_SUM,4)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,4)/INDEX(REASON_SUM,4)</f>
         <v>0.1527777777777778</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="20">
         <f>INDEX(REASON_FINANCIAL,4)/INDEX(REASON_SUM,4)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,4)/INDEX(REASON_SUM,4)</f>
         <v>0.10416666666666667</v>
       </c>
-      <c r="R7" s="19">
+      <c r="R7" s="20">
         <f>INDEX(REASON_PASARR,4)/INDEX(REASON_SUM,4)</f>
         <v>0.0</v>
       </c>
-      <c r="S7" s="19">
+      <c r="S7" s="20">
         <f>INDEX(REASON_OTHER,4)/INDEX(REASON_SUM,4)</f>
         <v>0.08333333333333333</v>
       </c>
@@ -5527,11 +5641,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>INDEX(WL_DAYS,5)/INDEX(WL_PATIENTS,5)</f>
         <v>12.187943982139233</v>
       </c>
@@ -5539,7 +5653,7 @@
         <f>INDEX(WL_PATIENTS,5)*BENCH_DAYS</f>
         <v>68978.0</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <f>INDEX(DAYS_PER_PT,5)-BENCH_DAYS</f>
         <v>-1.8120560178607672</v>
       </c>
@@ -5555,7 +5669,7 @@
         <f>INDEX(WL_DAYS,5)-INDEX(EXCESS_DAYS,5)</f>
         <v>60050.0</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="20">
         <f>INDEX(EXCESS_DAYS,5)/INDEX(WL_DAYS,5)</f>
         <v>0.0</v>
       </c>
@@ -5563,7 +5677,7 @@
         <f>DATE(INDEX(YEAR,5)+1,1,1)-DATE(INDEX(YEAR,5),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="19">
         <f>INDEX(EXCESS_DAYS,5)/INDEX(DAYS_IN_YEAR,5)</f>
         <v>0.0</v>
       </c>
@@ -5575,31 +5689,31 @@
         <f>INDEX(REASON_NO_BED,5)+INDEX(REASON_BEHAVIOR,5)+INDEX(REASON_SPECIAL_CARE,5)+INDEX(REASON_FINANCIAL,5)+INDEX(REASON_GUARDIANSHIP,5)+INDEX(REASON_PASARR,5)+INDEX(REASON_OTHER,5)</f>
         <v>189.0</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="20">
         <f>INDEX(REASON_NO_BED,5)/INDEX(REASON_SUM,5)</f>
         <v>0.26455026455026454</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="20">
         <f>INDEX(REASON_BEHAVIOR,5)/INDEX(REASON_SUM,5)</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,5)/INDEX(REASON_SUM,5)</f>
         <v>0.1164021164021164</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="20">
         <f>INDEX(REASON_FINANCIAL,5)/INDEX(REASON_SUM,5)</f>
         <v>0.2275132275132275</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="Q8" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,5)/INDEX(REASON_SUM,5)</f>
         <v>0.10582010582010581</v>
       </c>
-      <c r="R8" s="19">
+      <c r="R8" s="20">
         <f>INDEX(REASON_PASARR,5)/INDEX(REASON_SUM,5)</f>
         <v>0.0</v>
       </c>
-      <c r="S8" s="19">
+      <c r="S8" s="20">
         <f>INDEX(REASON_OTHER,5)/INDEX(REASON_SUM,5)</f>
         <v>0.09523809523809523</v>
       </c>
@@ -5613,11 +5727,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>INDEX(WL_DAYS,6)/INDEX(WL_PATIENTS,6)</f>
         <v>21.34229828850856</v>
       </c>
@@ -5625,7 +5739,7 @@
         <f>INDEX(WL_PATIENTS,6)*BENCH_DAYS</f>
         <v>51534.0</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>INDEX(DAYS_PER_PT,6)-BENCH_DAYS</f>
         <v>7.342298288508559</v>
       </c>
@@ -5641,7 +5755,7 @@
         <f>INDEX(WL_DAYS,6)-INDEX(EXCESS_DAYS,6)</f>
         <v>51534.0</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="20">
         <f>INDEX(EXCESS_DAYS,6)/INDEX(WL_DAYS,6)</f>
         <v>0.3440256615878107</v>
       </c>
@@ -5649,7 +5763,7 @@
         <f>DATE(INDEX(YEAR,6)+1,1,1)-DATE(INDEX(YEAR,6),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="19">
         <f>INDEX(EXCESS_DAYS,6)/INDEX(DAYS_IN_YEAR,6)</f>
         <v>74.04657534246576</v>
       </c>
@@ -5661,31 +5775,31 @@
         <f>INDEX(REASON_NO_BED,6)+INDEX(REASON_BEHAVIOR,6)+INDEX(REASON_SPECIAL_CARE,6)+INDEX(REASON_FINANCIAL,6)+INDEX(REASON_GUARDIANSHIP,6)+INDEX(REASON_PASARR,6)+INDEX(REASON_OTHER,6)</f>
         <v>250.0</v>
       </c>
-      <c r="M9" s="19">
+      <c r="M9" s="20">
         <f>INDEX(REASON_NO_BED,6)/INDEX(REASON_SUM,6)</f>
         <v>0.228</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="20">
         <f>INDEX(REASON_BEHAVIOR,6)/INDEX(REASON_SUM,6)</f>
         <v>0.14</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,6)/INDEX(REASON_SUM,6)</f>
         <v>0.156</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="20">
         <f>INDEX(REASON_FINANCIAL,6)/INDEX(REASON_SUM,6)</f>
         <v>0.3</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="Q9" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,6)/INDEX(REASON_SUM,6)</f>
         <v>0.116</v>
       </c>
-      <c r="R9" s="19">
+      <c r="R9" s="20">
         <f>INDEX(REASON_PASARR,6)/INDEX(REASON_SUM,6)</f>
         <v>0.02</v>
       </c>
-      <c r="S9" s="19">
+      <c r="S9" s="20">
         <f>INDEX(REASON_OTHER,6)/INDEX(REASON_SUM,6)</f>
         <v>0.04</v>
       </c>
@@ -5699,11 +5813,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>INDEX(WL_DAYS,7)/INDEX(WL_PATIENTS,7)</f>
         <v>23.018559556786702</v>
       </c>
@@ -5711,7 +5825,7 @@
         <f>INDEX(WL_PATIENTS,7)*BENCH_DAYS</f>
         <v>50540.0</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>INDEX(DAYS_PER_PT,7)-BENCH_DAYS</f>
         <v>9.018559556786702</v>
       </c>
@@ -5727,7 +5841,7 @@
         <f>INDEX(WL_DAYS,7)-INDEX(EXCESS_DAYS,7)</f>
         <v>50540.0</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="20">
         <f>INDEX(EXCESS_DAYS,7)/INDEX(WL_DAYS,7)</f>
         <v>0.3917951309914919</v>
       </c>
@@ -5735,7 +5849,7 @@
         <f>DATE(INDEX(YEAR,7)+1,1,1)-DATE(INDEX(YEAR,7),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="19">
         <f>INDEX(EXCESS_DAYS,7)/INDEX(DAYS_IN_YEAR,7)</f>
         <v>89.1972602739726</v>
       </c>
@@ -5747,31 +5861,31 @@
         <f>INDEX(REASON_NO_BED,7)+INDEX(REASON_BEHAVIOR,7)+INDEX(REASON_SPECIAL_CARE,7)+INDEX(REASON_FINANCIAL,7)+INDEX(REASON_GUARDIANSHIP,7)+INDEX(REASON_PASARR,7)+INDEX(REASON_OTHER,7)</f>
         <v>191.0</v>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="20">
         <f>INDEX(REASON_NO_BED,7)/INDEX(REASON_SUM,7)</f>
         <v>0.2198952879581152</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="20">
         <f>INDEX(REASON_BEHAVIOR,7)/INDEX(REASON_SUM,7)</f>
         <v>0.2513089005235602</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,7)/INDEX(REASON_SUM,7)</f>
         <v>0.13612565445026178</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="20">
         <f>INDEX(REASON_FINANCIAL,7)/INDEX(REASON_SUM,7)</f>
         <v>0.2356020942408377</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,7)/INDEX(REASON_SUM,7)</f>
         <v>0.14659685863874344</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="20">
         <f>INDEX(REASON_PASARR,7)/INDEX(REASON_SUM,7)</f>
         <v>0.005235602094240838</v>
       </c>
-      <c r="S10" s="19">
+      <c r="S10" s="20">
         <f>INDEX(REASON_OTHER,7)/INDEX(REASON_SUM,7)</f>
         <v>0.005235602094240838</v>
       </c>
@@ -5785,11 +5899,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>INDEX(WL_DAYS,8)/INDEX(WL_PATIENTS,8)</f>
         <v>19.492795389048993</v>
       </c>
@@ -5797,7 +5911,7 @@
         <f>INDEX(WL_PATIENTS,8)*BENCH_DAYS</f>
         <v>43722.0</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f>INDEX(DAYS_PER_PT,8)-BENCH_DAYS</f>
         <v>5.492795389048993</v>
       </c>
@@ -5813,7 +5927,7 @@
         <f>INDEX(WL_DAYS,8)-INDEX(EXCESS_DAYS,8)</f>
         <v>43722.0</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="20">
         <f>INDEX(EXCESS_DAYS,8)/INDEX(WL_DAYS,8)</f>
         <v>0.281785925487877</v>
       </c>
@@ -5821,7 +5935,7 @@
         <f>DATE(INDEX(YEAR,8)+1,1,1)-DATE(INDEX(YEAR,8),1,1)</f>
         <v>366.0</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="19">
         <f>INDEX(EXCESS_DAYS,8)/INDEX(DAYS_IN_YEAR,8)</f>
         <v>46.868852459016395</v>
       </c>
@@ -5833,31 +5947,31 @@
         <f>INDEX(REASON_NO_BED,8)+INDEX(REASON_BEHAVIOR,8)+INDEX(REASON_SPECIAL_CARE,8)+INDEX(REASON_FINANCIAL,8)+INDEX(REASON_GUARDIANSHIP,8)+INDEX(REASON_PASARR,8)+INDEX(REASON_OTHER,8)</f>
         <v>173.0</v>
       </c>
-      <c r="M11" s="19">
+      <c r="M11" s="20">
         <f>INDEX(REASON_NO_BED,8)/INDEX(REASON_SUM,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="20">
         <f>INDEX(REASON_BEHAVIOR,8)/INDEX(REASON_SUM,8)</f>
         <v>0.1676300578034682</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,8)/INDEX(REASON_SUM,8)</f>
         <v>0.10404624277456648</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="20">
         <f>INDEX(REASON_FINANCIAL,8)/INDEX(REASON_SUM,8)</f>
         <v>0.3468208092485549</v>
       </c>
-      <c r="Q11" s="19">
+      <c r="Q11" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,8)/INDEX(REASON_SUM,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="R11" s="19">
+      <c r="R11" s="20">
         <f>INDEX(REASON_PASARR,8)/INDEX(REASON_SUM,8)</f>
         <v>0.0</v>
       </c>
-      <c r="S11" s="19">
+      <c r="S11" s="20">
         <f>INDEX(REASON_OTHER,8)/INDEX(REASON_SUM,8)</f>
         <v>0.023121387283236993</v>
       </c>
@@ -5887,7 +6001,7 @@
         <f>INDEX(REASON_SUM,1)&lt;INDEX(DEC31_TOTAL,1)</f>
         <v>1</v>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>2017 reasons recorded for 120 of 157 patients on Dec 31; its shares use the recorded reasons only.</t>
         </is>
@@ -5903,7 +6017,7 @@
         <f>INDEX(LTC_UNSTAFFED,8)</f>
         <v>548</v>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Staffing note (reported only)</t>
         </is>
@@ -5921,7 +6035,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Excess days are measured against the average benchmark and are a lower bound on days patients spent beyond 14. All levels of care. Beds use calendar days (366 in 2020 and 2024).</t>
         </is>
@@ -5938,7 +6052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" style="7" min="1" max="1"/>
@@ -5983,7 +6097,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Excess days</t>
         </is>
@@ -6007,7 +6121,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Waitlisted rate, January</t>
         </is>
@@ -6027,7 +6141,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Waitlisted rate, July</t>
         </is>
@@ -6047,7 +6161,7 @@
       </c>
     </row>
     <row r="7" ht="31" customHeight="1" s="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Average waitlisted rate (WL_RATE_AVG); Now = WL_RATE_2026</t>
         </is>
@@ -6071,7 +6185,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Net cost per day, low (NET_COST_LO)</t>
         </is>
@@ -6095,7 +6209,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Net cost per day, high (NET_COST_HI)</t>
         </is>
@@ -6119,7 +6233,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Cost of excess days, low (EXCESS_COST_LO)</t>
         </is>
@@ -6143,7 +6257,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Cost of excess days, high (EXCESS_COST_HI)</t>
         </is>
@@ -6167,7 +6281,7 @@
       </c>
     </row>
     <row r="12" ht="31" customHeight="1" s="7">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Nursing-facility share of Dec 31 waitlist (NF_SHARE_DEC31), reported beside the result only</t>
         </is>
@@ -6177,86 +6291,102 @@
           <t>share</t>
         </is>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <f>INDEX(DEC31_NF,MATCH(2023,YEAR,0))/INDEX(DEC31_TOTAL,MATCH(2023,YEAR,0))</f>
         <v>0.8219895287958116</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>INDEX(DEC31_NF,MATCH(2024,YEAR,0))/INDEX(DEC31_TOTAL,MATCH(2024,YEAR,0))</f>
         <v>0.6936416184971098</v>
       </c>
     </row>
     <row r="13" ht="31" customHeight="1" s="7">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Ceiling per placed patient, low (CEIL_PER_PT_LO): net cost per day now x 2024 days per patient</t>
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Days saved per placed patient (DAYS_SAVED_PER_PT): 2024 days per patient minus the admission window</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="E13" s="24">
+        <f>MAX(0,INDEX(DAYS_PER_PT,MATCH(2024,YEAR,0))-ADMIT_WINDOW_DAYS)</f>
+        <v>5.492795389048993</v>
+      </c>
+    </row>
+    <row r="14" ht="31" customHeight="1" s="7">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Ceiling per placed patient, low (CEIL_PER_PT_LO): net cost per day now x days saved</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>USD per patient</t>
         </is>
       </c>
-      <c r="E13" s="35">
-        <f>NET_COST_LO_NOW*INDEX(DAYS_PER_PT,MATCH(2024,YEAR,0))</f>
-        <v>1232.7243804034586</v>
-      </c>
-    </row>
-    <row r="14" ht="31" customHeight="1" s="7">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>Ceiling per placed patient, high (CEIL_PER_PT_HI): net cost per day now x 2024 days per patient</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="E14" s="35">
+        <f>NET_COST_LO_NOW*DAYS_SAVED_PER_PT</f>
+        <v>347.36438040345837</v>
+      </c>
+    </row>
+    <row r="15" ht="31" customHeight="1" s="7">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Ceiling per placed patient, high (CEIL_PER_PT_HI): net cost per day now x days saved</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>USD per patient</t>
         </is>
       </c>
-      <c r="E14" s="35">
-        <f>NET_COST_HI_NOW*INDEX(DAYS_PER_PT,MATCH(2024,YEAR,0))</f>
-        <v>19166.096138328532</v>
-      </c>
-    </row>
-    <row r="16" ht="31" customHeight="1" s="7">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="E15" s="35">
+        <f>NET_COST_HI_NOW*DAYS_SAVED_PER_PT</f>
+        <v>5400.736138328532</v>
+      </c>
+    </row>
+    <row r="17" ht="31" customHeight="1" s="7">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Change in waitlist days, 2023 to 2024 (WL_DAYS_CHANGE_2024)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="C16" s="19">
+      <c r="C17" s="20">
         <f>INDEX(WL_DAYS,MATCH(2024,YEAR,0))/INDEX(WL_DAYS,MATCH(2023,YEAR,0))-1</f>
         <v>-0.26741037582584204</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Note: Leahi Hospital, Jan 2026 waitlisted rate</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>USD per day</t>
         </is>
       </c>
-      <c r="C17" s="35">
+      <c r="C18" s="35">
         <f>WL_RATE_LEAHI_2026</f>
         <v>480.19</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Reported as a note; the other hospitals are at WL_RATE_2026. Not used in a calculation.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Avoidable cost range AVOID_COST_LO to AVOID_COST_HI per waitlisted day, net of the waitlisted rate. All levels of care.</t>
         </is>
@@ -6313,11 +6443,11 @@
           <t>Financial share, Dec 31 2020</t>
         </is>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2020,YEAR,0))</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>COVID year</t>
         </is>
@@ -6329,11 +6459,11 @@
           <t>Financial share, Dec 31 2021</t>
         </is>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2021,YEAR,0))</f>
         <v>0.2275132275132275</v>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>COVID year</t>
         </is>
@@ -6345,11 +6475,11 @@
           <t>Drop, 2020 to 2021 (T1_DROP_2021; negative = rise)</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2020,YEAR,0))-INDEX(SHARE_FINANCIAL,MATCH(2021,YEAR,0))</f>
         <v>-0.019179894179894158</v>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Shown as a percent of the reasons total, i.e. percentage points</t>
         </is>
@@ -6365,7 +6495,7 @@
         <f>T1_DROP_2021*100&gt;=T1_MIN_DROP_PTS</f>
         <v>0</v>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Unrounded comparison; 2021 comparison is COVID-confounded</t>
         </is>
@@ -6377,7 +6507,7 @@
           <t>Financial share, Dec 31 2023</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2023,YEAR,0))</f>
         <v>0.2356020942408377</v>
       </c>
@@ -6388,7 +6518,7 @@
           <t>Financial share, Dec 31 2024</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2024,YEAR,0))</f>
         <v>0.3468208092485549</v>
       </c>
@@ -6399,11 +6529,11 @@
           <t>Drop, 2023 to 2024 (T1_DROP_2024; negative = rise)</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2023,YEAR,0))-INDEX(SHARE_FINANCIAL,MATCH(2024,YEAR,0))</f>
         <v>-0.11121871500771721</v>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Shown as a percent of the reasons total, i.e. percentage points</t>
         </is>
@@ -6419,7 +6549,7 @@
         <f>T1_DROP_2024*100&gt;=T1_MIN_DROP_PTS</f>
         <v>0</v>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Unrounded comparison</t>
         </is>
@@ -6435,7 +6565,7 @@
         <f>IF(AND(NOT(T1_PASS_2021),NOT(T1_PASS_2024)),"Falsified",IF(AND(T1_PASS_2021,NOT(T1_PASS_2024)),"Not falsified; weak (rests on the COVID-confounded 2021 comparison)","Not falsified"))</f>
         <v>Falsified</v>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Fails only if both drops fall short (lenient reading)</t>
         </is>
@@ -6464,11 +6594,11 @@
           <t>Least-squares slope of days per patient, 2017 to 2023 (T2_SLOPE)</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <f>SLOPE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7),INDEX(YEAR,1):INDEX(YEAR,7))</f>
         <v>1.8814212714379457</v>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>days per patient per year</t>
         </is>
@@ -6484,7 +6614,7 @@
         <f>IF(T2_SLOPE&lt;0,"Met","Not met")</f>
         <v>Not met</v>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Met = the trend slopes down (falling steadily toward 14)</t>
         </is>
@@ -6518,7 +6648,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14">
+      <c r="A19" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
@@ -6540,7 +6670,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
@@ -6562,7 +6692,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14">
+      <c r="A21" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
@@ -6584,7 +6714,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
@@ -6606,7 +6736,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14">
+      <c r="A23" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
@@ -6628,7 +6758,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
@@ -6650,7 +6780,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14">
+      <c r="A25" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
@@ -6672,7 +6802,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
@@ -6703,7 +6833,7 @@
         <f>COUNTIF(LARGEST_REASON,"No bed")</f>
         <v>5</v>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>of 8 years, 2017 to 2024</t>
         </is>
@@ -6719,7 +6849,7 @@
         <f>IF(T3_YEARS&gt;8/2,"Met","Not met")</f>
         <v>Met</v>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Met = more than half of 8 years (5 or more); a tie counts as not largest</t>
         </is>
@@ -6735,14 +6865,14 @@
         <f>FLAG_2017_INCOMPLETE</f>
         <v>1</v>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>2017 is counted on its recorded reasons (120 of 157) and flagged</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>The model reports each test's verdict. It does not rank or cost the options and does not choose between the add-on and the top-up.</t>
         </is>
@@ -6771,11 +6901,11 @@
           <t>Financial count change, Dec 2020 to Dec 2021 (T1_FIN_CHANGE_2021)</t>
         </is>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="25">
         <f>INDEX(REASON_FINANCIAL,MATCH(2021,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2020,YEAR,0))</f>
         <v>13.0</v>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>patients, Dec 31</t>
         </is>
@@ -6787,7 +6917,7 @@
           <t>Other six reasons change, Dec 2020 to Dec 2021 (T1_OTHER_CHANGE_2021)</t>
         </is>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="25">
         <f>(INDEX(REASON_SUM,MATCH(2021,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2021,YEAR,0)))-(INDEX(REASON_SUM,MATCH(2020,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2020,YEAR,0)))</f>
         <v>32.0</v>
       </c>
@@ -6798,7 +6928,7 @@
           <t>Financial count change, Dec 2023 to Dec 2024 (T1_FIN_CHANGE_2024)</t>
         </is>
       </c>
-      <c r="B36" s="23">
+      <c r="B36" s="25">
         <f>INDEX(REASON_FINANCIAL,MATCH(2024,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2023,YEAR,0))</f>
         <v>15.0</v>
       </c>
@@ -6809,13 +6939,13 @@
           <t>Other six reasons change, Dec 2023 to Dec 2024 (T1_OTHER_CHANGE_2024)</t>
         </is>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="25">
         <f>(INDEX(REASON_SUM,MATCH(2024,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2024,YEAR,0)))-(INDEX(REASON_SUM,MATCH(2023,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2023,YEAR,0)))</f>
         <v>-33.0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Side diagnostic: not a test; no verdict. Chosen on Sep 29, after the results were known (spec Conventions).</t>
         </is>
@@ -6881,19 +7011,19 @@
         <f>INDEX(COUNTY,1)</f>
         <v>Hawaii</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <f>INDEX(CTY_DAYS,1,1)/INDEX(CTY_PATIENTS,1,1)</f>
         <v>26.711162255466053</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <f>INDEX(CTY_DAYS,1,2)/INDEX(CTY_PATIENTS,1,2)</f>
         <v>27.74965612104539</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="20">
         <f>INDEX(CTY_DAYS,1,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.27933619745598515</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="20">
         <f>INDEX(CTY_DAYS,1,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.33139496681779357</v>
       </c>
@@ -6903,19 +7033,19 @@
         <f>INDEX(COUNTY,2)</f>
         <v>Honolulu</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>INDEX(CTY_DAYS,2,1)/INDEX(CTY_PATIENTS,2,1)</f>
         <v>17.883370288248337</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>INDEX(CTY_DAYS,2,2)/INDEX(CTY_PATIENTS,2,2)</f>
         <v>13.835270338554826</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <f>INDEX(CTY_DAYS,2,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.4853003116839356</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="20">
         <f>INDEX(CTY_DAYS,2,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.4497667389447401</v>
       </c>
@@ -6925,19 +7055,19 @@
         <f>INDEX(COUNTY,3)</f>
         <v>Kauai</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>INDEX(CTY_DAYS,3,1)/INDEX(CTY_PATIENTS,3,1)</f>
         <v>20.0</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>INDEX(CTY_DAYS,3,2)/INDEX(CTY_PATIENTS,3,2)</f>
         <v>30.109375</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <f>INDEX(CTY_DAYS,3,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.02069870151750364</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>INDEX(CTY_DAYS,3,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.031654510808857346</v>
       </c>
@@ -6947,19 +7077,19 @@
         <f>INDEX(COUNTY,4)</f>
         <v>Maui</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>INDEX(CTY_DAYS,4,1)/INDEX(CTY_PATIENTS,4,1)</f>
         <v>44.595</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>INDEX(CTY_DAYS,4,2)/INDEX(CTY_PATIENTS,4,2)</f>
         <v>32.28045325779037</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <f>INDEX(CTY_DAYS,4,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.21466478934257555</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <f>INDEX(CTY_DAYS,4,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.18718378342860897</v>
       </c>
@@ -6970,17 +7100,17 @@
           <t>Total share</t>
         </is>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <f>INDEX(CTY_DAY_SHARE,1,1)+INDEX(CTY_DAY_SHARE,2,1)+INDEX(CTY_DAY_SHARE,3,1)+INDEX(CTY_DAY_SHARE,4,1)</f>
         <v>1.0</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>INDEX(CTY_DAY_SHARE,1,2)+INDEX(CTY_DAY_SHARE,2,2)+INDEX(CTY_DAY_SHARE,3,2)+INDEX(CTY_DAY_SHARE,4,2)</f>
         <v>1.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>County = the county of the reporting hospital (Table 18 hospital rows summed).</t>
         </is>
@@ -7036,11 +7166,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14">
+      <c r="A4" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <f>INDEX(EXCESS_BEDS,1)</f>
         <v>0.0</v>
       </c>
@@ -7054,11 +7184,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>INDEX(EXCESS_BEDS,2)</f>
         <v>0.0</v>
       </c>
@@ -7072,11 +7202,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>INDEX(EXCESS_BEDS,3)</f>
         <v>32.46849315068493</v>
       </c>
@@ -7090,11 +7220,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>INDEX(EXCESS_BEDS,4)</f>
         <v>0.0</v>
       </c>
@@ -7108,11 +7238,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>INDEX(EXCESS_BEDS,5)</f>
         <v>0.0</v>
       </c>
@@ -7126,11 +7256,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>INDEX(EXCESS_BEDS,6)</f>
         <v>74.04657534246576</v>
       </c>
@@ -7144,11 +7274,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>INDEX(EXCESS_BEDS,7)</f>
         <v>89.1972602739726</v>
       </c>
@@ -7162,11 +7292,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>INDEX(EXCESS_BEDS,8)</f>
         <v>46.868852459016395</v>
       </c>
@@ -7202,35 +7332,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Blank where a year has no excess beds (no division by zero).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Limits (spec Conventions, Capacity comparison):</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>(1) Excess beds cover the acute waitlist across all levels of care on an average day; unstaffed beds are long-term-care beds on Dec 31. Not a bed-for-bed match.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>(2) Reopening beds idle for lack of staff is a workforce lever outside the scope; the capacity option is new transitional capacity.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>(3) Excess days are a lower bound, so excess beds are too.</t>
         </is>
@@ -7250,7 +7380,7 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" style="7" min="1" max="1"/>
+    <col width="88" customWidth="1" style="7" min="1" max="1"/>
     <col width="14" customWidth="1" style="7" min="2" max="2"/>
     <col width="20" customWidth="1" style="7" min="3" max="3"/>
     <col width="16" customWidth="1" style="7" min="4" max="4"/>
@@ -7308,7 +7438,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <f>INDEX(MB_GROSS,1)</f>
         <v>0.03</v>
       </c>
@@ -7323,7 +7453,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>INDEX(MB_GROSS,2)</f>
         <v>0.03</v>
       </c>
@@ -7338,7 +7468,7 @@
           <t>FY2026</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>INDEX(MB_GROSS,3)</f>
         <v>0.033</v>
       </c>
@@ -7350,7 +7480,7 @@
         <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2026,1,1),RATE_DATE,0))</f>
         <v>495.26</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>1-INDEX(RATE_FWD,1)/INDEX(COST_FWD,3)</f>
         <v>0.021380290392819967</v>
       </c>
@@ -7361,7 +7491,7 @@
           <t>FY2027</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>INDEX(MB_GROSS,4)</f>
         <v>0.033</v>
       </c>
@@ -7373,7 +7503,7 @@
         <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2026,1,1),RATE_DATE,0))*(1+RATE_GROWTH_2024_2026)</f>
         <v>502.1147295121337</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>1-INDEX(RATE_FWD,2)/INDEX(COST_FWD,4)</f>
         <v>0.039531015821562265</v>
       </c>
@@ -7384,39 +7514,55 @@
           <t>Post-reset rate pace, Jan 2024 to Jan 2026 (RATE_GROWTH_2024_2026)</t>
         </is>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <f>(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2026,1,1),RATE_DATE,0))/INDEX(NF_RATE_MEDIAN,MATCH(DATE(2024,1,1),RATE_DATE,0)))^(1/2)-1</f>
         <v>0.013840668562237424</v>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>a year, compounded over two years</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Cost above the rate over a median Medicaid stay, FY2026 (STAY_SHORTFALL)</t>
+        </is>
+      </c>
+      <c r="B11" s="35">
+        <f>(INDEX(COST_FWD,3)-INDEX(RATE_FWD,1))*MEDIAN_MCD_LOS</f>
+        <v>5873.496793247295</v>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>USD per stay; a rough comparison (spec Conventions)</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Rate for FY2026 = the January 2026 median; FY2027 carries it forward at the post-reset pace.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Cost is dated July 1 of the fiscal year and the rate January: a half-year mismatch.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>The market basket is a national Medicare index standing in for Hawaii nursing-home cost growth.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Not a forecast; the model does not rank or cost the options (spec Conventions, Condition (a)).</t>
         </is>
@@ -7489,7 +7635,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
@@ -7497,7 +7643,7 @@
         <f>DATE(INDEX(YEAR,1),7,1)</f>
         <v>42917</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>INDEX(DAYS_PER_PT,1)</f>
         <v>9.935348310974625</v>
       </c>
@@ -7511,7 +7657,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
@@ -7519,7 +7665,7 @@
         <f>DATE(INDEX(YEAR,2),7,1)</f>
         <v>43282</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>INDEX(DAYS_PER_PT,2)</f>
         <v>12.484132980732905</v>
       </c>
@@ -7533,7 +7679,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
@@ -7541,7 +7687,7 @@
         <f>DATE(INDEX(YEAR,3),7,1)</f>
         <v>43647</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>INDEX(DAYS_PER_PT,3)</f>
         <v>16.4741127348643</v>
       </c>
@@ -7555,7 +7701,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
@@ -7563,7 +7709,7 @@
         <f>DATE(INDEX(YEAR,4),7,1)</f>
         <v>44013</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>INDEX(DAYS_PER_PT,4)</f>
         <v>12.584449813309906</v>
       </c>
@@ -7577,7 +7723,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
@@ -7585,7 +7731,7 @@
         <f>DATE(INDEX(YEAR,5),7,1)</f>
         <v>44378</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>INDEX(DAYS_PER_PT,5)</f>
         <v>12.187943982139233</v>
       </c>
@@ -7599,7 +7745,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
@@ -7607,7 +7753,7 @@
         <f>DATE(INDEX(YEAR,6),7,1)</f>
         <v>44743</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>INDEX(DAYS_PER_PT,6)</f>
         <v>21.34229828850856</v>
       </c>
@@ -7621,7 +7767,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
@@ -7629,7 +7775,7 @@
         <f>DATE(INDEX(YEAR,7),7,1)</f>
         <v>45108</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <f>INDEX(DAYS_PER_PT,7)</f>
         <v>23.018559556786702</v>
       </c>
@@ -7643,7 +7789,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14">
+      <c r="A12" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
@@ -7651,7 +7797,7 @@
         <f>DATE(INDEX(YEAR,8),7,1)</f>
         <v>45474</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <f>INDEX(DAYS_PER_PT,8)</f>
         <v>19.492795389048993</v>
       </c>
@@ -7760,35 +7906,35 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14">
+      <c r="A21" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>INDEX(SHARE_NO_BED,1)</f>
         <v>0.325</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <f>INDEX(SHARE_BEHAVIOR,1)</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,1)</f>
         <v>0.19166666666666668</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <f>INDEX(SHARE_FINANCIAL,1)</f>
         <v>0.15</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,1)</f>
         <v>0.09166666666666666</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="20">
         <f>INDEX(SHARE_PASARR,1)</f>
         <v>0.016666666666666666</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="20">
         <f>INDEX(SHARE_OTHER,1)</f>
         <v>0.09166666666666666</v>
       </c>
@@ -7798,35 +7944,35 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>INDEX(SHARE_NO_BED,2)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <f>INDEX(SHARE_BEHAVIOR,2)</f>
         <v>0.1695906432748538</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,2)</f>
         <v>0.09941520467836257</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <f>INDEX(SHARE_FINANCIAL,2)</f>
         <v>0.18128654970760233</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,2)</f>
         <v>0.10526315789473684</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="20">
         <f>INDEX(SHARE_PASARR,2)</f>
         <v>0.011695906432748537</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="20">
         <f>INDEX(SHARE_OTHER,2)</f>
         <v>0.09941520467836257</v>
       </c>
@@ -7836,35 +7982,35 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14">
+      <c r="A23" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="20">
         <f>INDEX(SHARE_NO_BED,3)</f>
         <v>0.391304347826087</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="20">
         <f>INDEX(SHARE_BEHAVIOR,3)</f>
         <v>0.14673913043478262</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,3)</f>
         <v>0.11413043478260869</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="20">
         <f>INDEX(SHARE_FINANCIAL,3)</f>
         <v>0.17391304347826086</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,3)</f>
         <v>0.14130434782608695</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="20">
         <f>INDEX(SHARE_PASARR,3)</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="20">
         <f>INDEX(SHARE_OTHER,3)</f>
         <v>0.03260869565217391</v>
       </c>
@@ -7874,35 +8020,35 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <f>INDEX(SHARE_NO_BED,4)</f>
         <v>0.2847222222222222</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <f>INDEX(SHARE_BEHAVIOR,4)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,4)</f>
         <v>0.1527777777777778</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <f>INDEX(SHARE_FINANCIAL,4)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,4)</f>
         <v>0.10416666666666667</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <f>INDEX(SHARE_PASARR,4)</f>
         <v>0.0</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <f>INDEX(SHARE_OTHER,4)</f>
         <v>0.08333333333333333</v>
       </c>
@@ -7912,35 +8058,35 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14">
+      <c r="A25" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="20">
         <f>INDEX(SHARE_NO_BED,5)</f>
         <v>0.26455026455026454</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="20">
         <f>INDEX(SHARE_BEHAVIOR,5)</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,5)</f>
         <v>0.1164021164021164</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="20">
         <f>INDEX(SHARE_FINANCIAL,5)</f>
         <v>0.2275132275132275</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,5)</f>
         <v>0.10582010582010581</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="20">
         <f>INDEX(SHARE_PASARR,5)</f>
         <v>0.0</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="20">
         <f>INDEX(SHARE_OTHER,5)</f>
         <v>0.09523809523809523</v>
       </c>
@@ -7950,35 +8096,35 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="20">
         <f>INDEX(SHARE_NO_BED,6)</f>
         <v>0.228</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <f>INDEX(SHARE_BEHAVIOR,6)</f>
         <v>0.14</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,6)</f>
         <v>0.156</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <f>INDEX(SHARE_FINANCIAL,6)</f>
         <v>0.3</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,6)</f>
         <v>0.116</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <f>INDEX(SHARE_PASARR,6)</f>
         <v>0.02</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="20">
         <f>INDEX(SHARE_OTHER,6)</f>
         <v>0.04</v>
       </c>
@@ -7988,35 +8134,35 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14">
+      <c r="A27" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <f>INDEX(SHARE_NO_BED,7)</f>
         <v>0.2198952879581152</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <f>INDEX(SHARE_BEHAVIOR,7)</f>
         <v>0.2513089005235602</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,7)</f>
         <v>0.13612565445026178</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <f>INDEX(SHARE_FINANCIAL,7)</f>
         <v>0.2356020942408377</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,7)</f>
         <v>0.14659685863874344</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <f>INDEX(SHARE_PASARR,7)</f>
         <v>0.005235602094240838</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="20">
         <f>INDEX(SHARE_OTHER,7)</f>
         <v>0.005235602094240838</v>
       </c>
@@ -8026,35 +8172,35 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14">
+      <c r="A28" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="20">
         <f>INDEX(SHARE_NO_BED,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <f>INDEX(SHARE_BEHAVIOR,8)</f>
         <v>0.1676300578034682</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,8)</f>
         <v>0.10404624277456648</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <f>INDEX(SHARE_FINANCIAL,8)</f>
         <v>0.3468208092485549</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="20">
         <f>INDEX(SHARE_PASARR,8)</f>
         <v>0.0</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="20">
         <f>INDEX(SHARE_OTHER,8)</f>
         <v>0.023121387283236993</v>
       </c>
@@ -8093,11 +8239,11 @@
           <t>Across the 12% adjustment</t>
         </is>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="28">
         <f>YEAR(DATE_ADJ_2021)-1</f>
         <v>2020.0</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="28">
         <f>YEAR(DATE_ADJ_2021)</f>
         <v>2021</v>
       </c>
@@ -8108,11 +8254,11 @@
           <t>Across the reset</t>
         </is>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <f>YEAR(DATE_RESET_2024)-1</f>
         <v>2023.0</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="28">
         <f>YEAR(DATE_RESET_2024)</f>
         <v>2024</v>
       </c>
@@ -8142,7 +8288,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16">
+      <c r="A37" s="17">
         <f>DATE(2016,1,1)</f>
         <v>42370</v>
       </c>
@@ -8156,7 +8302,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16">
+      <c r="A38" s="17">
         <f>DATE(2016,7,1)</f>
         <v>42552</v>
       </c>
@@ -8170,7 +8316,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16">
+      <c r="A39" s="17">
         <f>DATE(2017,1,1)</f>
         <v>42736</v>
       </c>
@@ -8184,7 +8330,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16">
+      <c r="A40" s="17">
         <f>DATE(2017,7,1)</f>
         <v>42917</v>
       </c>
@@ -8198,7 +8344,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16">
+      <c r="A41" s="17">
         <f>DATE(2018,1,1)</f>
         <v>43101</v>
       </c>
@@ -8212,7 +8358,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16">
+      <c r="A42" s="17">
         <f>DATE(2018,7,1)</f>
         <v>43282</v>
       </c>
@@ -8226,7 +8372,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16">
+      <c r="A43" s="17">
         <f>DATE(2019,1,1)</f>
         <v>43466</v>
       </c>
@@ -8240,7 +8386,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16">
+      <c r="A44" s="17">
         <f>DATE(2019,7,1)</f>
         <v>43647</v>
       </c>
@@ -8254,7 +8400,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16">
+      <c r="A45" s="17">
         <f>DATE(2020,1,1)</f>
         <v>43831</v>
       </c>
@@ -8268,7 +8414,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16">
+      <c r="A46" s="17">
         <f>DATE(2020,7,1)</f>
         <v>44013</v>
       </c>
@@ -8282,7 +8428,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16">
+      <c r="A47" s="17">
         <f>DATE(2021,1,1)</f>
         <v>44197</v>
       </c>
@@ -8296,7 +8442,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16">
+      <c r="A48" s="17">
         <f>DATE(2021,7,1)</f>
         <v>44378</v>
       </c>
@@ -8310,7 +8456,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16">
+      <c r="A49" s="17">
         <f>DATE(2022,1,1)</f>
         <v>44562</v>
       </c>
@@ -8324,7 +8470,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16">
+      <c r="A50" s="17">
         <f>DATE(2022,7,1)</f>
         <v>44743</v>
       </c>
@@ -8338,7 +8484,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16">
+      <c r="A51" s="17">
         <f>DATE(2023,1,1)</f>
         <v>44927</v>
       </c>
@@ -8352,7 +8498,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16">
+      <c r="A52" s="17">
         <f>DATE(2023,7,1)</f>
         <v>45108</v>
       </c>
@@ -8366,7 +8512,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16">
+      <c r="A53" s="17">
         <f>DATE(2024,1,1)</f>
         <v>45292</v>
       </c>
@@ -8380,7 +8526,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16">
+      <c r="A54" s="17">
         <f>DATE(2024,7,1)</f>
         <v>45474</v>
       </c>
@@ -8394,7 +8540,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16">
+      <c r="A55" s="17">
         <f>DATE(2025,1,1)</f>
         <v>45658</v>
       </c>
@@ -8408,7 +8554,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="16">
+      <c r="A56" s="17">
         <f>DATE(2025,7,1)</f>
         <v>45839</v>
       </c>
@@ -8422,7 +8568,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16">
+      <c r="A57" s="17">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
       </c>
@@ -8465,7 +8611,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14">
+      <c r="A61" s="15">
         <f>INDEX(COST_FY,1)</f>
         <v>2011</v>
       </c>
@@ -8483,7 +8629,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14">
+      <c r="A62" s="15">
         <f>INDEX(COST_FY,2)</f>
         <v>2012</v>
       </c>
@@ -8501,7 +8647,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="14">
+      <c r="A63" s="15">
         <f>INDEX(COST_FY,3)</f>
         <v>2013</v>
       </c>
@@ -8519,7 +8665,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14">
+      <c r="A64" s="15">
         <f>INDEX(COST_FY,4)</f>
         <v>2014</v>
       </c>
@@ -8537,7 +8683,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14">
+      <c r="A65" s="15">
         <f>INDEX(COST_FY,5)</f>
         <v>2015</v>
       </c>
@@ -8555,7 +8701,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14">
+      <c r="A66" s="15">
         <f>INDEX(COST_FY,6)</f>
         <v>2016</v>
       </c>
@@ -8573,7 +8719,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14">
+      <c r="A67" s="15">
         <f>INDEX(COST_FY,7)</f>
         <v>2017</v>
       </c>
@@ -8591,7 +8737,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="14">
+      <c r="A68" s="15">
         <f>INDEX(COST_FY,8)</f>
         <v>2018</v>
       </c>
@@ -8609,7 +8755,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="14">
+      <c r="A69" s="15">
         <f>INDEX(COST_FY,9)</f>
         <v>2019</v>
       </c>
@@ -8627,7 +8773,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="14">
+      <c r="A70" s="15">
         <f>INDEX(COST_FY,10)</f>
         <v>2020</v>
       </c>
@@ -8645,7 +8791,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="14">
+      <c r="A71" s="15">
         <f>INDEX(COST_FY,11)</f>
         <v>2021</v>
       </c>
@@ -8663,7 +8809,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="14">
+      <c r="A72" s="15">
         <f>INDEX(COST_FY,12)</f>
         <v>2022</v>
       </c>
@@ -8681,7 +8827,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="14">
+      <c r="A73" s="15">
         <f>INDEX(COST_FY,13)</f>
         <v>2023</v>
       </c>
@@ -8728,7 +8874,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="14">
+      <c r="A77" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
@@ -8746,7 +8892,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="14">
+      <c r="A78" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
@@ -8764,7 +8910,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="14">
+      <c r="A79" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
@@ -8782,7 +8928,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="14">
+      <c r="A80" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
@@ -8800,7 +8946,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="14">
+      <c r="A81" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
@@ -8818,7 +8964,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="14">
+      <c r="A82" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
@@ -8836,7 +8982,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="14">
+      <c r="A83" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
@@ -8854,7 +9000,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="14">
+      <c r="A84" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
@@ -8872,7 +9018,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="15" t="inlineStr">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Figure g: schematic, no data (illustrative, not to scale).</t>
         </is>
@@ -8984,11 +9130,11 @@
       <c r="D8" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>C8/B8</f>
         <v>10.0</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="19">
         <f>D8/B8</f>
         <v>20.0</v>
       </c>
@@ -9006,11 +9152,11 @@
       <c r="D9" s="6" t="n">
         <v>1400</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>C9/B9</f>
         <v>14.0</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>D9/B9</f>
         <v>14.0</v>
       </c>
@@ -9028,11 +9174,11 @@
       <c r="D10" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>C10/B10</f>
         <v>20.0</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>D10/B10</f>
         <v>10.0</v>
       </c>
@@ -9168,10 +9314,10 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="B22" s="28" t="n">
+      <c r="B22" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C22" s="28" t="n">
+      <c r="C22" s="12" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9181,10 +9327,10 @@
           <t>E2</t>
         </is>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C23" s="12" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -9194,10 +9340,10 @@
           <t>E3</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n">
+      <c r="B24" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C24" s="12" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9207,10 +9353,10 @@
           <t>E4</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="12" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -9220,10 +9366,10 @@
           <t>E5</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C26" s="12" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -9966,7 +10112,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>Case E feeds the drops (in points) straight into the verdict formula; the share-to-drop step is covered by the regression anchors on Checks.</t>
         </is>

--- a/capabilities/economic-research/model.xlsx
+++ b/capabilities/economic-research/model.xlsx
@@ -112,6 +112,12 @@
     <definedName name="COND_A_GAP">'Conditions'!$E$7:$E$8</definedName>
     <definedName name="RATE_GROWTH_2024_2026">'Conditions'!$B$10</definedName>
     <definedName name="STAY_SHORTFALL">'Conditions'!$B$11</definedName>
+    <definedName name="RATE_COST_GAP">'Conditions'!$D$19:$D$26</definedName>
+    <definedName name="RATE_COST_GAP_MIN">'Conditions'!$B$28</definedName>
+    <definedName name="RATE_COST_GAP_MAX">'Conditions'!$B$29</definedName>
+    <definedName name="RATE_RISE_2021">'Conditions'!$B$31</definedName>
+    <definedName name="RATE_RISE_2024">'Conditions'!$B$32</definedName>
+    <definedName name="BEH_GUARD_SHARE_2024">'Conditions'!$B$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2913,7 +2919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="7" min="1" max="1"/>
@@ -4416,291 +4422,291 @@
         <v>PASS</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="29">
+        <f>46</f>
+        <v>46</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>RATE_RISE_2021</t>
+        </is>
+      </c>
+      <c r="D50" s="20">
+        <f>RATE_RISE_2021</f>
+        <v>0.1829457912219945</v>
+      </c>
+      <c r="E50" s="20">
+        <f>0.183</f>
+        <v>0.183</v>
+      </c>
+      <c r="F50">
+        <f>0.0005</f>
+        <v>0.0005</v>
+      </c>
+      <c r="G50" t="str">
+        <f>IF(AND(ISNUMBER(D50),ISNUMBER(E50)),IF(ABS(D50-E50)&lt;=F50,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Invariants (must pass for any inputs; part of ALL CHECKS)</t>
-        </is>
+      <c r="A51" s="29">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>RATE_RISE_2024</t>
+        </is>
+      </c>
+      <c r="D51" s="20">
+        <f>RATE_RISE_2024</f>
+        <v>0.29527675475147164</v>
+      </c>
+      <c r="E51" s="20">
+        <f>0.295</f>
+        <v>0.295</v>
+      </c>
+      <c r="F51">
+        <f>0.0005</f>
+        <v>0.0005</v>
+      </c>
+      <c r="G51" t="str">
+        <f>IF(AND(ISNUMBER(D51),ISNUMBER(E51)),IF(ABS(D51-E51)&lt;=F51,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
+      <c r="A52" s="29">
+        <f>48</f>
+        <v>48</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>RATE_COST_GAP_MIN</t>
+        </is>
+      </c>
+      <c r="D52" s="26">
+        <f>RATE_COST_GAP_MIN</f>
+        <v>0.19446068559301843</v>
+      </c>
+      <c r="E52" s="26">
+        <f>0.1945</f>
+        <v>0.1945</v>
+      </c>
+      <c r="F52">
+        <f>5e-05</f>
+        <v>5e-05</v>
+      </c>
+      <c r="G52" t="str">
+        <f>IF(AND(ISNUMBER(D52),ISNUMBER(E52)),IF(ABS(D52-E52)&lt;=F52,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="29">
+        <f>49</f>
+        <v>49</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>RATE_COST_GAP_MAX</t>
+        </is>
+      </c>
+      <c r="D53" s="26">
+        <f>RATE_COST_GAP_MAX</f>
+        <v>0.289584013255341</v>
+      </c>
+      <c r="E53" s="26">
+        <f>0.2896</f>
+        <v>0.2896</v>
+      </c>
+      <c r="F53">
+        <f>5e-05</f>
+        <v>5e-05</v>
+      </c>
+      <c r="G53" t="str">
+        <f>IF(AND(ISNUMBER(D53),ISNUMBER(E53)),IF(ABS(D53-E53)&lt;=F53,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29">
+        <f>50</f>
+        <v>50</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>BEH_GUARD_SHARE_2024</t>
+        </is>
+      </c>
+      <c r="D54" s="20">
+        <f>BEH_GUARD_SHARE_2024</f>
+        <v>0.3468208092485549</v>
+      </c>
+      <c r="E54" s="20">
+        <f>0.347</f>
+        <v>0.347</v>
+      </c>
+      <c r="F54">
+        <f>0.0005</f>
+        <v>0.0005</v>
+      </c>
+      <c r="G54" t="str">
+        <f>IF(AND(ISNUMBER(D54),ISNUMBER(E54)),IF(ABS(D54-E54)&lt;=F54,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Invariants (must pass for any inputs; part of ALL CHECKS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>I1</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>The seven SHARE_ values sum to 1, every year</t>
         </is>
       </c>
-      <c r="D53" t="b">
+      <c r="D58" t="b">
         <f>AND(ABS(INDEX(SHARE_NO_BED,1)+INDEX(SHARE_BEHAVIOR,1)+INDEX(SHARE_SPECIAL_CARE,1)+INDEX(SHARE_FINANCIAL,1)+INDEX(SHARE_GUARDIANSHIP,1)+INDEX(SHARE_PASARR,1)+INDEX(SHARE_OTHER,1)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,2)+INDEX(SHARE_BEHAVIOR,2)+INDEX(SHARE_SPECIAL_CARE,2)+INDEX(SHARE_FINANCIAL,2)+INDEX(SHARE_GUARDIANSHIP,2)+INDEX(SHARE_PASARR,2)+INDEX(SHARE_OTHER,2)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,3)+INDEX(SHARE_BEHAVIOR,3)+INDEX(SHARE_SPECIAL_CARE,3)+INDEX(SHARE_FINANCIAL,3)+INDEX(SHARE_GUARDIANSHIP,3)+INDEX(SHARE_PASARR,3)+INDEX(SHARE_OTHER,3)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,4)+INDEX(SHARE_BEHAVIOR,4)+INDEX(SHARE_SPECIAL_CARE,4)+INDEX(SHARE_FINANCIAL,4)+INDEX(SHARE_GUARDIANSHIP,4)+INDEX(SHARE_PASARR,4)+INDEX(SHARE_OTHER,4)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,5)+INDEX(SHARE_BEHAVIOR,5)+INDEX(SHARE_SPECIAL_CARE,5)+INDEX(SHARE_FINANCIAL,5)+INDEX(SHARE_GUARDIANSHIP,5)+INDEX(SHARE_PASARR,5)+INDEX(SHARE_OTHER,5)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,6)+INDEX(SHARE_BEHAVIOR,6)+INDEX(SHARE_SPECIAL_CARE,6)+INDEX(SHARE_FINANCIAL,6)+INDEX(SHARE_GUARDIANSHIP,6)+INDEX(SHARE_PASARR,6)+INDEX(SHARE_OTHER,6)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,7)+INDEX(SHARE_BEHAVIOR,7)+INDEX(SHARE_SPECIAL_CARE,7)+INDEX(SHARE_FINANCIAL,7)+INDEX(SHARE_GUARDIANSHIP,7)+INDEX(SHARE_PASARR,7)+INDEX(SHARE_OTHER,7)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,8)+INDEX(SHARE_BEHAVIOR,8)+INDEX(SHARE_SPECIAL_CARE,8)+INDEX(SHARE_FINANCIAL,8)+INDEX(SHARE_GUARDIANSHIP,8)+INDEX(SHARE_PASARR,8)+INDEX(SHARE_OTHER,8)-1)&lt;=1e-06)</f>
         <v>1</v>
       </c>
-      <c r="E53" t="b">
+      <c r="E58" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="F53" t="str">
+      <c r="F58" t="str">
         <f>"exact"</f>
         <v>exact</v>
       </c>
-      <c r="G53" t="str">
-        <f>IF(D53=E53,"PASS","FAIL")</f>
+      <c r="G58" t="str">
+        <f>IF(D58=E58,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="29">
+    <row r="59">
+      <c r="A59" s="29">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>I2</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>WITHIN_DAYS + EXCESS_DAYS = WL_DAYS, every year</t>
         </is>
       </c>
-      <c r="D54" t="b">
+      <c r="D59" t="b">
         <f>AND(ABS(INDEX(WITHIN_DAYS,1)+INDEX(EXCESS_DAYS,1)-INDEX(WL_DAYS,1))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,2)+INDEX(EXCESS_DAYS,2)-INDEX(WL_DAYS,2))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,3)+INDEX(EXCESS_DAYS,3)-INDEX(WL_DAYS,3))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,4)+INDEX(EXCESS_DAYS,4)-INDEX(WL_DAYS,4))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,5)+INDEX(EXCESS_DAYS,5)-INDEX(WL_DAYS,5))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,6)+INDEX(EXCESS_DAYS,6)-INDEX(WL_DAYS,6))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,7)+INDEX(EXCESS_DAYS,7)-INDEX(WL_DAYS,7))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,8)+INDEX(EXCESS_DAYS,8)-INDEX(WL_DAYS,8))&lt;=1e-06)</f>
         <v>1</v>
       </c>
-      <c r="E54" t="b">
+      <c r="E59" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="F54" t="str">
+      <c r="F59" t="str">
         <f>"exact"</f>
         <v>exact</v>
       </c>
-      <c r="G54" t="str">
-        <f>IF(D54=E54,"PASS","FAIL")</f>
+      <c r="G59" t="str">
+        <f>IF(D59=E59,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="29">
+    <row r="60">
+      <c r="A60" s="29">
         <f>3</f>
         <v>3</v>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>I3</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>EXCESS_DAYS = MAX(0, GAP_PER_PT x WL_PATIENTS), every year (covers 2019 and 2022)</t>
         </is>
       </c>
-      <c r="D55" t="b">
+      <c r="D60" t="b">
         <f>AND(ABS(INDEX(EXCESS_DAYS,1)-MAX(0,INDEX(GAP_PER_PT,1)*INDEX(WL_PATIENTS,1)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,2)-MAX(0,INDEX(GAP_PER_PT,2)*INDEX(WL_PATIENTS,2)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,3)-MAX(0,INDEX(GAP_PER_PT,3)*INDEX(WL_PATIENTS,3)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,4)-MAX(0,INDEX(GAP_PER_PT,4)*INDEX(WL_PATIENTS,4)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,5)-MAX(0,INDEX(GAP_PER_PT,5)*INDEX(WL_PATIENTS,5)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,6)-MAX(0,INDEX(GAP_PER_PT,6)*INDEX(WL_PATIENTS,6)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,7)-MAX(0,INDEX(GAP_PER_PT,7)*INDEX(WL_PATIENTS,7)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,8)-MAX(0,INDEX(GAP_PER_PT,8)*INDEX(WL_PATIENTS,8)))&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E55" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F55" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G55" t="str">
-        <f>IF(D55=E55,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="29">
-        <f>4</f>
-        <v>4</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>County CTY_DAYS sum to WL_DAYS, 2023 and 2024</t>
-        </is>
-      </c>
-      <c r="D56" t="b">
-        <f>AND(ABS(INDEX(CTY_DAYS,1,1)+INDEX(CTY_DAYS,2,1)+INDEX(CTY_DAYS,3,1)+INDEX(CTY_DAYS,4,1)-INDEX(WL_DAYS,MATCH(2023,YEAR,0)))&lt;=1e-06,ABS(INDEX(CTY_DAYS,1,2)+INDEX(CTY_DAYS,2,2)+INDEX(CTY_DAYS,3,2)+INDEX(CTY_DAYS,4,2)-INDEX(WL_DAYS,MATCH(2024,YEAR,0)))&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E56" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F56" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G56" t="str">
-        <f>IF(D56=E56,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="29">
-        <f>5</f>
-        <v>5</v>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>I5</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>County CTY_DAY_SHARE sum to 1, 2023 and 2024</t>
-        </is>
-      </c>
-      <c r="D57" t="b">
-        <f>AND(ABS(INDEX(CTY_DAY_SHARE,1,1)+INDEX(CTY_DAY_SHARE,2,1)+INDEX(CTY_DAY_SHARE,3,1)+INDEX(CTY_DAY_SHARE,4,1)-1)&lt;=1e-06,ABS(INDEX(CTY_DAY_SHARE,1,2)+INDEX(CTY_DAY_SHARE,2,2)+INDEX(CTY_DAY_SHARE,3,2)+INDEX(CTY_DAY_SHARE,4,2)-1)&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E57" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F57" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G57" t="str">
-        <f>IF(D57=E57,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="29">
-        <f>6</f>
-        <v>6</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>I6</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>T2_SLOPE = least-squares slope written out by hand, 2017 to 2023</t>
-        </is>
-      </c>
-      <c r="D58" s="24">
-        <f>((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,1)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,2)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,3)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,4)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,5)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,6)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,7)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7))))/((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2)</f>
-        <v>1.8814212714379457</v>
-      </c>
-      <c r="E58" s="24">
-        <f>T2_SLOPE</f>
-        <v>1.8814212714379457</v>
-      </c>
-      <c r="F58">
-        <f>1e-06</f>
-        <v>1e-06</v>
-      </c>
-      <c r="G58" t="str">
-        <f>IF(AND(ISNUMBER(D58),ISNUMBER(E58)),IF(ABS(D58-E58)&lt;=F58,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="29">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>I7</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>T3_YEARS recomputed from the counts (no bed above each other reason)</t>
-        </is>
-      </c>
-      <c r="D59" s="3">
-        <f>IF(AND(INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_BEHAVIOR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_SPECIAL_CARE,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_FINANCIAL,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_GUARDIANSHIP,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_PASARR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_OTHER,1)),1,0)+IF(AND(INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_BEHAVIOR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_SPECIAL_CARE,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_FINANCIAL,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_GUARDIANSHIP,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_PASARR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_OTHER,2)),1,0)+IF(AND(INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_BEHAVIOR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_SPECIAL_CARE,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_FINANCIAL,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_GUARDIANSHIP,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_PASARR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_OTHER,3)),1,0)+IF(AND(INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_BEHAVIOR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_SPECIAL_CARE,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_FINANCIAL,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_GUARDIANSHIP,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_PASARR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_OTHER,4)),1,0)+IF(AND(INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_BEHAVIOR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_SPECIAL_CARE,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_FINANCIAL,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_GUARDIANSHIP,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_PASARR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_OTHER,5)),1,0)+IF(AND(INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_BEHAVIOR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_SPECIAL_CARE,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_FINANCIAL,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_GUARDIANSHIP,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_PASARR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_OTHER,6)),1,0)+IF(AND(INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_BEHAVIOR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_SPECIAL_CARE,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_FINANCIAL,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_GUARDIANSHIP,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_PASARR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_OTHER,7)),1,0)+IF(AND(INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_BEHAVIOR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_SPECIAL_CARE,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_FINANCIAL,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_GUARDIANSHIP,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_PASARR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_OTHER,8)),1,0)</f>
-        <v>5.0</v>
-      </c>
-      <c r="E59" s="3">
-        <f>T3_YEARS</f>
-        <v>5</v>
-      </c>
-      <c r="F59">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G59" t="str">
-        <f>IF(AND(ISNUMBER(D59),ISNUMBER(E59)),IF(ABS(D59-E59)&lt;=F59,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="29">
-        <f>8</f>
-        <v>8</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>I8</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>MEETS_BENCH is TRUE exactly when GAP_PER_PT &lt;= 0, every year</t>
-        </is>
-      </c>
-      <c r="D60" t="b">
-        <f>AND(INDEX(MEETS_BENCH,1)=(INDEX(GAP_PER_PT,1)&lt;=0),INDEX(MEETS_BENCH,2)=(INDEX(GAP_PER_PT,2)&lt;=0),INDEX(MEETS_BENCH,3)=(INDEX(GAP_PER_PT,3)&lt;=0),INDEX(MEETS_BENCH,4)=(INDEX(GAP_PER_PT,4)&lt;=0),INDEX(MEETS_BENCH,5)=(INDEX(GAP_PER_PT,5)&lt;=0),INDEX(MEETS_BENCH,6)=(INDEX(GAP_PER_PT,6)&lt;=0),INDEX(MEETS_BENCH,7)=(INDEX(GAP_PER_PT,7)&lt;=0),INDEX(MEETS_BENCH,8)=(INDEX(GAP_PER_PT,8)&lt;=0))</f>
         <v>1</v>
       </c>
       <c r="E60" t="b">
@@ -4718,134 +4724,186 @@
     </row>
     <row r="61">
       <c r="A61" s="29">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>County CTY_DAYS sum to WL_DAYS, 2023 and 2024</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <f>AND(ABS(INDEX(CTY_DAYS,1,1)+INDEX(CTY_DAYS,2,1)+INDEX(CTY_DAYS,3,1)+INDEX(CTY_DAYS,4,1)-INDEX(WL_DAYS,MATCH(2023,YEAR,0)))&lt;=1e-06,ABS(INDEX(CTY_DAYS,1,2)+INDEX(CTY_DAYS,2,2)+INDEX(CTY_DAYS,3,2)+INDEX(CTY_DAYS,4,2)-INDEX(WL_DAYS,MATCH(2024,YEAR,0)))&lt;=1e-06)</f>
+        <v>1</v>
+      </c>
+      <c r="E61" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F61" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
+      </c>
+      <c r="G61" t="str">
+        <f>IF(D61=E61,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>County CTY_DAY_SHARE sum to 1, 2023 and 2024</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <f>AND(ABS(INDEX(CTY_DAY_SHARE,1,1)+INDEX(CTY_DAY_SHARE,2,1)+INDEX(CTY_DAY_SHARE,3,1)+INDEX(CTY_DAY_SHARE,4,1)-1)&lt;=1e-06,ABS(INDEX(CTY_DAY_SHARE,1,2)+INDEX(CTY_DAY_SHARE,2,2)+INDEX(CTY_DAY_SHARE,3,2)+INDEX(CTY_DAY_SHARE,4,2)-1)&lt;=1e-06)</f>
+        <v>1</v>
+      </c>
+      <c r="E62" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F62" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
+      </c>
+      <c r="G62" t="str">
+        <f>IF(D62=E62,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>T2_SLOPE = least-squares slope written out by hand, 2017 to 2023</t>
+        </is>
+      </c>
+      <c r="D63" s="24">
+        <f>((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,1)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,2)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,3)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,4)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,5)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,6)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,7)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7))))/((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2)</f>
+        <v>1.8814212714379457</v>
+      </c>
+      <c r="E63" s="24">
+        <f>T2_SLOPE</f>
+        <v>1.8814212714379457</v>
+      </c>
+      <c r="F63">
+        <f>1e-06</f>
+        <v>1e-06</v>
+      </c>
+      <c r="G63" t="str">
+        <f>IF(AND(ISNUMBER(D63),ISNUMBER(E63)),IF(ABS(D63-E63)&lt;=F63,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="29">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>T3_YEARS recomputed from the counts (no bed above each other reason)</t>
+        </is>
+      </c>
+      <c r="D64" s="3">
+        <f>IF(AND(INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_BEHAVIOR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_SPECIAL_CARE,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_FINANCIAL,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_GUARDIANSHIP,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_PASARR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_OTHER,1)),1,0)+IF(AND(INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_BEHAVIOR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_SPECIAL_CARE,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_FINANCIAL,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_GUARDIANSHIP,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_PASARR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_OTHER,2)),1,0)+IF(AND(INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_BEHAVIOR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_SPECIAL_CARE,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_FINANCIAL,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_GUARDIANSHIP,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_PASARR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_OTHER,3)),1,0)+IF(AND(INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_BEHAVIOR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_SPECIAL_CARE,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_FINANCIAL,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_GUARDIANSHIP,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_PASARR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_OTHER,4)),1,0)+IF(AND(INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_BEHAVIOR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_SPECIAL_CARE,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_FINANCIAL,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_GUARDIANSHIP,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_PASARR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_OTHER,5)),1,0)+IF(AND(INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_BEHAVIOR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_SPECIAL_CARE,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_FINANCIAL,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_GUARDIANSHIP,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_PASARR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_OTHER,6)),1,0)+IF(AND(INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_BEHAVIOR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_SPECIAL_CARE,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_FINANCIAL,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_GUARDIANSHIP,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_PASARR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_OTHER,7)),1,0)+IF(AND(INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_BEHAVIOR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_SPECIAL_CARE,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_FINANCIAL,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_GUARDIANSHIP,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_PASARR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_OTHER,8)),1,0)</f>
+        <v>5.0</v>
+      </c>
+      <c r="E64" s="3">
+        <f>T3_YEARS</f>
+        <v>5</v>
+      </c>
+      <c r="F64">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G64" t="str">
+        <f>IF(AND(ISNUMBER(D64),ISNUMBER(E64)),IF(ABS(D64-E64)&lt;=F64,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>I8</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>MEETS_BENCH is TRUE exactly when GAP_PER_PT &lt;= 0, every year</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <f>AND(INDEX(MEETS_BENCH,1)=(INDEX(GAP_PER_PT,1)&lt;=0),INDEX(MEETS_BENCH,2)=(INDEX(GAP_PER_PT,2)&lt;=0),INDEX(MEETS_BENCH,3)=(INDEX(GAP_PER_PT,3)&lt;=0),INDEX(MEETS_BENCH,4)=(INDEX(GAP_PER_PT,4)&lt;=0),INDEX(MEETS_BENCH,5)=(INDEX(GAP_PER_PT,5)&lt;=0),INDEX(MEETS_BENCH,6)=(INDEX(GAP_PER_PT,6)&lt;=0),INDEX(MEETS_BENCH,7)=(INDEX(GAP_PER_PT,7)&lt;=0),INDEX(MEETS_BENCH,8)=(INDEX(GAP_PER_PT,8)&lt;=0))</f>
+        <v>1</v>
+      </c>
+      <c r="E65" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F65" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
+      </c>
+      <c r="G65" t="str">
+        <f>IF(D65=E65,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29">
         <f>9</f>
         <v>9</v>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>I9</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Every WorkedExample row reads "match"</t>
         </is>
       </c>
-      <c r="D61" s="3">
+      <c r="D66" s="3">
         <f>COUNTIF(WorkedExample!E29:E57,"match")</f>
         <v>29</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E66" s="3">
         <f>ROWS(WorkedExample!E29:E57)</f>
         <v>29</v>
-      </c>
-      <c r="F61">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G61" t="str">
-        <f>IF(AND(ISNUMBER(D61),ISNUMBER(E61)),IF(ABS(D61-E61)&lt;=F61,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Error scans (count of error values in each sheet's used range; part of ALL CHECKS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="29">
-        <f>1</f>
-        <v>1</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>No error values: Inputs (A1:S86)</t>
-        </is>
-      </c>
-      <c r="D65" s="3">
-        <f>SUMPRODUCT(--ISERROR(Inputs!A1:S86))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E65" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G65" t="str">
-        <f>IF(AND(ISNUMBER(D65),ISNUMBER(E65)),IF(ABS(D65-E65)&lt;=F65,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="29">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>No error values: Waitlist (A1:V19)</t>
-        </is>
-      </c>
-      <c r="D66" s="3">
-        <f>SUMPRODUCT(--ISERROR(Waitlist!A1:V19))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E66" s="3">
-        <f>0</f>
-        <v>0</v>
       </c>
       <c r="F66">
         <f>0</f>
@@ -4856,106 +4914,54 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29">
-        <f>3</f>
-        <v>3</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>No error values: Cost (A1:F22)</t>
-        </is>
-      </c>
-      <c r="D67" s="3">
-        <f>SUMPRODUCT(--ISERROR(Cost!A1:F22))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E67" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G67" t="str">
-        <f>IF(AND(ISNUMBER(D67),ISNUMBER(E67)),IF(ABS(D67-E67)&lt;=F67,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
     <row r="68">
-      <c r="A68" s="29">
-        <f>4</f>
-        <v>4</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>No error values: Tests (A1:F41)</t>
-        </is>
-      </c>
-      <c r="D68" s="3">
-        <f>SUMPRODUCT(--ISERROR(Tests!A1:F41))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E68" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G68" t="str">
-        <f>IF(AND(ISNUMBER(D68),ISNUMBER(E68)),IF(ABS(D68-E68)&lt;=F68,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Error scans (count of error values in each sheet's used range; part of ALL CHECKS)</t>
+        </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29">
-        <f>5</f>
-        <v>5</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>No error values: County (A1:F12)</t>
-        </is>
-      </c>
-      <c r="D69" s="3">
-        <f>SUMPRODUCT(--ISERROR(County!A1:F12))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E69" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F69">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G69" t="str">
-        <f>IF(AND(ISNUMBER(D69),ISNUMBER(E69)),IF(ABS(D69-E69)&lt;=F69,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="29">
-        <f>6</f>
-        <v>6</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
@@ -4964,11 +4970,11 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>No error values: Capacity (A1:E22)</t>
+          <t>No error values: Inputs (A1:S86)</t>
         </is>
       </c>
       <c r="D70" s="3">
-        <f>SUMPRODUCT(--ISERROR(Capacity!A1:E22))</f>
+        <f>SUMPRODUCT(--ISERROR(Inputs!A1:S86))</f>
         <v>0.0</v>
       </c>
       <c r="E70" s="3">
@@ -4986,8 +4992,8 @@
     </row>
     <row r="71">
       <c r="A71" s="29">
-        <f>7</f>
-        <v>7</v>
+        <f>2</f>
+        <v>2</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
@@ -4996,11 +5002,11 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>No error values: Conditions (A1:F17)</t>
+          <t>No error values: Waitlist (A1:V19)</t>
         </is>
       </c>
       <c r="D71" s="3">
-        <f>SUMPRODUCT(--ISERROR(Conditions!A1:F17))</f>
+        <f>SUMPRODUCT(--ISERROR(Waitlist!A1:V19))</f>
         <v>0.0</v>
       </c>
       <c r="E71" s="3">
@@ -5018,8 +5024,8 @@
     </row>
     <row r="72">
       <c r="A72" s="29">
-        <f>8</f>
-        <v>8</v>
+        <f>3</f>
+        <v>3</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
@@ -5028,11 +5034,11 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>No error values: FigureData (A1:J88)</t>
+          <t>No error values: Cost (A1:F22)</t>
         </is>
       </c>
       <c r="D72" s="3">
-        <f>SUMPRODUCT(--ISERROR(FigureData!A1:J88))</f>
+        <f>SUMPRODUCT(--ISERROR(Cost!A1:F22))</f>
         <v>0.0</v>
       </c>
       <c r="E72" s="3">
@@ -5050,8 +5056,8 @@
     </row>
     <row r="73">
       <c r="A73" s="29">
-        <f>9</f>
-        <v>9</v>
+        <f>4</f>
+        <v>4</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
@@ -5060,11 +5066,11 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>No error values: WorkedExample (A1:G62)</t>
+          <t>No error values: Tests (A1:F41)</t>
         </is>
       </c>
       <c r="D73" s="3">
-        <f>SUMPRODUCT(--ISERROR(WorkedExample!A1:G62))</f>
+        <f>SUMPRODUCT(--ISERROR(Tests!A1:F41))</f>
         <v>0.0</v>
       </c>
       <c r="E73" s="3">
@@ -5082,8 +5088,8 @@
     </row>
     <row r="74">
       <c r="A74" s="29">
-        <f>10</f>
-        <v>10</v>
+        <f>5</f>
+        <v>5</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
@@ -5092,11 +5098,11 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>No error values: Checks (rows 1 to 73, above this row)</t>
+          <t>No error values: County (A1:F12)</t>
         </is>
       </c>
       <c r="D74" s="3">
-        <f>SUMPRODUCT(--ISERROR(A1:G73))</f>
+        <f>SUMPRODUCT(--ISERROR(County!A1:F12))</f>
         <v>0.0</v>
       </c>
       <c r="E74" s="3">
@@ -5112,34 +5118,194 @@
         <v>PASS</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>No error values: Capacity (A1:E22)</t>
+        </is>
+      </c>
+      <c r="D75" s="3">
+        <f>SUMPRODUCT(--ISERROR(Capacity!A1:E22))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E75" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G75" t="str">
+        <f>IF(AND(ISNUMBER(D75),ISNUMBER(E75)),IF(ABS(D75-E75)&lt;=F75,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
     <row r="76">
+      <c r="A76" s="29">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>No error values: Conditions (A1:F38)</t>
+        </is>
+      </c>
+      <c r="D76" s="3">
+        <f>SUMPRODUCT(--ISERROR(Conditions!A1:F38))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E76" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G76" t="str">
+        <f>IF(AND(ISNUMBER(D76),ISNUMBER(E76)),IF(ABS(D76-E76)&lt;=F76,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>No error values: FigureData (A1:J88)</t>
+        </is>
+      </c>
+      <c r="D77" s="3">
+        <f>SUMPRODUCT(--ISERROR(FigureData!A1:J88))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E77" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G77" t="str">
+        <f>IF(AND(ISNUMBER(D77),ISNUMBER(E77)),IF(ABS(D77-E77)&lt;=F77,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="29">
+        <f>9</f>
+        <v>9</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>No error values: WorkedExample (A1:G62)</t>
+        </is>
+      </c>
+      <c r="D78" s="3">
+        <f>SUMPRODUCT(--ISERROR(WorkedExample!A1:G62))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E78" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G78" t="str">
+        <f>IF(AND(ISNUMBER(D78),ISNUMBER(E78)),IF(ABS(D78-E78)&lt;=F78,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="29">
+        <f>10</f>
+        <v>10</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>No error values: Checks (rows 1 to 78, above this row)</t>
+        </is>
+      </c>
+      <c r="D79" s="3">
+        <f>SUMPRODUCT(--ISERROR(A1:G78))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E79" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G79" t="str">
+        <f>IF(AND(ISNUMBER(D79),ISNUMBER(E79)),IF(ABS(D79-E79)&lt;=F79,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
           <t>ALL CHECKS (invariants and error scans)</t>
         </is>
       </c>
-      <c r="D76" s="4" t="str">
-        <f>IF(AND(COUNTIF(G53:G61,"FAIL")+COUNTIF(G65:G74,"FAIL")=0,COUNTIF(G53:G61,"PASS")+COUNTIF(G65:G74,"PASS")=19),"ALL PASS","REVIEW")</f>
+      <c r="D81" s="4" t="str">
+        <f>IF(AND(COUNTIF(G58:G66,"FAIL")+COUNTIF(G70:G79,"FAIL")=0,COUNTIF(G58:G66,"PASS")+COUNTIF(G70:G79,"PASS")=19),"ALL PASS","REVIEW")</f>
         <v>ALL PASS</v>
       </c>
     </row>
-    <row r="77">
-      <c r="C77" s="2" t="inlineStr">
+    <row r="82">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Anchors matching</t>
         </is>
       </c>
-      <c r="D77" s="3">
-        <f>COUNTIF(G5:G49,"PASS")</f>
-        <v>45</v>
-      </c>
-      <c r="E77" t="str">
-        <f>"of "&amp;ROWS(G5:G49)</f>
-        <v>of 45</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+      <c r="D82" s="3">
+        <f>COUNTIF(G5:G54,"PASS")</f>
+        <v>50</v>
+      </c>
+      <c r="E82" t="str">
+        <f>"of "&amp;ROWS(G5:G54)</f>
+        <v>of 50</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Anchor tolerance = half a unit of the spec's shown precision; invariant tolerance 1e-6. Checked outside the workbook by script (spec Audit findings): every calculated cell is a formula; every spec name exists as an absolute defined name and no others; every input cell is yellow and no calculated cell is.</t>
         </is>
@@ -7377,13 +7543,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" style="7" min="1" max="1"/>
-    <col width="14" customWidth="1" style="7" min="2" max="2"/>
+    <col width="16" customWidth="1" style="7" min="2" max="2"/>
     <col width="20" customWidth="1" style="7" min="3" max="3"/>
-    <col width="16" customWidth="1" style="7" min="4" max="4"/>
+    <col width="22" customWidth="1" style="7" min="4" max="4"/>
     <col width="22" customWidth="1" style="7" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -7565,6 +7731,249 @@
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Not a forecast; the model does not rank or cost the options (spec Conventions, Condition (a)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Paper figures: the rate against Medicaid-heavy cost, the two rate rises, and the behavior and guardianship share</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1" s="7">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Fiscal year</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>July rate median</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Medicaid-heavy cost</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Gap, 1 - rate / cost (RATE_COST_GAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="B19" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2016,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2016,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2016,7,1),RATE_DATE,0)),"")</f>
+        <v>252.4</v>
+      </c>
+      <c r="C19" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2016,COST_FY,0))</f>
+        <v>344.38</v>
+      </c>
+      <c r="D19" s="26">
+        <f>IF(ISNUMBER(B19),1-B19/C19,"")</f>
+        <v>0.26708868110807826</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="B20" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2017,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2017,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2017,7,1),RATE_DATE,0)),"")</f>
+        <v>261.45</v>
+      </c>
+      <c r="C20" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2017,COST_FY,0))</f>
+        <v>356.1</v>
+      </c>
+      <c r="D20" s="26">
+        <f>IF(ISNUMBER(B20),1-B20/C20,"")</f>
+        <v>0.26579612468407754</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="B21" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2018,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2018,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2018,7,1),RATE_DATE,0)),"")</f>
+        <v>270.66</v>
+      </c>
+      <c r="C21" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2018,COST_FY,0))</f>
+        <v>365.93</v>
+      </c>
+      <c r="D21" s="26">
+        <f>IF(ISNUMBER(B21),1-B21/C21,"")</f>
+        <v>0.2603503402290055</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="str">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2019,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2019,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2019,7,1),RATE_DATE,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2019,COST_FY,0))</f>
+        <v>373.25</v>
+      </c>
+      <c r="D22" s="26" t="str">
+        <f>IF(ISNUMBER(B22),1-B22/C22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="B23" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2020,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2020,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2020,7,1),RATE_DATE,0)),"")</f>
+        <v>282.98</v>
+      </c>
+      <c r="C23" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2020,COST_FY,0))</f>
+        <v>398.33</v>
+      </c>
+      <c r="D23" s="26">
+        <f>IF(ISNUMBER(B23),1-B23/C23,"")</f>
+        <v>0.289584013255341</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="B24" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2021,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2021,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2021,7,1),RATE_DATE,0)),"")</f>
+        <v>334.75</v>
+      </c>
+      <c r="C24" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2021,COST_FY,0))</f>
+        <v>423.44</v>
+      </c>
+      <c r="D24" s="26">
+        <f>IF(ISNUMBER(B24),1-B24/C24,"")</f>
+        <v>0.20945116191195923</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="str">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2022,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2022,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2022,7,1),RATE_DATE,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2022,COST_FY,0))</f>
+        <v>435.63</v>
+      </c>
+      <c r="D25" s="26" t="str">
+        <f>IF(ISNUMBER(B25),1-B25/C25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="B26" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2023,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2023,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2023,7,1),RATE_DATE,0)),"")</f>
+        <v>371.99</v>
+      </c>
+      <c r="C26" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2023,COST_FY,0))</f>
+        <v>461.79</v>
+      </c>
+      <c r="D26" s="26">
+        <f>IF(ISNUMBER(B26),1-B26/C26,"")</f>
+        <v>0.19446068559301843</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Smallest gap, FY2016 to FY2023 (RATE_COST_GAP_MIN)</t>
+        </is>
+      </c>
+      <c r="B28" s="26">
+        <f>MIN(D19:D26)</f>
+        <v>0.19446068559301843</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Largest gap, FY2016 to FY2023 (RATE_COST_GAP_MAX)</t>
+        </is>
+      </c>
+      <c r="B29" s="26">
+        <f>MAX(D19:D26)</f>
+        <v>0.289584013255341</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Rate rise, July 2020 to July 2021 (RATE_RISE_2021)</t>
+        </is>
+      </c>
+      <c r="B31" s="20">
+        <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2021,7,1),RATE_DATE,0))/INDEX(NF_RATE_MEDIAN,MATCH(DATE(2020,7,1),RATE_DATE,0))-1</f>
+        <v>0.1829457912219945</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Rate rise, July 2023 to January 2024 (RATE_RISE_2024)</t>
+        </is>
+      </c>
+      <c r="B32" s="20">
+        <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2024,1,1),RATE_DATE,0))/INDEX(NF_RATE_MEDIAN,MATCH(DATE(2023,7,1),RATE_DATE,0))-1</f>
+        <v>0.29527675475147164</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Behavior and guardianship share, Dec 31, 2024 (BEH_GUARD_SHARE_2024)</t>
+        </is>
+      </c>
+      <c r="B34" s="20">
+        <f>INDEX(SHARE_BEHAVIOR,MATCH(2024,YEAR,0))+INDEX(SHARE_GUARDIANSHIP,MATCH(2024,YEAR,0))</f>
+        <v>0.3468208092485549</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>The gap pairs each fiscal year's cost with that July's rate memo; years with no July median in the rate series (2019, 2022) are blank. The rate median covers all homes; the cost median covers Medicaid-heavy homes.</t>
         </is>
       </c>
     </row>

--- a/capabilities/economic-research/model.xlsx
+++ b/capabilities/economic-research/model.xlsx
@@ -29,31 +29,33 @@
     <definedName name="DATE_ADJ_2021">'Inputs'!$B$13</definedName>
     <definedName name="DATE_RESET_2024">'Inputs'!$B$14</definedName>
     <definedName name="T1_MIN_DROP_PTS">'Inputs'!$B$15</definedName>
-    <definedName name="COVID_YEARS">'Inputs'!$B$16:$B$17</definedName>
-    <definedName name="YEAR">'Inputs'!$A$22:$A$29</definedName>
-    <definedName name="WL_PATIENTS">'Inputs'!$B$22:$B$29</definedName>
-    <definedName name="WL_DAYS">'Inputs'!$C$22:$C$29</definedName>
-    <definedName name="REASON_NO_BED">'Inputs'!$D$22:$D$29</definedName>
-    <definedName name="REASON_BEHAVIOR">'Inputs'!$E$22:$E$29</definedName>
-    <definedName name="REASON_SPECIAL_CARE">'Inputs'!$F$22:$F$29</definedName>
-    <definedName name="REASON_FINANCIAL">'Inputs'!$G$22:$G$29</definedName>
-    <definedName name="REASON_GUARDIANSHIP">'Inputs'!$H$22:$H$29</definedName>
-    <definedName name="REASON_PASARR">'Inputs'!$I$22:$I$29</definedName>
-    <definedName name="REASON_OTHER">'Inputs'!$J$22:$J$29</definedName>
-    <definedName name="DEC31_TOTAL">'Inputs'!$K$22:$K$29</definedName>
-    <definedName name="DEC31_NF">'Inputs'!$L$22:$L$29</definedName>
-    <definedName name="LTC_UNSTAFFED">'Inputs'!$M$22:$M$29</definedName>
-    <definedName name="WL_RATE_JAN">'Inputs'!$N$22:$N$29</definedName>
-    <definedName name="WL_RATE_JUL">'Inputs'!$O$22:$O$29</definedName>
-    <definedName name="COUNTY">'Inputs'!$A$34:$A$37</definedName>
-    <definedName name="CTY_PATIENTS">'Inputs'!$B$34:$C$37</definedName>
-    <definedName name="CTY_DAYS">'Inputs'!$D$34:$E$37</definedName>
-    <definedName name="RATE_DATE">'Inputs'!$A$41:$A$57</definedName>
-    <definedName name="NF_RATE_MEDIAN">'Inputs'!$C$41:$C$57</definedName>
-    <definedName name="COST_FY">'Inputs'!$A$61:$A$73</definedName>
-    <definedName name="NF_COST_ALL">'Inputs'!$B$61:$B$73</definedName>
-    <definedName name="NF_COST_MCD_HEAVY">'Inputs'!$C$61:$C$73</definedName>
-    <definedName name="MB_GROSS">'Inputs'!$B$78:$B$81</definedName>
+    <definedName name="ADMIT_WINDOW_DAYS">'Inputs'!$B$16</definedName>
+    <definedName name="MEDIAN_MCD_LOS">'Inputs'!$B$17</definedName>
+    <definedName name="COVID_YEARS">'Inputs'!$B$18:$B$19</definedName>
+    <definedName name="YEAR">'Inputs'!$A$24:$A$31</definedName>
+    <definedName name="WL_PATIENTS">'Inputs'!$B$24:$B$31</definedName>
+    <definedName name="WL_DAYS">'Inputs'!$C$24:$C$31</definedName>
+    <definedName name="REASON_NO_BED">'Inputs'!$D$24:$D$31</definedName>
+    <definedName name="REASON_BEHAVIOR">'Inputs'!$E$24:$E$31</definedName>
+    <definedName name="REASON_SPECIAL_CARE">'Inputs'!$F$24:$F$31</definedName>
+    <definedName name="REASON_FINANCIAL">'Inputs'!$G$24:$G$31</definedName>
+    <definedName name="REASON_GUARDIANSHIP">'Inputs'!$H$24:$H$31</definedName>
+    <definedName name="REASON_PASARR">'Inputs'!$I$24:$I$31</definedName>
+    <definedName name="REASON_OTHER">'Inputs'!$J$24:$J$31</definedName>
+    <definedName name="DEC31_TOTAL">'Inputs'!$K$24:$K$31</definedName>
+    <definedName name="DEC31_NF">'Inputs'!$L$24:$L$31</definedName>
+    <definedName name="LTC_UNSTAFFED">'Inputs'!$M$24:$M$31</definedName>
+    <definedName name="WL_RATE_JAN">'Inputs'!$N$24:$N$31</definedName>
+    <definedName name="WL_RATE_JUL">'Inputs'!$O$24:$O$31</definedName>
+    <definedName name="COUNTY">'Inputs'!$A$36:$A$39</definedName>
+    <definedName name="CTY_PATIENTS">'Inputs'!$B$36:$C$39</definedName>
+    <definedName name="CTY_DAYS">'Inputs'!$D$36:$E$39</definedName>
+    <definedName name="RATE_DATE">'Inputs'!$A$43:$A$59</definedName>
+    <definedName name="NF_RATE_MEDIAN">'Inputs'!$C$43:$C$59</definedName>
+    <definedName name="COST_FY">'Inputs'!$A$63:$A$75</definedName>
+    <definedName name="NF_COST_ALL">'Inputs'!$B$63:$B$75</definedName>
+    <definedName name="NF_COST_MCD_HEAVY">'Inputs'!$C$63:$C$75</definedName>
+    <definedName name="MB_GROSS">'Inputs'!$B$80:$B$83</definedName>
     <definedName name="DAYS_PER_PT">'Waitlist'!$B$4:$B$11</definedName>
     <definedName name="BENCH_TOTAL">'Waitlist'!$C$4:$C$11</definedName>
     <definedName name="GAP_PER_PT">'Waitlist'!$D$4:$D$11</definedName>
@@ -83,9 +85,10 @@
     <definedName name="EXCESS_COST_HI">'Cost'!$C$11:$D$11</definedName>
     <definedName name="EXCESS_COST_HI_NOW">'Cost'!$E$11</definedName>
     <definedName name="NF_SHARE_DEC31">'Cost'!$C$12:$D$12</definedName>
-    <definedName name="CEIL_PER_PT_LO">'Cost'!$E$13</definedName>
-    <definedName name="CEIL_PER_PT_HI">'Cost'!$E$14</definedName>
-    <definedName name="WL_DAYS_CHANGE_2024">'Cost'!$C$16</definedName>
+    <definedName name="DAYS_SAVED_PER_PT">'Cost'!$E$13</definedName>
+    <definedName name="CEIL_PER_PT_LO">'Cost'!$E$14</definedName>
+    <definedName name="CEIL_PER_PT_HI">'Cost'!$E$15</definedName>
+    <definedName name="WL_DAYS_CHANGE_2024">'Cost'!$C$17</definedName>
     <definedName name="T1_DROP_2021">'Tests'!$B$6</definedName>
     <definedName name="T1_PASS_2021">'Tests'!$B$7</definedName>
     <definedName name="T1_DROP_2024">'Tests'!$B$10</definedName>
@@ -108,6 +111,13 @@
     <definedName name="RATE_FWD">'Conditions'!$D$7:$D$8</definedName>
     <definedName name="COND_A_GAP">'Conditions'!$E$7:$E$8</definedName>
     <definedName name="RATE_GROWTH_2024_2026">'Conditions'!$B$10</definedName>
+    <definedName name="STAY_SHORTFALL">'Conditions'!$B$11</definedName>
+    <definedName name="RATE_COST_GAP">'Conditions'!$D$19:$D$26</definedName>
+    <definedName name="RATE_COST_GAP_MIN">'Conditions'!$B$28</definedName>
+    <definedName name="RATE_COST_GAP_MAX">'Conditions'!$B$29</definedName>
+    <definedName name="RATE_RISE_2021">'Conditions'!$B$31</definedName>
+    <definedName name="RATE_RISE_2024">'Conditions'!$B$32</definedName>
+    <definedName name="BEH_GUARD_SHARE_2024">'Conditions'!$B$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -200,6 +210,7 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,12 +226,11 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -595,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R82"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="7" min="1" max="1"/>
@@ -632,12 +642,12 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>COUNT(R6:R17,R22:R29,R34:R37,R41:R57,R61:R73,R78:R81)</f>
+        <f>COUNT(R6:R19,R24:R31,R36:R39,R43:R59,R63:R75,R80:R83)</f>
         <v>57</v>
       </c>
       <c r="C2" t="str">
-        <f>"of "&amp;(ROWS(R6:R17)+ROWS(R22:R29)+ROWS(R34:R37)+ROWS(R41:R57)+ROWS(R61:R73)+ROWS(R78:R81))</f>
-        <v>of 58</v>
+        <f>"of "&amp;(ROWS(R6:R19)+ROWS(R24:R31)+ROWS(R36:R39)+ROWS(R43:R59)+ROWS(R63:R75)+ROWS(R80:R83))</f>
+        <v>of 60</v>
       </c>
     </row>
     <row r="3"/>
@@ -1018,378 +1028,322 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>COVID_YEARS</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>2020</v>
+          <t>ADMIT_WINDOW_DAYS</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Brief</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>Brief line 79</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R16" s="31" t="n">
-        <v>46294</v>
-      </c>
+          <t>My judgment (2026-10-01): the time within which a home giving the guarantee must admit. Set equal to the benchmark</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="34" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>MEDIAN_MCD_LOS</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>542.83</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CMS SNF cost reports, FY2023 file, "SNF Average Length of Stay Title XIX", each Hawaii home's latest report: median of the 31 homes reporting a value (range 8.26 to 1,680.75). Rounded to 543 in the paper</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="34" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>COVID_YEARS</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Brief</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>Brief line 79</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R18" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>(COVID_YEARS, 2nd)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>2021</v>
       </c>
-      <c r="P17" s="8" t="inlineStr">
+      <c r="P19" s="8" t="inlineStr">
         <is>
           <t>Brief line 79</t>
         </is>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="Q19" s="8" t="inlineStr">
         <is>
           <t>MK</t>
         </is>
       </c>
-      <c r="R17" s="31" t="n">
+      <c r="R19" s="31" t="n">
         <v>46294</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Year table (SHPDA Table 18 statewide; Table 16 statewide; Med-QUEST waitlisted rates)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1" s="7">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="22" ht="32" customHeight="1" s="7">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>WL_PATIENTS</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>WL_DAYS</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>REASON_NO_BED</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>REASON_BEHAVIOR</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>REASON_SPECIAL_CARE</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>REASON_FINANCIAL</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>REASON_GUARDIANSHIP</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>REASON_PASARR</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>REASON_OTHER</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>DEC31_TOTAL</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>DEC31_NF</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>LTC_UNSTAFFED</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>WL_RATE_JAN</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>WL_RATE_JUL</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="inlineStr">
+      <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R20" s="5" t="inlineStr">
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" s="7">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23" ht="30" customHeight="1" s="7">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>T18 total</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>T18 total</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>T18 reason F</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>T18 reason G</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>T18 reason H</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>T18 reason I</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>T18 reason J</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>T18 reason K</t>
         </is>
       </c>
-      <c r="J21" s="13" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>T18 reason L</t>
         </is>
       </c>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>T18 by level of care</t>
         </is>
       </c>
-      <c r="L21" s="13" t="inlineStr">
+      <c r="L23" s="14" t="inlineStr">
         <is>
           <t>T18 type A</t>
         </is>
       </c>
-      <c r="M21" s="13" t="inlineStr">
+      <c r="M23" s="14" t="inlineStr">
         <is>
           <t>T16 statewide</t>
         </is>
       </c>
-      <c r="N21" s="13" t="inlineStr">
+      <c r="N23" s="14" t="inlineStr">
         <is>
           <t>QI-2225, QI-2342</t>
         </is>
       </c>
-      <c r="O21" s="13" t="inlineStr">
+      <c r="O23" s="14" t="inlineStr">
         <is>
           <t>QI-2326, QI-2413</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="n">
+    <row r="24">
+      <c r="A24" s="15" t="n">
         <v>2017</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B24" s="6" t="n">
         <v>6187</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C24" s="6" t="n">
         <v>61470</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D24" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E24" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F24" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G24" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H24" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>157</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M24" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="P24" s="8" t="inlineStr">
         <is>
           <t>T18 2017 p. 72; T16 2017 p. 69</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R22" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>5294</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>66091</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>171</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>160</v>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>T18 2018 p. 82; T16 p. 79</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R23" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>4790</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>78911</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>184</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>248</v>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>T18 2019 p. 82; T16 p. 79</t>
         </is>
       </c>
       <c r="Q24" s="8" t="inlineStr">
@@ -1402,45 +1356,45 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
-        <v>2020</v>
+      <c r="A25" s="15" t="n">
+        <v>2018</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>4553</v>
+        <v>5294</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>57297</v>
+        <v>66091</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>462</v>
+        <v>160</v>
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>T18 2020 p. 85; T16 p. 81</t>
+          <t>T18 2018 p. 82; T16 p. 79</t>
         </is>
       </c>
       <c r="Q25" s="8" t="inlineStr">
@@ -1453,45 +1407,45 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="n">
-        <v>2021</v>
+      <c r="A26" s="15" t="n">
+        <v>2019</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>4927</v>
+        <v>4790</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>60050</v>
+        <v>78911</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>614</v>
+        <v>248</v>
       </c>
       <c r="P26" s="8" t="inlineStr">
         <is>
-          <t>T18 2021 p. 87; T16 p. 83</t>
+          <t>T18 2019 p. 82; T16 p. 79</t>
         </is>
       </c>
       <c r="Q26" s="8" t="inlineStr">
@@ -1504,45 +1458,45 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="n">
-        <v>2022</v>
+      <c r="A27" s="15" t="n">
+        <v>2020</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>3681</v>
+        <v>4553</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>78561</v>
+        <v>57297</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>661</v>
+        <v>462</v>
       </c>
       <c r="P27" s="8" t="inlineStr">
         <is>
-          <t>T18 2022 p. 86; T16 p. 82</t>
+          <t>T18 2020 p. 85; T16 p. 81</t>
         </is>
       </c>
       <c r="Q27" s="8" t="inlineStr">
@@ -1555,54 +1509,45 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="n">
-        <v>2023</v>
+      <c r="A28" s="15" t="n">
+        <v>2021</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3610</v>
+        <v>4927</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>83097</v>
+        <v>60050</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>191</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="N28" s="33" t="n">
-        <v>283.6</v>
-      </c>
-      <c r="O28" s="33" t="n">
-        <v>302.89</v>
+        <v>614</v>
       </c>
       <c r="P28" s="8" t="inlineStr">
         <is>
-          <t>T18 2023 p. 86; T16 p. 82; QI-2225 p. 2; QI-2326 p. 2</t>
+          <t>T18 2021 p. 87; T16 p. 83</t>
         </is>
       </c>
       <c r="Q28" s="8" t="inlineStr">
@@ -1615,54 +1560,45 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="n">
-        <v>2024</v>
+      <c r="A29" s="15" t="n">
+        <v>2022</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3123</v>
+        <v>3681</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>60876</v>
+        <v>78561</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E29" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="H29" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="F29" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>31</v>
-      </c>
       <c r="I29" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>173</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>548</v>
-      </c>
-      <c r="N29" s="33" t="n">
-        <v>464.97</v>
-      </c>
-      <c r="O29" s="33" t="n">
-        <v>455.59</v>
+        <v>661</v>
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>T18 2024 p. 86; T16 p. 82; QI-2342 p. 2; QI-2413 p. 2</t>
+          <t>T18 2022 p. 86; T16 p. 82</t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
@@ -1675,143 +1611,199 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3610</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>83097</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="N30" s="33" t="n">
+        <v>283.6</v>
+      </c>
+      <c r="O30" s="33" t="n">
+        <v>302.89</v>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>T18 2023 p. 86; T16 p. 82; QI-2225 p. 2; QI-2326 p. 2</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R30" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>3123</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>60876</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>548</v>
+      </c>
+      <c r="N31" s="33" t="n">
+        <v>464.97</v>
+      </c>
+      <c r="O31" s="33" t="n">
+        <v>455.59</v>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>T18 2024 p. 86; T16 p. 82; QI-2342 p. 2; QI-2413 p. 2</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R31" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Reason columns F to L; 2017 reasons sum to 120 against 157 by level of care (Maui Memorial records reasons for 6 of 47 patients; Queen's Punchbowl's reasons sum to 43 against 39). DEC31_NF and the waitlisted rates exist for 2023 and 2024 only (blank, not inputs, in other years).</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>County table (Table 18 hospital rows summed by county, shpda-table18-by-hospital-2023-2024.csv)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1" s="7">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="35" ht="32" customHeight="1" s="7">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>COUNTY</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>CTY_PATIENTS 2023</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>CTY_PATIENTS 2024</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>CTY_DAYS 2023</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>CTY_DAYS 2024</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="P35" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="inlineStr">
+      <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R33" s="5" t="inlineStr">
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>869</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>727</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>23212</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>20174</v>
-      </c>
-      <c r="P34" s="8" t="inlineStr">
-        <is>
-          <t>T18 2023 and 2024, pp. 85-86 (hospital rows summed; county totals)</t>
-        </is>
-      </c>
-      <c r="Q34" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R34" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Honolulu</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n">
-        <v>2255</v>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>1979</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>40327</v>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>27380</v>
-      </c>
-      <c r="P35" s="8" t="inlineStr">
-        <is>
-          <t>T18 2023 and 2024, pp. 85-86 (hospital rows summed; county totals)</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R35" s="31" t="n">
-        <v>46294</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Kauai</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>86</v>
+        <v>869</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>64</v>
+        <v>727</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1720</v>
+        <v>23212</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1927</v>
+        <v>20174</v>
       </c>
       <c r="P36" s="8" t="inlineStr">
         <is>
@@ -1830,20 +1822,20 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Maui</t>
+          <t>Honolulu</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>400</v>
+        <v>2255</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>353</v>
+        <v>1979</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>17838</v>
+        <v>40327</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>11395</v>
+        <v>27380</v>
       </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
@@ -1859,113 +1851,125 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="38"/>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>1720</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>1927</v>
+      </c>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>T18 2023 and 2024, pp. 85-86 (hospital rows summed; county totals)</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R38" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>353</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>17838</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>11395</v>
+      </c>
+      <c r="P39" s="8" t="inlineStr">
+        <is>
+          <t>T18 2023 and 2024, pp. 85-86 (hospital rows summed; county totals)</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R39" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Median nursing-facility rate by memo (Med-QUEST memos, hi-medicaid-rate-series-2016-2026.csv)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1" s="7">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="42" ht="32" customHeight="1" s="7">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>RATE_DATE (effective month)</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Memo</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>NF_RATE_MEDIAN</t>
         </is>
       </c>
-      <c r="P40" s="5" t="inlineStr">
+      <c r="P42" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q40" s="5" t="inlineStr">
+      <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R40" s="5" t="inlineStr">
+      <c r="R42" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="16" t="n">
+    <row r="43">
+      <c r="A43" s="17" t="n">
         <v>42370</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>QI-1521</t>
         </is>
       </c>
-      <c r="C41" s="33" t="n">
+      <c r="C43" s="33" t="n">
         <v>246.97</v>
       </c>
-      <c r="P41" s="8" t="inlineStr">
+      <c r="P43" s="8" t="inlineStr">
         <is>
           <t>QI-1521 p. 2</t>
-        </is>
-      </c>
-      <c r="Q41" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R41" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="n">
-        <v>42552</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>QI-1607</t>
-        </is>
-      </c>
-      <c r="C42" s="33" t="n">
-        <v>252.4</v>
-      </c>
-      <c r="P42" s="8" t="inlineStr">
-        <is>
-          <t>QI-1607 p. 5</t>
-        </is>
-      </c>
-      <c r="Q42" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R42" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="n">
-        <v>42736</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>QI-1622</t>
-        </is>
-      </c>
-      <c r="C43" s="33" t="n">
-        <v>251.93</v>
-      </c>
-      <c r="P43" s="8" t="inlineStr">
-        <is>
-          <t>QI-1622 p. 2</t>
         </is>
       </c>
       <c r="Q43" s="8" t="inlineStr">
@@ -1978,20 +1982,20 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n">
-        <v>42917</v>
+      <c r="A44" s="17" t="n">
+        <v>42552</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>QI-1710</t>
+          <t>QI-1607</t>
         </is>
       </c>
       <c r="C44" s="33" t="n">
-        <v>261.45</v>
+        <v>252.4</v>
       </c>
       <c r="P44" s="8" t="inlineStr">
         <is>
-          <t>QI-1710 p. 8</t>
+          <t>QI-1607 p. 5</t>
         </is>
       </c>
       <c r="Q44" s="8" t="inlineStr">
@@ -2004,20 +2008,20 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n">
-        <v>43282</v>
+      <c r="A45" s="17" t="n">
+        <v>42736</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>QI-1809</t>
+          <t>QI-1622</t>
         </is>
       </c>
       <c r="C45" s="33" t="n">
-        <v>270.66</v>
+        <v>251.93</v>
       </c>
       <c r="P45" s="8" t="inlineStr">
         <is>
-          <t>QI-1809 p. 9</t>
+          <t>QI-1622 p. 2</t>
         </is>
       </c>
       <c r="Q45" s="8" t="inlineStr">
@@ -2030,20 +2034,20 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n">
-        <v>43466</v>
+      <c r="A46" s="17" t="n">
+        <v>42917</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>QI-1820</t>
+          <t>QI-1710</t>
         </is>
       </c>
       <c r="C46" s="33" t="n">
-        <v>270.15</v>
+        <v>261.45</v>
       </c>
       <c r="P46" s="8" t="inlineStr">
         <is>
-          <t>QI-1820 p. 5</t>
+          <t>QI-1710 p. 8</t>
         </is>
       </c>
       <c r="Q46" s="8" t="inlineStr">
@@ -2056,23 +2060,20 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n">
-        <v>43647</v>
+      <c r="A47" s="17" t="n">
+        <v>43282</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>QI-1911B</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>Left blank: QI-1911B, the controlling July 2019 memo, lists but omits its acuity rate table</t>
-        </is>
+          <t>QI-1809</t>
+        </is>
+      </c>
+      <c r="C47" s="33" t="n">
+        <v>270.66</v>
       </c>
       <c r="P47" s="8" t="inlineStr">
         <is>
-          <t>Blank by decision: QI-1911B omits Att. H</t>
+          <t>QI-1809 p. 9</t>
         </is>
       </c>
       <c r="Q47" s="8" t="inlineStr">
@@ -2080,23 +2081,25 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="R47" s="34" t="n"/>
+      <c r="R47" s="31" t="n">
+        <v>46294</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n">
-        <v>44013</v>
+      <c r="A48" s="17" t="n">
+        <v>43466</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>QI-2022</t>
+          <t>QI-1820</t>
         </is>
       </c>
       <c r="C48" s="33" t="n">
-        <v>282.98</v>
+        <v>270.15</v>
       </c>
       <c r="P48" s="8" t="inlineStr">
         <is>
-          <t>QI-2022 p. 11</t>
+          <t>QI-1820 p. 5</t>
         </is>
       </c>
       <c r="Q48" s="8" t="inlineStr">
@@ -2109,20 +2112,23 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n">
-        <v>44378</v>
+      <c r="A49" s="17" t="n">
+        <v>43647</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>QI-2113B</t>
-        </is>
-      </c>
-      <c r="C49" s="33" t="n">
-        <v>334.75</v>
+          <t>QI-1911B</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Left blank: QI-1911B, the controlling July 2019 memo, lists but omits its acuity rate table</t>
+        </is>
       </c>
       <c r="P49" s="8" t="inlineStr">
         <is>
-          <t>QI-2113B p. 11</t>
+          <t>Blank by decision: QI-1911B omits Att. H</t>
         </is>
       </c>
       <c r="Q49" s="8" t="inlineStr">
@@ -2130,25 +2136,23 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="R49" s="31" t="n">
-        <v>46294</v>
-      </c>
+      <c r="R49" s="34" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n">
-        <v>44562</v>
+      <c r="A50" s="17" t="n">
+        <v>44013</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>QI-2166</t>
+          <t>QI-2022</t>
         </is>
       </c>
       <c r="C50" s="33" t="n">
-        <v>332.59</v>
+        <v>282.98</v>
       </c>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>QI-2166 p. 7</t>
+          <t>QI-2022 p. 11</t>
         </is>
       </c>
       <c r="Q50" s="8" t="inlineStr">
@@ -2161,20 +2165,20 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n">
-        <v>44927</v>
+      <c r="A51" s="17" t="n">
+        <v>44378</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>QI-2225</t>
+          <t>QI-2113B</t>
         </is>
       </c>
       <c r="C51" s="33" t="n">
-        <v>355.11</v>
+        <v>334.75</v>
       </c>
       <c r="P51" s="8" t="inlineStr">
         <is>
-          <t>QI-2225 p. 3</t>
+          <t>QI-2113B p. 11</t>
         </is>
       </c>
       <c r="Q51" s="8" t="inlineStr">
@@ -2187,20 +2191,20 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n">
-        <v>45108</v>
+      <c r="A52" s="17" t="n">
+        <v>44562</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>QI-2326</t>
+          <t>QI-2166</t>
         </is>
       </c>
       <c r="C52" s="33" t="n">
-        <v>371.99</v>
+        <v>332.59</v>
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>QI-2326 p. 3</t>
+          <t>QI-2166 p. 7</t>
         </is>
       </c>
       <c r="Q52" s="8" t="inlineStr">
@@ -2213,20 +2217,20 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n">
-        <v>45292</v>
+      <c r="A53" s="17" t="n">
+        <v>44927</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>QI-2342</t>
+          <t>QI-2225</t>
         </is>
       </c>
       <c r="C53" s="33" t="n">
-        <v>481.83</v>
+        <v>355.11</v>
       </c>
       <c r="P53" s="8" t="inlineStr">
         <is>
-          <t>QI-2342 p. 3</t>
+          <t>QI-2225 p. 3</t>
         </is>
       </c>
       <c r="Q53" s="8" t="inlineStr">
@@ -2239,20 +2243,20 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n">
-        <v>45474</v>
+      <c r="A54" s="17" t="n">
+        <v>45108</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>QI-2413</t>
+          <t>QI-2326</t>
         </is>
       </c>
       <c r="C54" s="33" t="n">
-        <v>482.2</v>
+        <v>371.99</v>
       </c>
       <c r="P54" s="8" t="inlineStr">
         <is>
-          <t>QI-2413 p. 3</t>
+          <t>QI-2326 p. 3</t>
         </is>
       </c>
       <c r="Q54" s="8" t="inlineStr">
@@ -2265,20 +2269,20 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n">
-        <v>45658</v>
+      <c r="A55" s="17" t="n">
+        <v>45292</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>QI-2427</t>
+          <t>QI-2342</t>
         </is>
       </c>
       <c r="C55" s="33" t="n">
-        <v>509.69</v>
+        <v>481.83</v>
       </c>
       <c r="P55" s="8" t="inlineStr">
         <is>
-          <t>QI-2427 p. 3</t>
+          <t>QI-2342 p. 3</t>
         </is>
       </c>
       <c r="Q55" s="8" t="inlineStr">
@@ -2291,20 +2295,20 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n">
-        <v>45839</v>
+      <c r="A56" s="17" t="n">
+        <v>45474</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>QI-2515</t>
+          <t>QI-2413</t>
         </is>
       </c>
       <c r="C56" s="33" t="n">
-        <v>506.65</v>
+        <v>482.2</v>
       </c>
       <c r="P56" s="8" t="inlineStr">
         <is>
-          <t>QI-2515 p. 3</t>
+          <t>QI-2413 p. 3</t>
         </is>
       </c>
       <c r="Q56" s="8" t="inlineStr">
@@ -2317,20 +2321,20 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n">
-        <v>46023</v>
+      <c r="A57" s="17" t="n">
+        <v>45658</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>QI-2532</t>
+          <t>QI-2427</t>
         </is>
       </c>
       <c r="C57" s="33" t="n">
-        <v>495.26</v>
+        <v>509.69</v>
       </c>
       <c r="P57" s="8" t="inlineStr">
         <is>
-          <t>QI-2532 p. 3 (median 495.255, rounded half up)</t>
+          <t>QI-2427 p. 3</t>
         </is>
       </c>
       <c r="Q57" s="8" t="inlineStr">
@@ -2342,103 +2346,107 @@
         <v>46294</v>
       </c>
     </row>
-    <row r="58"/>
+    <row r="58">
+      <c r="A58" s="17" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>QI-2515</t>
+        </is>
+      </c>
+      <c r="C58" s="33" t="n">
+        <v>506.65</v>
+      </c>
+      <c r="P58" s="8" t="inlineStr">
+        <is>
+          <t>QI-2515 p. 3</t>
+        </is>
+      </c>
+      <c r="Q58" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R58" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="17" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>QI-2532</t>
+        </is>
+      </c>
+      <c r="C59" s="33" t="n">
+        <v>495.26</v>
+      </c>
+      <c r="P59" s="8" t="inlineStr">
+        <is>
+          <t>QI-2532 p. 3 (median 495.255, rounded half up)</t>
+        </is>
+      </c>
+      <c r="Q59" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R59" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Median nursing-home cost per patient day (CMS SNF cost reports, hi-snf-cost-per-day-series-2011-2023.csv)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="32" customHeight="1" s="7">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="62" ht="32" customHeight="1" s="7">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>COST_FY</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>NF_COST_ALL</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>NF_COST_MCD_HEAVY</t>
         </is>
       </c>
-      <c r="P60" s="5" t="inlineStr">
+      <c r="P62" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q60" s="5" t="inlineStr">
+      <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R60" s="5" t="inlineStr">
+      <c r="R62" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="14" t="n">
+    <row r="63">
+      <c r="A63" s="15" t="n">
         <v>2011</v>
       </c>
-      <c r="B61" s="33" t="n">
+      <c r="B63" s="33" t="n">
         <v>295.13</v>
       </c>
-      <c r="C61" s="33" t="n">
+      <c r="C63" s="33" t="n">
         <v>287.76</v>
-      </c>
-      <c r="P61" s="8" t="inlineStr">
-        <is>
-          <t>CMS SNF cost report FY20xx (data.cms.gov), Worksheet A; median re-derived</t>
-        </is>
-      </c>
-      <c r="Q61" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R61" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B62" s="33" t="n">
-        <v>314.68</v>
-      </c>
-      <c r="C62" s="33" t="n">
-        <v>311.89</v>
-      </c>
-      <c r="P62" s="8" t="inlineStr">
-        <is>
-          <t>CMS SNF cost report FY20xx (data.cms.gov), Worksheet A; median re-derived</t>
-        </is>
-      </c>
-      <c r="Q62" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R62" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="14" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B63" s="33" t="n">
-        <v>342.42</v>
-      </c>
-      <c r="C63" s="33" t="n">
-        <v>322.2</v>
       </c>
       <c r="P63" s="8" t="inlineStr">
         <is>
@@ -2455,14 +2463,14 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14" t="n">
-        <v>2014</v>
+      <c r="A64" s="15" t="n">
+        <v>2012</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>344.19</v>
+        <v>314.68</v>
       </c>
       <c r="C64" s="33" t="n">
-        <v>322.2</v>
+        <v>311.89</v>
       </c>
       <c r="P64" s="8" t="inlineStr">
         <is>
@@ -2479,14 +2487,14 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="n">
-        <v>2015</v>
+      <c r="A65" s="15" t="n">
+        <v>2013</v>
       </c>
       <c r="B65" s="33" t="n">
-        <v>340.9</v>
+        <v>342.42</v>
       </c>
       <c r="C65" s="33" t="n">
-        <v>322.1</v>
+        <v>322.2</v>
       </c>
       <c r="P65" s="8" t="inlineStr">
         <is>
@@ -2503,14 +2511,14 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="n">
-        <v>2016</v>
+      <c r="A66" s="15" t="n">
+        <v>2014</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>358.8</v>
+        <v>344.19</v>
       </c>
       <c r="C66" s="33" t="n">
-        <v>344.38</v>
+        <v>322.2</v>
       </c>
       <c r="P66" s="8" t="inlineStr">
         <is>
@@ -2527,14 +2535,14 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="n">
-        <v>2017</v>
+      <c r="A67" s="15" t="n">
+        <v>2015</v>
       </c>
       <c r="B67" s="33" t="n">
-        <v>376.01</v>
+        <v>340.9</v>
       </c>
       <c r="C67" s="33" t="n">
-        <v>356.1</v>
+        <v>322.1</v>
       </c>
       <c r="P67" s="8" t="inlineStr">
         <is>
@@ -2551,14 +2559,14 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="14" t="n">
-        <v>2018</v>
+      <c r="A68" s="15" t="n">
+        <v>2016</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>380.99</v>
+        <v>358.8</v>
       </c>
       <c r="C68" s="33" t="n">
-        <v>365.93</v>
+        <v>344.38</v>
       </c>
       <c r="P68" s="8" t="inlineStr">
         <is>
@@ -2575,14 +2583,14 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="14" t="n">
-        <v>2019</v>
+      <c r="A69" s="15" t="n">
+        <v>2017</v>
       </c>
       <c r="B69" s="33" t="n">
-        <v>379.87</v>
+        <v>376.01</v>
       </c>
       <c r="C69" s="33" t="n">
-        <v>373.25</v>
+        <v>356.1</v>
       </c>
       <c r="P69" s="8" t="inlineStr">
         <is>
@@ -2599,14 +2607,14 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="14" t="n">
-        <v>2020</v>
+      <c r="A70" s="15" t="n">
+        <v>2018</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>428.4</v>
+        <v>380.99</v>
       </c>
       <c r="C70" s="33" t="n">
-        <v>398.33</v>
+        <v>365.93</v>
       </c>
       <c r="P70" s="8" t="inlineStr">
         <is>
@@ -2623,14 +2631,14 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="14" t="n">
-        <v>2021</v>
+      <c r="A71" s="15" t="n">
+        <v>2019</v>
       </c>
       <c r="B71" s="33" t="n">
-        <v>450.4</v>
+        <v>379.87</v>
       </c>
       <c r="C71" s="33" t="n">
-        <v>423.44</v>
+        <v>373.25</v>
       </c>
       <c r="P71" s="8" t="inlineStr">
         <is>
@@ -2647,14 +2655,14 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="14" t="n">
-        <v>2022</v>
+      <c r="A72" s="15" t="n">
+        <v>2020</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>459.47</v>
+        <v>428.4</v>
       </c>
       <c r="C72" s="33" t="n">
-        <v>435.63</v>
+        <v>398.33</v>
       </c>
       <c r="P72" s="8" t="inlineStr">
         <is>
@@ -2671,14 +2679,14 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="14" t="n">
-        <v>2023</v>
+      <c r="A73" s="15" t="n">
+        <v>2021</v>
       </c>
       <c r="B73" s="33" t="n">
-        <v>519.16</v>
+        <v>450.4</v>
       </c>
       <c r="C73" s="33" t="n">
-        <v>461.79</v>
+        <v>423.44</v>
       </c>
       <c r="P73" s="8" t="inlineStr">
         <is>
@@ -2695,119 +2703,115 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="15" t="inlineStr">
+      <c r="A74" s="15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B74" s="33" t="n">
+        <v>459.47</v>
+      </c>
+      <c r="C74" s="33" t="n">
+        <v>435.63</v>
+      </c>
+      <c r="P74" s="8" t="inlineStr">
+        <is>
+          <t>CMS SNF cost report FY20xx (data.cms.gov), Worksheet A; median re-derived</t>
+        </is>
+      </c>
+      <c r="Q74" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R74" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B75" s="33" t="n">
+        <v>519.16</v>
+      </c>
+      <c r="C75" s="33" t="n">
+        <v>461.79</v>
+      </c>
+      <c r="P75" s="8" t="inlineStr">
+        <is>
+          <t>CMS SNF cost report FY20xx (data.cms.gov), Worksheet A; median re-derived</t>
+        </is>
+      </c>
+      <c r="Q75" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R75" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>Medicaid-heavy = Medicaid (Title XIX) days at least 50% of total days, excluding complex-care Kulana Malama (CCN 125057) and Islands Skilled Nursing and Rehab (CCN 125067). All facilities = every Hawaii facility in the file. Medians on unrounded values, half up to the cent.</t>
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Market basket for condition (a) (CMS SNF PPS final rules, FY2024 to FY2027)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Fiscal year</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>MB_GROSS</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="P77" s="5" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="Q77" s="5" t="inlineStr">
+      <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="R77" s="5" t="inlineStr">
+      <c r="R79" s="5" t="inlineStr">
         <is>
           <t>Date verified</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="14" t="n">
+    <row r="80">
+      <c r="A80" s="15" t="n">
         <v>2024</v>
       </c>
-      <c r="B78" s="17" t="n">
+      <c r="B80" s="18" t="n">
         <v>0.03</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>CMS SNF PPS final rule FY2024: market basket before the forecast-error and productivity adjustments</t>
         </is>
       </c>
-      <c r="P78" s="8" t="inlineStr">
+      <c r="P80" s="8" t="inlineStr">
         <is>
           <t>CMS-1779-F fact sheet (FY2024)</t>
-        </is>
-      </c>
-      <c r="Q78" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R78" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B79" s="17" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>CMS SNF PPS final rule FY2025: market basket before the forecast-error and productivity adjustments</t>
-        </is>
-      </c>
-      <c r="P79" s="8" t="inlineStr">
-        <is>
-          <t>CMS-1802-F fact sheet (FY2025)</t>
-        </is>
-      </c>
-      <c r="Q79" s="8" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="R79" s="31" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B80" s="17" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>CMS SNF PPS final rule FY2026: market basket before the forecast-error and productivity adjustments</t>
-        </is>
-      </c>
-      <c r="P80" s="8" t="inlineStr">
-        <is>
-          <t>CMS-1827-F fact sheet (FY2026)</t>
         </is>
       </c>
       <c r="Q80" s="8" t="inlineStr">
@@ -2820,20 +2824,20 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="14" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B81" s="17" t="n">
-        <v>0.033</v>
+      <c r="A81" s="15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B81" s="18" t="n">
+        <v>0.03</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CMS SNF PPS final rule FY2027: market basket before the forecast-error and productivity adjustments</t>
+          <t>CMS SNF PPS final rule FY2025: market basket before the forecast-error and productivity adjustments</t>
         </is>
       </c>
       <c r="P81" s="8" t="inlineStr">
         <is>
-          <t>CMS-1843-F fact sheet (FY2027)</t>
+          <t>CMS-1802-F fact sheet (FY2025)</t>
         </is>
       </c>
       <c r="Q81" s="8" t="inlineStr">
@@ -2846,7 +2850,59 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="15" t="inlineStr">
+      <c r="A82" s="15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B82" s="18" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CMS SNF PPS final rule FY2026: market basket before the forecast-error and productivity adjustments</t>
+        </is>
+      </c>
+      <c r="P82" s="8" t="inlineStr">
+        <is>
+          <t>CMS-1827-F fact sheet (FY2026)</t>
+        </is>
+      </c>
+      <c r="Q82" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R82" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B83" s="18" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CMS SNF PPS final rule FY2027: market basket before the forecast-error and productivity adjustments</t>
+        </is>
+      </c>
+      <c r="P83" s="8" t="inlineStr">
+        <is>
+          <t>CMS-1843-F fact sheet (FY2027)</t>
+        </is>
+      </c>
+      <c r="Q83" s="8" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="R83" s="31" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>CMS SNF PPS final rule fact sheets, FY2024 to FY2027. A national Medicare index standing in for Hawaii nursing-home cost growth.</t>
         </is>
@@ -2863,7 +2919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="7" min="1" max="1"/>
@@ -3069,11 +3125,11 @@
           <t>EXCESS_BEDS(2023) (365 days)</t>
         </is>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>INDEX(EXCESS_BEDS,MATCH(2023,YEAR,0))</f>
         <v>89.1972602739726</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>89.2</f>
         <v>89.2</v>
       </c>
@@ -3101,11 +3157,11 @@
           <t>EXCESS_BEDS(2024) (366 days)</t>
         </is>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>INDEX(EXCESS_BEDS,MATCH(2024,YEAR,0))</f>
         <v>46.868852459016395</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>46.9</f>
         <v>46.9</v>
       </c>
@@ -3482,16 +3538,16 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CEIL_PER_PT_LO</t>
-        </is>
-      </c>
-      <c r="D22" s="35">
-        <f>CEIL_PER_PT_LO</f>
-        <v>1232.7243804034586</v>
-      </c>
-      <c r="E22" s="35">
-        <f>1232.72</f>
-        <v>1232.72</v>
+          <t>DAYS_SAVED_PER_PT</t>
+        </is>
+      </c>
+      <c r="D22" s="24">
+        <f>DAYS_SAVED_PER_PT</f>
+        <v>5.492795389048993</v>
+      </c>
+      <c r="E22" s="24">
+        <f>5.49</f>
+        <v>5.49</v>
       </c>
       <c r="F22">
         <f>0.005</f>
@@ -3514,16 +3570,16 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CEIL_PER_PT_HI</t>
+          <t>CEIL_PER_PT_LO</t>
         </is>
       </c>
       <c r="D23" s="35">
-        <f>CEIL_PER_PT_HI</f>
-        <v>19166.096138328532</v>
+        <f>CEIL_PER_PT_LO</f>
+        <v>347.36438040345837</v>
       </c>
       <c r="E23" s="35">
-        <f>19166.10</f>
-        <v>19166.1</v>
+        <f>347.36</f>
+        <v>347.36</v>
       </c>
       <c r="F23">
         <f>0.005</f>
@@ -3546,20 +3602,20 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>WL_DAYS_CHANGE_2024</t>
-        </is>
-      </c>
-      <c r="D24" s="19">
-        <f>WL_DAYS_CHANGE_2024</f>
-        <v>-0.26741037582584204</v>
-      </c>
-      <c r="E24" s="19">
-        <f>-0.267</f>
-        <v>-0.267</v>
+          <t>CEIL_PER_PT_HI</t>
+        </is>
+      </c>
+      <c r="D24" s="35">
+        <f>CEIL_PER_PT_HI</f>
+        <v>5400.736138328532</v>
+      </c>
+      <c r="E24" s="35">
+        <f>5400.74</f>
+        <v>5400.74</v>
       </c>
       <c r="F24">
-        <f>0.0005</f>
-        <v>0.0005</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G24" t="str">
         <f>IF(AND(ISNUMBER(D24),ISNUMBER(E24)),IF(ABS(D24-E24)&lt;=F24,"PASS","FAIL"),"FAIL")</f>
@@ -3578,20 +3634,20 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>T1_DROP_2021 (points)</t>
-        </is>
-      </c>
-      <c r="D25" s="24">
-        <f>T1_DROP_2021*100</f>
-        <v>-1.917989417989416</v>
-      </c>
-      <c r="E25" s="24">
-        <f>-1.92</f>
-        <v>-1.92</v>
+          <t>WL_DAYS_CHANGE_2024</t>
+        </is>
+      </c>
+      <c r="D25" s="20">
+        <f>WL_DAYS_CHANGE_2024</f>
+        <v>-0.26741037582584204</v>
+      </c>
+      <c r="E25" s="20">
+        <f>-0.267</f>
+        <v>-0.267</v>
       </c>
       <c r="F25">
-        <f>0.005</f>
-        <v>0.005</v>
+        <f>0.0005</f>
+        <v>0.0005</v>
       </c>
       <c r="G25" t="str">
         <f>IF(AND(ISNUMBER(D25),ISNUMBER(E25)),IF(ABS(D25-E25)&lt;=F25,"PASS","FAIL"),"FAIL")</f>
@@ -3610,16 +3666,16 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>T1_DROP_2024 (points)</t>
+          <t>T1_DROP_2021 (points)</t>
         </is>
       </c>
       <c r="D26" s="24">
-        <f>T1_DROP_2024*100</f>
-        <v>-11.121871500771721</v>
+        <f>T1_DROP_2021*100</f>
+        <v>-1.917989417989416</v>
       </c>
       <c r="E26" s="24">
-        <f>-11.12</f>
-        <v>-11.12</v>
+        <f>-1.92</f>
+        <v>-1.92</v>
       </c>
       <c r="F26">
         <f>0.005</f>
@@ -3642,16 +3698,16 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>T2_SLOPE (about)</t>
+          <t>T1_DROP_2024 (points)</t>
         </is>
       </c>
       <c r="D27" s="24">
-        <f>T2_SLOPE</f>
-        <v>1.8814212714379457</v>
+        <f>T1_DROP_2024*100</f>
+        <v>-11.121871500771721</v>
       </c>
       <c r="E27" s="24">
-        <f>1.88</f>
-        <v>1.88</v>
+        <f>-11.12</f>
+        <v>-11.12</v>
       </c>
       <c r="F27">
         <f>0.005</f>
@@ -3674,20 +3730,20 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>T3_YEARS</t>
-        </is>
-      </c>
-      <c r="D28" s="3">
-        <f>T3_YEARS</f>
-        <v>5</v>
-      </c>
-      <c r="E28" s="3">
-        <f>5</f>
-        <v>5</v>
+          <t>T2_SLOPE (about)</t>
+        </is>
+      </c>
+      <c r="D28" s="24">
+        <f>T2_SLOPE</f>
+        <v>1.8814212714379457</v>
+      </c>
+      <c r="E28" s="24">
+        <f>1.88</f>
+        <v>1.88</v>
       </c>
       <c r="F28">
-        <f>0</f>
-        <v>0</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G28" t="str">
         <f>IF(AND(ISNUMBER(D28),ISNUMBER(E28)),IF(ABS(D28-E28)&lt;=F28,"PASS","FAIL"),"FAIL")</f>
@@ -3706,23 +3762,23 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>T3: no bed largest in each of 2017 to 2021</t>
-        </is>
-      </c>
-      <c r="D29" t="b">
-        <f>AND(INDEX(LARGEST_REASON,MATCH(2017,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2018,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2019,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2020,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2021,YEAR,0))="No bed")</f>
-        <v>1</v>
-      </c>
-      <c r="E29" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F29" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
+          <t>T3_YEARS</t>
+        </is>
+      </c>
+      <c r="D29" s="3">
+        <f>T3_YEARS</f>
+        <v>5</v>
+      </c>
+      <c r="E29" s="3">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="F29">
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="G29" t="str">
-        <f>IF(D29=E29,"PASS","FAIL")</f>
+        <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29)),IF(ABS(D29-E29)&lt;=F29,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -3738,11 +3794,11 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>REASON_SUM(y) = DEC31_TOTAL(y), 2018 to 2024</t>
+          <t>T3: no bed largest in each of 2017 to 2021</t>
         </is>
       </c>
       <c r="D30" t="b">
-        <f>AND(INDEX(REASON_SUM,2)=INDEX(DEC31_TOTAL,2),INDEX(REASON_SUM,3)=INDEX(DEC31_TOTAL,3),INDEX(REASON_SUM,4)=INDEX(DEC31_TOTAL,4),INDEX(REASON_SUM,5)=INDEX(DEC31_TOTAL,5),INDEX(REASON_SUM,6)=INDEX(DEC31_TOTAL,6),INDEX(REASON_SUM,7)=INDEX(DEC31_TOTAL,7),INDEX(REASON_SUM,8)=INDEX(DEC31_TOTAL,8))</f>
+        <f>AND(INDEX(LARGEST_REASON,MATCH(2017,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2018,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2019,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2020,YEAR,0))="No bed",INDEX(LARGEST_REASON,MATCH(2021,YEAR,0))="No bed")</f>
         <v>1</v>
       </c>
       <c r="E30" t="b">
@@ -3770,23 +3826,23 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>REASON_SUM(2017)</t>
-        </is>
-      </c>
-      <c r="D31" s="3">
-        <f>INDEX(REASON_SUM,MATCH(2017,YEAR,0))</f>
-        <v>120.0</v>
-      </c>
-      <c r="E31" s="3">
-        <f>120</f>
-        <v>120</v>
-      </c>
-      <c r="F31">
-        <f>0</f>
-        <v>0</v>
+          <t>REASON_SUM(y) = DEC31_TOTAL(y), 2018 to 2024</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <f>AND(INDEX(REASON_SUM,2)=INDEX(DEC31_TOTAL,2),INDEX(REASON_SUM,3)=INDEX(DEC31_TOTAL,3),INDEX(REASON_SUM,4)=INDEX(DEC31_TOTAL,4),INDEX(REASON_SUM,5)=INDEX(DEC31_TOTAL,5),INDEX(REASON_SUM,6)=INDEX(DEC31_TOTAL,6),INDEX(REASON_SUM,7)=INDEX(DEC31_TOTAL,7),INDEX(REASON_SUM,8)=INDEX(DEC31_TOTAL,8))</f>
+        <v>1</v>
+      </c>
+      <c r="E31" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F31" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
       </c>
       <c r="G31" t="str">
-        <f>IF(AND(ISNUMBER(D31),ISNUMBER(E31)),IF(ABS(D31-E31)&lt;=F31,"PASS","FAIL"),"FAIL")</f>
+        <f>IF(D31=E31,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -3802,16 +3858,16 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DEC31_TOTAL(2017)</t>
+          <t>REASON_SUM(2017)</t>
         </is>
       </c>
       <c r="D32" s="3">
-        <f>INDEX(DEC31_TOTAL,MATCH(2017,YEAR,0))</f>
-        <v>157</v>
+        <f>INDEX(REASON_SUM,MATCH(2017,YEAR,0))</f>
+        <v>120.0</v>
       </c>
       <c r="E32" s="3">
-        <f>157</f>
-        <v>157</v>
+        <f>120</f>
+        <v>120</v>
       </c>
       <c r="F32">
         <f>0</f>
@@ -3834,20 +3890,20 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>KFF_COST_DAY x 0.15 (arithmetic on the input)</t>
-        </is>
-      </c>
-      <c r="D33" s="35">
-        <f>KFF_COST_DAY*0.15</f>
-        <v>549.6</v>
-      </c>
-      <c r="E33" s="35">
-        <f>549.6</f>
-        <v>549.6</v>
+          <t>DEC31_TOTAL(2017)</t>
+        </is>
+      </c>
+      <c r="D33" s="3">
+        <f>INDEX(DEC31_TOTAL,MATCH(2017,YEAR,0))</f>
+        <v>157</v>
+      </c>
+      <c r="E33" s="3">
+        <f>157</f>
+        <v>157</v>
       </c>
       <c r="F33">
-        <f>0.005</f>
-        <v>0.005</v>
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="G33" t="str">
         <f>IF(AND(ISNUMBER(D33),ISNUMBER(E33)),IF(ABS(D33-E33)&lt;=F33,"PASS","FAIL"),"FAIL")</f>
@@ -3866,16 +3922,16 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>KFF_COST_DAY x 0.40 (arithmetic on the input)</t>
+          <t>KFF_COST_DAY x 0.15 (arithmetic on the input)</t>
         </is>
       </c>
       <c r="D34" s="35">
-        <f>KFF_COST_DAY*0.4</f>
-        <v>1465.6000000000001</v>
+        <f>KFF_COST_DAY*0.15</f>
+        <v>549.6</v>
       </c>
       <c r="E34" s="35">
-        <f>1465.6</f>
-        <v>1465.6</v>
+        <f>549.6</f>
+        <v>549.6</v>
       </c>
       <c r="F34">
         <f>0.005</f>
@@ -3898,20 +3954,20 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>KFF_COST_DAY x 0.15 within rounding (to $10) of AVOID_COST_LO</t>
+          <t>KFF_COST_DAY x 0.40 (arithmetic on the input)</t>
         </is>
       </c>
       <c r="D35" s="35">
-        <f>KFF_COST_DAY*0.15</f>
-        <v>549.6</v>
+        <f>KFF_COST_DAY*0.4</f>
+        <v>1465.6000000000001</v>
       </c>
       <c r="E35" s="35">
-        <f>AVOID_COST_LO</f>
-        <v>550</v>
+        <f>1465.6</f>
+        <v>1465.6</v>
       </c>
       <c r="F35">
-        <f>5</f>
-        <v>5</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G35" t="str">
         <f>IF(AND(ISNUMBER(D35),ISNUMBER(E35)),IF(ABS(D35-E35)&lt;=F35,"PASS","FAIL"),"FAIL")</f>
@@ -3930,16 +3986,16 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>KFF_COST_DAY x 0.40 within rounding (to $10) of AVOID_COST_HI</t>
+          <t>KFF_COST_DAY x 0.15 within rounding (to $10) of AVOID_COST_LO</t>
         </is>
       </c>
       <c r="D36" s="35">
-        <f>KFF_COST_DAY*0.4</f>
-        <v>1465.6000000000001</v>
+        <f>KFF_COST_DAY*0.15</f>
+        <v>549.6</v>
       </c>
       <c r="E36" s="35">
-        <f>AVOID_COST_HI</f>
-        <v>1470</v>
+        <f>AVOID_COST_LO</f>
+        <v>550</v>
       </c>
       <c r="F36">
         <f>5</f>
@@ -3962,20 +4018,20 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CAP_RATIO(2024)</t>
-        </is>
-      </c>
-      <c r="D37" s="24">
-        <f>INDEX(CAP_RATIO,MATCH(2024,YEAR,0))</f>
-        <v>11.692200069954529</v>
-      </c>
-      <c r="E37" s="24">
-        <f>11.69</f>
-        <v>11.69</v>
+          <t>KFF_COST_DAY x 0.40 within rounding (to $10) of AVOID_COST_HI</t>
+        </is>
+      </c>
+      <c r="D37" s="35">
+        <f>KFF_COST_DAY*0.4</f>
+        <v>1465.6000000000001</v>
+      </c>
+      <c r="E37" s="35">
+        <f>AVOID_COST_HI</f>
+        <v>1470</v>
       </c>
       <c r="F37">
-        <f>0.005</f>
-        <v>0.005</v>
+        <f>5</f>
+        <v>5</v>
       </c>
       <c r="G37" t="str">
         <f>IF(AND(ISNUMBER(D37),ISNUMBER(E37)),IF(ABS(D37-E37)&lt;=F37,"PASS","FAIL"),"FAIL")</f>
@@ -3994,16 +4050,16 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CAP_RATIO_STAFF_2024</t>
+          <t>CAP_RATIO(2024)</t>
         </is>
       </c>
       <c r="D38" s="24">
-        <f>CAP_RATIO_STAFF_2024</f>
-        <v>7.531654424623994</v>
+        <f>INDEX(CAP_RATIO,MATCH(2024,YEAR,0))</f>
+        <v>11.692200069954529</v>
       </c>
       <c r="E38" s="24">
-        <f>7.53</f>
-        <v>7.53</v>
+        <f>11.69</f>
+        <v>11.69</v>
       </c>
       <c r="F38">
         <f>0.005</f>
@@ -4026,20 +4082,20 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>T1_FIN_CHANGE_2021</t>
-        </is>
-      </c>
-      <c r="D39" s="3">
-        <f>T1_FIN_CHANGE_2021</f>
-        <v>13.0</v>
-      </c>
-      <c r="E39" s="3">
-        <f>13</f>
-        <v>13</v>
+          <t>CAP_RATIO_STAFF_2024</t>
+        </is>
+      </c>
+      <c r="D39" s="24">
+        <f>CAP_RATIO_STAFF_2024</f>
+        <v>7.531654424623994</v>
+      </c>
+      <c r="E39" s="24">
+        <f>7.53</f>
+        <v>7.53</v>
       </c>
       <c r="F39">
-        <f>0</f>
-        <v>0</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G39" t="str">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(E39)),IF(ABS(D39-E39)&lt;=F39,"PASS","FAIL"),"FAIL")</f>
@@ -4058,16 +4114,16 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>T1_OTHER_CHANGE_2021</t>
+          <t>T1_FIN_CHANGE_2021</t>
         </is>
       </c>
       <c r="D40" s="3">
-        <f>T1_OTHER_CHANGE_2021</f>
-        <v>32.0</v>
+        <f>T1_FIN_CHANGE_2021</f>
+        <v>13.0</v>
       </c>
       <c r="E40" s="3">
-        <f>32</f>
-        <v>32</v>
+        <f>13</f>
+        <v>13</v>
       </c>
       <c r="F40">
         <f>0</f>
@@ -4090,16 +4146,16 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>T1_FIN_CHANGE_2024</t>
+          <t>T1_OTHER_CHANGE_2021</t>
         </is>
       </c>
       <c r="D41" s="3">
-        <f>T1_FIN_CHANGE_2024</f>
-        <v>15.0</v>
+        <f>T1_OTHER_CHANGE_2021</f>
+        <v>32.0</v>
       </c>
       <c r="E41" s="3">
-        <f>15</f>
-        <v>15</v>
+        <f>32</f>
+        <v>32</v>
       </c>
       <c r="F41">
         <f>0</f>
@@ -4122,16 +4178,16 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>T1_OTHER_CHANGE_2024</t>
+          <t>T1_FIN_CHANGE_2024</t>
         </is>
       </c>
       <c r="D42" s="3">
-        <f>T1_OTHER_CHANGE_2024</f>
-        <v>-33.0</v>
+        <f>T1_FIN_CHANGE_2024</f>
+        <v>15.0</v>
       </c>
       <c r="E42" s="3">
-        <f>-33</f>
-        <v>-33.0</v>
+        <f>15</f>
+        <v>15</v>
       </c>
       <c r="F42">
         <f>0</f>
@@ -4154,20 +4210,20 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>RATE_GROWTH_2024_2026</t>
-        </is>
-      </c>
-      <c r="D43" s="25">
-        <f>RATE_GROWTH_2024_2026</f>
-        <v>0.013840668562237424</v>
-      </c>
-      <c r="E43" s="25">
-        <f>0.0138</f>
-        <v>0.0138</v>
+          <t>T1_OTHER_CHANGE_2024</t>
+        </is>
+      </c>
+      <c r="D43" s="3">
+        <f>T1_OTHER_CHANGE_2024</f>
+        <v>-33.0</v>
+      </c>
+      <c r="E43" s="3">
+        <f>-33</f>
+        <v>-33.0</v>
       </c>
       <c r="F43">
-        <f>5e-05</f>
-        <v>5e-05</v>
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="G43" t="str">
         <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43)),IF(ABS(D43-E43)&lt;=F43,"PASS","FAIL"),"FAIL")</f>
@@ -4186,20 +4242,20 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COST_FWD(2026)</t>
-        </is>
-      </c>
-      <c r="D44" s="35">
-        <f>INDEX(COST_FWD,3)</f>
-        <v>506.080140363</v>
-      </c>
-      <c r="E44" s="35">
-        <f>506.08</f>
-        <v>506.08</v>
+          <t>RATE_GROWTH_2024_2026</t>
+        </is>
+      </c>
+      <c r="D44" s="26">
+        <f>RATE_GROWTH_2024_2026</f>
+        <v>0.013840668562237424</v>
+      </c>
+      <c r="E44" s="26">
+        <f>0.0138</f>
+        <v>0.0138</v>
       </c>
       <c r="F44">
-        <f>0.005</f>
-        <v>0.005</v>
+        <f>5e-05</f>
+        <v>5e-05</v>
       </c>
       <c r="G44" t="str">
         <f>IF(AND(ISNUMBER(D44),ISNUMBER(E44)),IF(ABS(D44-E44)&lt;=F44,"PASS","FAIL"),"FAIL")</f>
@@ -4218,16 +4274,16 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COST_FWD(2027)</t>
+          <t>COST_FWD(2026)</t>
         </is>
       </c>
       <c r="D45" s="35">
-        <f>INDEX(COST_FWD,4)</f>
-        <v>522.780784994979</v>
+        <f>INDEX(COST_FWD,3)</f>
+        <v>506.080140363</v>
       </c>
       <c r="E45" s="35">
-        <f>522.78</f>
-        <v>522.78</v>
+        <f>506.08</f>
+        <v>506.08</v>
       </c>
       <c r="F45">
         <f>0.005</f>
@@ -4250,20 +4306,20 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COND_A_GAP(2026)</t>
-        </is>
-      </c>
-      <c r="D46" s="25">
-        <f>INDEX(COND_A_GAP,1)</f>
-        <v>0.021380290392819967</v>
-      </c>
-      <c r="E46" s="25">
-        <f>0.0214</f>
-        <v>0.0214</v>
+          <t>COST_FWD(2027)</t>
+        </is>
+      </c>
+      <c r="D46" s="35">
+        <f>INDEX(COST_FWD,4)</f>
+        <v>522.780784994979</v>
+      </c>
+      <c r="E46" s="35">
+        <f>522.78</f>
+        <v>522.78</v>
       </c>
       <c r="F46">
-        <f>5e-05</f>
-        <v>5e-05</v>
+        <f>0.005</f>
+        <v>0.005</v>
       </c>
       <c r="G46" t="str">
         <f>IF(AND(ISNUMBER(D46),ISNUMBER(E46)),IF(ABS(D46-E46)&lt;=F46,"PASS","FAIL"),"FAIL")</f>
@@ -4282,16 +4338,16 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COND_A_GAP(2027)</t>
-        </is>
-      </c>
-      <c r="D47" s="25">
-        <f>INDEX(COND_A_GAP,2)</f>
-        <v>0.039531015821562265</v>
-      </c>
-      <c r="E47" s="25">
-        <f>0.0395</f>
-        <v>0.0395</v>
+          <t>COND_A_GAP(2026)</t>
+        </is>
+      </c>
+      <c r="D47" s="26">
+        <f>INDEX(COND_A_GAP,1)</f>
+        <v>0.021380290392819967</v>
+      </c>
+      <c r="E47" s="26">
+        <f>0.0214</f>
+        <v>0.0214</v>
       </c>
       <c r="F47">
         <f>5e-05</f>
@@ -4302,291 +4358,291 @@
         <v>PASS</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="29">
+        <f>44</f>
+        <v>44</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>COND_A_GAP(2027)</t>
+        </is>
+      </c>
+      <c r="D48" s="26">
+        <f>INDEX(COND_A_GAP,2)</f>
+        <v>0.039531015821562265</v>
+      </c>
+      <c r="E48" s="26">
+        <f>0.0395</f>
+        <v>0.0395</v>
+      </c>
+      <c r="F48">
+        <f>5e-05</f>
+        <v>5e-05</v>
+      </c>
+      <c r="G48" t="str">
+        <f>IF(AND(ISNUMBER(D48),ISNUMBER(E48)),IF(ABS(D48-E48)&lt;=F48,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Invariants (must pass for any inputs; part of ALL CHECKS)</t>
-        </is>
+      <c r="A49" s="29">
+        <f>45</f>
+        <v>45</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>STAY_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="D49" s="35">
+        <f>STAY_SHORTFALL</f>
+        <v>5873.496793247295</v>
+      </c>
+      <c r="E49" s="35">
+        <f>5873.50</f>
+        <v>5873.5</v>
+      </c>
+      <c r="F49">
+        <f>0.005</f>
+        <v>0.005</v>
+      </c>
+      <c r="G49" t="str">
+        <f>IF(AND(ISNUMBER(D49),ISNUMBER(E49)),IF(ABS(D49-E49)&lt;=F49,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
+      <c r="A50" s="29">
+        <f>46</f>
+        <v>46</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>RATE_RISE_2021</t>
+        </is>
+      </c>
+      <c r="D50" s="20">
+        <f>RATE_RISE_2021</f>
+        <v>0.1829457912219945</v>
+      </c>
+      <c r="E50" s="20">
+        <f>0.183</f>
+        <v>0.183</v>
+      </c>
+      <c r="F50">
+        <f>0.0005</f>
+        <v>0.0005</v>
+      </c>
+      <c r="G50" t="str">
+        <f>IF(AND(ISNUMBER(D50),ISNUMBER(E50)),IF(ABS(D50-E50)&lt;=F50,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="29">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>RATE_RISE_2024</t>
+        </is>
+      </c>
+      <c r="D51" s="20">
+        <f>RATE_RISE_2024</f>
+        <v>0.29527675475147164</v>
+      </c>
+      <c r="E51" s="20">
+        <f>0.295</f>
+        <v>0.295</v>
+      </c>
+      <c r="F51">
+        <f>0.0005</f>
+        <v>0.0005</v>
+      </c>
+      <c r="G51" t="str">
+        <f>IF(AND(ISNUMBER(D51),ISNUMBER(E51)),IF(ABS(D51-E51)&lt;=F51,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29">
+        <f>48</f>
+        <v>48</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>RATE_COST_GAP_MIN</t>
+        </is>
+      </c>
+      <c r="D52" s="26">
+        <f>RATE_COST_GAP_MIN</f>
+        <v>0.19446068559301843</v>
+      </c>
+      <c r="E52" s="26">
+        <f>0.1945</f>
+        <v>0.1945</v>
+      </c>
+      <c r="F52">
+        <f>5e-05</f>
+        <v>5e-05</v>
+      </c>
+      <c r="G52" t="str">
+        <f>IF(AND(ISNUMBER(D52),ISNUMBER(E52)),IF(ABS(D52-E52)&lt;=F52,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29">
+        <f>49</f>
+        <v>49</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>RATE_COST_GAP_MAX</t>
+        </is>
+      </c>
+      <c r="D53" s="26">
+        <f>RATE_COST_GAP_MAX</f>
+        <v>0.289584013255341</v>
+      </c>
+      <c r="E53" s="26">
+        <f>0.2896</f>
+        <v>0.2896</v>
+      </c>
+      <c r="F53">
+        <f>5e-05</f>
+        <v>5e-05</v>
+      </c>
+      <c r="G53" t="str">
+        <f>IF(AND(ISNUMBER(D53),ISNUMBER(E53)),IF(ABS(D53-E53)&lt;=F53,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29">
+        <f>50</f>
+        <v>50</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>BEH_GUARD_SHARE_2024</t>
+        </is>
+      </c>
+      <c r="D54" s="20">
+        <f>BEH_GUARD_SHARE_2024</f>
+        <v>0.3468208092485549</v>
+      </c>
+      <c r="E54" s="20">
+        <f>0.347</f>
+        <v>0.347</v>
+      </c>
+      <c r="F54">
+        <f>0.0005</f>
+        <v>0.0005</v>
+      </c>
+      <c r="G54" t="str">
+        <f>IF(AND(ISNUMBER(D54),ISNUMBER(E54)),IF(ABS(D54-E54)&lt;=F54,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Invariants (must pass for any inputs; part of ALL CHECKS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>I1</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>The seven SHARE_ values sum to 1, every year</t>
         </is>
       </c>
-      <c r="D51" t="b">
+      <c r="D58" t="b">
         <f>AND(ABS(INDEX(SHARE_NO_BED,1)+INDEX(SHARE_BEHAVIOR,1)+INDEX(SHARE_SPECIAL_CARE,1)+INDEX(SHARE_FINANCIAL,1)+INDEX(SHARE_GUARDIANSHIP,1)+INDEX(SHARE_PASARR,1)+INDEX(SHARE_OTHER,1)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,2)+INDEX(SHARE_BEHAVIOR,2)+INDEX(SHARE_SPECIAL_CARE,2)+INDEX(SHARE_FINANCIAL,2)+INDEX(SHARE_GUARDIANSHIP,2)+INDEX(SHARE_PASARR,2)+INDEX(SHARE_OTHER,2)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,3)+INDEX(SHARE_BEHAVIOR,3)+INDEX(SHARE_SPECIAL_CARE,3)+INDEX(SHARE_FINANCIAL,3)+INDEX(SHARE_GUARDIANSHIP,3)+INDEX(SHARE_PASARR,3)+INDEX(SHARE_OTHER,3)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,4)+INDEX(SHARE_BEHAVIOR,4)+INDEX(SHARE_SPECIAL_CARE,4)+INDEX(SHARE_FINANCIAL,4)+INDEX(SHARE_GUARDIANSHIP,4)+INDEX(SHARE_PASARR,4)+INDEX(SHARE_OTHER,4)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,5)+INDEX(SHARE_BEHAVIOR,5)+INDEX(SHARE_SPECIAL_CARE,5)+INDEX(SHARE_FINANCIAL,5)+INDEX(SHARE_GUARDIANSHIP,5)+INDEX(SHARE_PASARR,5)+INDEX(SHARE_OTHER,5)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,6)+INDEX(SHARE_BEHAVIOR,6)+INDEX(SHARE_SPECIAL_CARE,6)+INDEX(SHARE_FINANCIAL,6)+INDEX(SHARE_GUARDIANSHIP,6)+INDEX(SHARE_PASARR,6)+INDEX(SHARE_OTHER,6)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,7)+INDEX(SHARE_BEHAVIOR,7)+INDEX(SHARE_SPECIAL_CARE,7)+INDEX(SHARE_FINANCIAL,7)+INDEX(SHARE_GUARDIANSHIP,7)+INDEX(SHARE_PASARR,7)+INDEX(SHARE_OTHER,7)-1)&lt;=1e-06,ABS(INDEX(SHARE_NO_BED,8)+INDEX(SHARE_BEHAVIOR,8)+INDEX(SHARE_SPECIAL_CARE,8)+INDEX(SHARE_FINANCIAL,8)+INDEX(SHARE_GUARDIANSHIP,8)+INDEX(SHARE_PASARR,8)+INDEX(SHARE_OTHER,8)-1)&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E51" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F51" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G51" t="str">
-        <f>IF(D51=E51,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="29">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>WITHIN_DAYS + EXCESS_DAYS = WL_DAYS, every year</t>
-        </is>
-      </c>
-      <c r="D52" t="b">
-        <f>AND(ABS(INDEX(WITHIN_DAYS,1)+INDEX(EXCESS_DAYS,1)-INDEX(WL_DAYS,1))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,2)+INDEX(EXCESS_DAYS,2)-INDEX(WL_DAYS,2))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,3)+INDEX(EXCESS_DAYS,3)-INDEX(WL_DAYS,3))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,4)+INDEX(EXCESS_DAYS,4)-INDEX(WL_DAYS,4))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,5)+INDEX(EXCESS_DAYS,5)-INDEX(WL_DAYS,5))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,6)+INDEX(EXCESS_DAYS,6)-INDEX(WL_DAYS,6))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,7)+INDEX(EXCESS_DAYS,7)-INDEX(WL_DAYS,7))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,8)+INDEX(EXCESS_DAYS,8)-INDEX(WL_DAYS,8))&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E52" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F52" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G52" t="str">
-        <f>IF(D52=E52,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="29">
-        <f>3</f>
-        <v>3</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>I3</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>EXCESS_DAYS = MAX(0, GAP_PER_PT x WL_PATIENTS), every year (covers 2019 and 2022)</t>
-        </is>
-      </c>
-      <c r="D53" t="b">
-        <f>AND(ABS(INDEX(EXCESS_DAYS,1)-MAX(0,INDEX(GAP_PER_PT,1)*INDEX(WL_PATIENTS,1)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,2)-MAX(0,INDEX(GAP_PER_PT,2)*INDEX(WL_PATIENTS,2)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,3)-MAX(0,INDEX(GAP_PER_PT,3)*INDEX(WL_PATIENTS,3)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,4)-MAX(0,INDEX(GAP_PER_PT,4)*INDEX(WL_PATIENTS,4)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,5)-MAX(0,INDEX(GAP_PER_PT,5)*INDEX(WL_PATIENTS,5)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,6)-MAX(0,INDEX(GAP_PER_PT,6)*INDEX(WL_PATIENTS,6)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,7)-MAX(0,INDEX(GAP_PER_PT,7)*INDEX(WL_PATIENTS,7)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,8)-MAX(0,INDEX(GAP_PER_PT,8)*INDEX(WL_PATIENTS,8)))&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E53" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F53" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G53" t="str">
-        <f>IF(D53=E53,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="29">
-        <f>4</f>
-        <v>4</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>County CTY_DAYS sum to WL_DAYS, 2023 and 2024</t>
-        </is>
-      </c>
-      <c r="D54" t="b">
-        <f>AND(ABS(INDEX(CTY_DAYS,1,1)+INDEX(CTY_DAYS,2,1)+INDEX(CTY_DAYS,3,1)+INDEX(CTY_DAYS,4,1)-INDEX(WL_DAYS,MATCH(2023,YEAR,0)))&lt;=1e-06,ABS(INDEX(CTY_DAYS,1,2)+INDEX(CTY_DAYS,2,2)+INDEX(CTY_DAYS,3,2)+INDEX(CTY_DAYS,4,2)-INDEX(WL_DAYS,MATCH(2024,YEAR,0)))&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E54" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F54" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G54" t="str">
-        <f>IF(D54=E54,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="29">
-        <f>5</f>
-        <v>5</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>I5</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>County CTY_DAY_SHARE sum to 1, 2023 and 2024</t>
-        </is>
-      </c>
-      <c r="D55" t="b">
-        <f>AND(ABS(INDEX(CTY_DAY_SHARE,1,1)+INDEX(CTY_DAY_SHARE,2,1)+INDEX(CTY_DAY_SHARE,3,1)+INDEX(CTY_DAY_SHARE,4,1)-1)&lt;=1e-06,ABS(INDEX(CTY_DAY_SHARE,1,2)+INDEX(CTY_DAY_SHARE,2,2)+INDEX(CTY_DAY_SHARE,3,2)+INDEX(CTY_DAY_SHARE,4,2)-1)&lt;=1e-06)</f>
-        <v>1</v>
-      </c>
-      <c r="E55" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-      <c r="F55" t="str">
-        <f>"exact"</f>
-        <v>exact</v>
-      </c>
-      <c r="G55" t="str">
-        <f>IF(D55=E55,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="29">
-        <f>6</f>
-        <v>6</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>I6</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>T2_SLOPE = least-squares slope written out by hand, 2017 to 2023</t>
-        </is>
-      </c>
-      <c r="D56" s="24">
-        <f>((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,1)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,2)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,3)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,4)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,5)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,6)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,7)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7))))/((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2)</f>
-        <v>1.8814212714379457</v>
-      </c>
-      <c r="E56" s="24">
-        <f>T2_SLOPE</f>
-        <v>1.8814212714379457</v>
-      </c>
-      <c r="F56">
-        <f>1e-06</f>
-        <v>1e-06</v>
-      </c>
-      <c r="G56" t="str">
-        <f>IF(AND(ISNUMBER(D56),ISNUMBER(E56)),IF(ABS(D56-E56)&lt;=F56,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="29">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>I7</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>T3_YEARS recomputed from the counts (no bed above each other reason)</t>
-        </is>
-      </c>
-      <c r="D57" s="3">
-        <f>IF(AND(INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_BEHAVIOR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_SPECIAL_CARE,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_FINANCIAL,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_GUARDIANSHIP,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_PASARR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_OTHER,1)),1,0)+IF(AND(INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_BEHAVIOR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_SPECIAL_CARE,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_FINANCIAL,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_GUARDIANSHIP,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_PASARR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_OTHER,2)),1,0)+IF(AND(INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_BEHAVIOR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_SPECIAL_CARE,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_FINANCIAL,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_GUARDIANSHIP,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_PASARR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_OTHER,3)),1,0)+IF(AND(INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_BEHAVIOR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_SPECIAL_CARE,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_FINANCIAL,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_GUARDIANSHIP,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_PASARR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_OTHER,4)),1,0)+IF(AND(INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_BEHAVIOR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_SPECIAL_CARE,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_FINANCIAL,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_GUARDIANSHIP,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_PASARR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_OTHER,5)),1,0)+IF(AND(INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_BEHAVIOR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_SPECIAL_CARE,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_FINANCIAL,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_GUARDIANSHIP,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_PASARR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_OTHER,6)),1,0)+IF(AND(INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_BEHAVIOR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_SPECIAL_CARE,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_FINANCIAL,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_GUARDIANSHIP,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_PASARR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_OTHER,7)),1,0)+IF(AND(INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_BEHAVIOR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_SPECIAL_CARE,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_FINANCIAL,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_GUARDIANSHIP,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_PASARR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_OTHER,8)),1,0)</f>
-        <v>5.0</v>
-      </c>
-      <c r="E57" s="3">
-        <f>T3_YEARS</f>
-        <v>5</v>
-      </c>
-      <c r="F57">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G57" t="str">
-        <f>IF(AND(ISNUMBER(D57),ISNUMBER(E57)),IF(ABS(D57-E57)&lt;=F57,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="29">
-        <f>8</f>
-        <v>8</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>I8</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>MEETS_BENCH is TRUE exactly when GAP_PER_PT &lt;= 0, every year</t>
-        </is>
-      </c>
-      <c r="D58" t="b">
-        <f>AND(INDEX(MEETS_BENCH,1)=(INDEX(GAP_PER_PT,1)&lt;=0),INDEX(MEETS_BENCH,2)=(INDEX(GAP_PER_PT,2)&lt;=0),INDEX(MEETS_BENCH,3)=(INDEX(GAP_PER_PT,3)&lt;=0),INDEX(MEETS_BENCH,4)=(INDEX(GAP_PER_PT,4)&lt;=0),INDEX(MEETS_BENCH,5)=(INDEX(GAP_PER_PT,5)&lt;=0),INDEX(MEETS_BENCH,6)=(INDEX(GAP_PER_PT,6)&lt;=0),INDEX(MEETS_BENCH,7)=(INDEX(GAP_PER_PT,7)&lt;=0),INDEX(MEETS_BENCH,8)=(INDEX(GAP_PER_PT,8)&lt;=0))</f>
         <v>1</v>
       </c>
       <c r="E58" t="b">
@@ -4604,106 +4660,158 @@
     </row>
     <row r="59">
       <c r="A59" s="29">
-        <f>9</f>
-        <v>9</v>
+        <f>2</f>
+        <v>2</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>I9</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Every WorkedExample row reads "match"</t>
-        </is>
-      </c>
-      <c r="D59" s="3">
-        <f>COUNTIF(WorkedExample!E29:E57,"match")</f>
-        <v>29</v>
-      </c>
-      <c r="E59" s="3">
-        <f>ROWS(WorkedExample!E29:E57)</f>
-        <v>29</v>
-      </c>
-      <c r="F59">
-        <f>0</f>
-        <v>0</v>
+          <t>WITHIN_DAYS + EXCESS_DAYS = WL_DAYS, every year</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <f>AND(ABS(INDEX(WITHIN_DAYS,1)+INDEX(EXCESS_DAYS,1)-INDEX(WL_DAYS,1))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,2)+INDEX(EXCESS_DAYS,2)-INDEX(WL_DAYS,2))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,3)+INDEX(EXCESS_DAYS,3)-INDEX(WL_DAYS,3))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,4)+INDEX(EXCESS_DAYS,4)-INDEX(WL_DAYS,4))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,5)+INDEX(EXCESS_DAYS,5)-INDEX(WL_DAYS,5))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,6)+INDEX(EXCESS_DAYS,6)-INDEX(WL_DAYS,6))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,7)+INDEX(EXCESS_DAYS,7)-INDEX(WL_DAYS,7))&lt;=1e-06,ABS(INDEX(WITHIN_DAYS,8)+INDEX(EXCESS_DAYS,8)-INDEX(WL_DAYS,8))&lt;=1e-06)</f>
+        <v>1</v>
+      </c>
+      <c r="E59" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F59" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
       </c>
       <c r="G59" t="str">
-        <f>IF(AND(ISNUMBER(D59),ISNUMBER(E59)),IF(ABS(D59-E59)&lt;=F59,"PASS","FAIL"),"FAIL")</f>
+        <f>IF(D59=E59,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="29">
+        <f>3</f>
+        <v>3</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EXCESS_DAYS = MAX(0, GAP_PER_PT x WL_PATIENTS), every year (covers 2019 and 2022)</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <f>AND(ABS(INDEX(EXCESS_DAYS,1)-MAX(0,INDEX(GAP_PER_PT,1)*INDEX(WL_PATIENTS,1)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,2)-MAX(0,INDEX(GAP_PER_PT,2)*INDEX(WL_PATIENTS,2)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,3)-MAX(0,INDEX(GAP_PER_PT,3)*INDEX(WL_PATIENTS,3)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,4)-MAX(0,INDEX(GAP_PER_PT,4)*INDEX(WL_PATIENTS,4)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,5)-MAX(0,INDEX(GAP_PER_PT,5)*INDEX(WL_PATIENTS,5)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,6)-MAX(0,INDEX(GAP_PER_PT,6)*INDEX(WL_PATIENTS,6)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,7)-MAX(0,INDEX(GAP_PER_PT,7)*INDEX(WL_PATIENTS,7)))&lt;=1e-06,ABS(INDEX(EXCESS_DAYS,8)-MAX(0,INDEX(GAP_PER_PT,8)*INDEX(WL_PATIENTS,8)))&lt;=1e-06)</f>
+        <v>1</v>
+      </c>
+      <c r="E60" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F60" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
+      </c>
+      <c r="G60" t="str">
+        <f>IF(D60=E60,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Error scans (count of error values in each sheet's used range; part of ALL CHECKS)</t>
-        </is>
+      <c r="A61" s="29">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>County CTY_DAYS sum to WL_DAYS, 2023 and 2024</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <f>AND(ABS(INDEX(CTY_DAYS,1,1)+INDEX(CTY_DAYS,2,1)+INDEX(CTY_DAYS,3,1)+INDEX(CTY_DAYS,4,1)-INDEX(WL_DAYS,MATCH(2023,YEAR,0)))&lt;=1e-06,ABS(INDEX(CTY_DAYS,1,2)+INDEX(CTY_DAYS,2,2)+INDEX(CTY_DAYS,3,2)+INDEX(CTY_DAYS,4,2)-INDEX(WL_DAYS,MATCH(2024,YEAR,0)))&lt;=1e-06)</f>
+        <v>1</v>
+      </c>
+      <c r="E61" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F61" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
+      </c>
+      <c r="G61" t="str">
+        <f>IF(D61=E61,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
+      <c r="A62" s="29">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>County CTY_DAY_SHARE sum to 1, 2023 and 2024</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <f>AND(ABS(INDEX(CTY_DAY_SHARE,1,1)+INDEX(CTY_DAY_SHARE,2,1)+INDEX(CTY_DAY_SHARE,3,1)+INDEX(CTY_DAY_SHARE,4,1)-1)&lt;=1e-06,ABS(INDEX(CTY_DAY_SHARE,1,2)+INDEX(CTY_DAY_SHARE,2,2)+INDEX(CTY_DAY_SHARE,3,2)+INDEX(CTY_DAY_SHARE,4,2)-1)&lt;=1e-06)</f>
+        <v>1</v>
+      </c>
+      <c r="E62" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F62" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
+      </c>
+      <c r="G62" t="str">
+        <f>IF(D62=E62,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="29">
-        <f>1</f>
-        <v>1</v>
+        <f>6</f>
+        <v>6</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Error scan</t>
+          <t>I6</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>No error values: Inputs (A1:S84)</t>
-        </is>
-      </c>
-      <c r="D63" s="3">
-        <f>SUMPRODUCT(--ISERROR(Inputs!A1:S84))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E63" s="3">
-        <f>0</f>
-        <v>0</v>
+          <t>T2_SLOPE = least-squares slope written out by hand, 2017 to 2023</t>
+        </is>
+      </c>
+      <c r="D63" s="24">
+        <f>((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,1)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,2)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,3)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,4)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,5)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,6)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7)))+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))*(INDEX(DAYS_PER_PT,7)-AVERAGE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7))))/((INDEX(YEAR,1)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,2)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,3)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,4)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,5)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,6)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2+(INDEX(YEAR,7)-AVERAGE(INDEX(YEAR,1):INDEX(YEAR,7)))^2)</f>
+        <v>1.8814212714379457</v>
+      </c>
+      <c r="E63" s="24">
+        <f>T2_SLOPE</f>
+        <v>1.8814212714379457</v>
       </c>
       <c r="F63">
-        <f>0</f>
-        <v>0</v>
+        <f>1e-06</f>
+        <v>1e-06</v>
       </c>
       <c r="G63" t="str">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(E63)),IF(ABS(D63-E63)&lt;=F63,"PASS","FAIL"),"FAIL")</f>
@@ -4712,26 +4820,26 @@
     </row>
     <row r="64">
       <c r="A64" s="29">
-        <f>2</f>
-        <v>2</v>
+        <f>7</f>
+        <v>7</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Error scan</t>
+          <t>I7</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>No error values: Waitlist (A1:V19)</t>
+          <t>T3_YEARS recomputed from the counts (no bed above each other reason)</t>
         </is>
       </c>
       <c r="D64" s="3">
-        <f>SUMPRODUCT(--ISERROR(Waitlist!A1:V19))</f>
-        <v>0.0</v>
+        <f>IF(AND(INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_BEHAVIOR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_SPECIAL_CARE,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_FINANCIAL,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_GUARDIANSHIP,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_PASARR,1),INDEX(REASON_NO_BED,1)&gt;INDEX(REASON_OTHER,1)),1,0)+IF(AND(INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_BEHAVIOR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_SPECIAL_CARE,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_FINANCIAL,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_GUARDIANSHIP,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_PASARR,2),INDEX(REASON_NO_BED,2)&gt;INDEX(REASON_OTHER,2)),1,0)+IF(AND(INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_BEHAVIOR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_SPECIAL_CARE,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_FINANCIAL,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_GUARDIANSHIP,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_PASARR,3),INDEX(REASON_NO_BED,3)&gt;INDEX(REASON_OTHER,3)),1,0)+IF(AND(INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_BEHAVIOR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_SPECIAL_CARE,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_FINANCIAL,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_GUARDIANSHIP,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_PASARR,4),INDEX(REASON_NO_BED,4)&gt;INDEX(REASON_OTHER,4)),1,0)+IF(AND(INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_BEHAVIOR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_SPECIAL_CARE,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_FINANCIAL,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_GUARDIANSHIP,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_PASARR,5),INDEX(REASON_NO_BED,5)&gt;INDEX(REASON_OTHER,5)),1,0)+IF(AND(INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_BEHAVIOR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_SPECIAL_CARE,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_FINANCIAL,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_GUARDIANSHIP,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_PASARR,6),INDEX(REASON_NO_BED,6)&gt;INDEX(REASON_OTHER,6)),1,0)+IF(AND(INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_BEHAVIOR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_SPECIAL_CARE,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_FINANCIAL,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_GUARDIANSHIP,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_PASARR,7),INDEX(REASON_NO_BED,7)&gt;INDEX(REASON_OTHER,7)),1,0)+IF(AND(INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_BEHAVIOR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_SPECIAL_CARE,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_FINANCIAL,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_GUARDIANSHIP,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_PASARR,8),INDEX(REASON_NO_BED,8)&gt;INDEX(REASON_OTHER,8)),1,0)</f>
+        <v>5.0</v>
       </c>
       <c r="E64" s="3">
-        <f>0</f>
-        <v>0</v>
+        <f>T3_YEARS</f>
+        <v>5</v>
       </c>
       <c r="F64">
         <f>0</f>
@@ -4744,58 +4852,58 @@
     </row>
     <row r="65">
       <c r="A65" s="29">
-        <f>3</f>
-        <v>3</v>
+        <f>8</f>
+        <v>8</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Error scan</t>
+          <t>I8</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>No error values: Cost (A1:F21)</t>
-        </is>
-      </c>
-      <c r="D65" s="3">
-        <f>SUMPRODUCT(--ISERROR(Cost!A1:F21))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E65" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <f>0</f>
-        <v>0</v>
+          <t>MEETS_BENCH is TRUE exactly when GAP_PER_PT &lt;= 0, every year</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <f>AND(INDEX(MEETS_BENCH,1)=(INDEX(GAP_PER_PT,1)&lt;=0),INDEX(MEETS_BENCH,2)=(INDEX(GAP_PER_PT,2)&lt;=0),INDEX(MEETS_BENCH,3)=(INDEX(GAP_PER_PT,3)&lt;=0),INDEX(MEETS_BENCH,4)=(INDEX(GAP_PER_PT,4)&lt;=0),INDEX(MEETS_BENCH,5)=(INDEX(GAP_PER_PT,5)&lt;=0),INDEX(MEETS_BENCH,6)=(INDEX(GAP_PER_PT,6)&lt;=0),INDEX(MEETS_BENCH,7)=(INDEX(GAP_PER_PT,7)&lt;=0),INDEX(MEETS_BENCH,8)=(INDEX(GAP_PER_PT,8)&lt;=0))</f>
+        <v>1</v>
+      </c>
+      <c r="E65" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="F65" t="str">
+        <f>"exact"</f>
+        <v>exact</v>
       </c>
       <c r="G65" t="str">
-        <f>IF(AND(ISNUMBER(D65),ISNUMBER(E65)),IF(ABS(D65-E65)&lt;=F65,"PASS","FAIL"),"FAIL")</f>
+        <f>IF(D65=E65,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="29">
-        <f>4</f>
-        <v>4</v>
+        <f>9</f>
+        <v>9</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Error scan</t>
+          <t>I9</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>No error values: Tests (A1:F41)</t>
+          <t>Every WorkedExample row reads "match"</t>
         </is>
       </c>
       <c r="D66" s="3">
-        <f>SUMPRODUCT(--ISERROR(Tests!A1:F41))</f>
-        <v>0.0</v>
+        <f>COUNTIF(WorkedExample!E29:E57,"match")</f>
+        <v>29</v>
       </c>
       <c r="E66" s="3">
-        <f>0</f>
-        <v>0</v>
+        <f>ROWS(WorkedExample!E29:E57)</f>
+        <v>29</v>
       </c>
       <c r="F66">
         <f>0</f>
@@ -4806,106 +4914,54 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29">
-        <f>5</f>
-        <v>5</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>No error values: County (A1:F12)</t>
-        </is>
-      </c>
-      <c r="D67" s="3">
-        <f>SUMPRODUCT(--ISERROR(County!A1:F12))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E67" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G67" t="str">
-        <f>IF(AND(ISNUMBER(D67),ISNUMBER(E67)),IF(ABS(D67-E67)&lt;=F67,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
     <row r="68">
-      <c r="A68" s="29">
-        <f>6</f>
-        <v>6</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>No error values: Capacity (A1:E22)</t>
-        </is>
-      </c>
-      <c r="D68" s="3">
-        <f>SUMPRODUCT(--ISERROR(Capacity!A1:E22))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E68" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G68" t="str">
-        <f>IF(AND(ISNUMBER(D68),ISNUMBER(E68)),IF(ABS(D68-E68)&lt;=F68,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Error scans (count of error values in each sheet's used range; part of ALL CHECKS)</t>
+        </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Error scan</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>No error values: Conditions (A1:F17)</t>
-        </is>
-      </c>
-      <c r="D69" s="3">
-        <f>SUMPRODUCT(--ISERROR(Conditions!A1:F17))</f>
-        <v>0.0</v>
-      </c>
-      <c r="E69" s="3">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F69">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="G69" t="str">
-        <f>IF(AND(ISNUMBER(D69),ISNUMBER(E69)),IF(ABS(D69-E69)&lt;=F69,"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="29">
-        <f>8</f>
-        <v>8</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
@@ -4914,11 +4970,11 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>No error values: FigureData (A1:J88)</t>
+          <t>No error values: Inputs (A1:S86)</t>
         </is>
       </c>
       <c r="D70" s="3">
-        <f>SUMPRODUCT(--ISERROR(FigureData!A1:J88))</f>
+        <f>SUMPRODUCT(--ISERROR(Inputs!A1:S86))</f>
         <v>0.0</v>
       </c>
       <c r="E70" s="3">
@@ -4936,8 +4992,8 @@
     </row>
     <row r="71">
       <c r="A71" s="29">
-        <f>9</f>
-        <v>9</v>
+        <f>2</f>
+        <v>2</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
@@ -4946,11 +5002,11 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>No error values: WorkedExample (A1:G62)</t>
+          <t>No error values: Waitlist (A1:V19)</t>
         </is>
       </c>
       <c r="D71" s="3">
-        <f>SUMPRODUCT(--ISERROR(WorkedExample!A1:G62))</f>
+        <f>SUMPRODUCT(--ISERROR(Waitlist!A1:V19))</f>
         <v>0.0</v>
       </c>
       <c r="E71" s="3">
@@ -4968,8 +5024,8 @@
     </row>
     <row r="72">
       <c r="A72" s="29">
-        <f>10</f>
-        <v>10</v>
+        <f>3</f>
+        <v>3</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
@@ -4978,11 +5034,11 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>No error values: Checks (rows 1 to 71, above this row)</t>
+          <t>No error values: Cost (A1:F22)</t>
         </is>
       </c>
       <c r="D72" s="3">
-        <f>SUMPRODUCT(--ISERROR(A1:G71))</f>
+        <f>SUMPRODUCT(--ISERROR(Cost!A1:F22))</f>
         <v>0.0</v>
       </c>
       <c r="E72" s="3">
@@ -4998,34 +5054,258 @@
         <v>PASS</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="29">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>No error values: Tests (A1:F41)</t>
+        </is>
+      </c>
+      <c r="D73" s="3">
+        <f>SUMPRODUCT(--ISERROR(Tests!A1:F41))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E73" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G73" t="str">
+        <f>IF(AND(ISNUMBER(D73),ISNUMBER(E73)),IF(ABS(D73-E73)&lt;=F73,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
     <row r="74">
+      <c r="A74" s="29">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>No error values: County (A1:F12)</t>
+        </is>
+      </c>
+      <c r="D74" s="3">
+        <f>SUMPRODUCT(--ISERROR(County!A1:F12))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E74" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G74" t="str">
+        <f>IF(AND(ISNUMBER(D74),ISNUMBER(E74)),IF(ABS(D74-E74)&lt;=F74,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>No error values: Capacity (A1:E22)</t>
+        </is>
+      </c>
+      <c r="D75" s="3">
+        <f>SUMPRODUCT(--ISERROR(Capacity!A1:E22))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E75" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G75" t="str">
+        <f>IF(AND(ISNUMBER(D75),ISNUMBER(E75)),IF(ABS(D75-E75)&lt;=F75,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>No error values: Conditions (A1:F38)</t>
+        </is>
+      </c>
+      <c r="D76" s="3">
+        <f>SUMPRODUCT(--ISERROR(Conditions!A1:F38))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E76" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G76" t="str">
+        <f>IF(AND(ISNUMBER(D76),ISNUMBER(E76)),IF(ABS(D76-E76)&lt;=F76,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>No error values: FigureData (A1:J88)</t>
+        </is>
+      </c>
+      <c r="D77" s="3">
+        <f>SUMPRODUCT(--ISERROR(FigureData!A1:J88))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E77" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G77" t="str">
+        <f>IF(AND(ISNUMBER(D77),ISNUMBER(E77)),IF(ABS(D77-E77)&lt;=F77,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="29">
+        <f>9</f>
+        <v>9</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>No error values: WorkedExample (A1:G62)</t>
+        </is>
+      </c>
+      <c r="D78" s="3">
+        <f>SUMPRODUCT(--ISERROR(WorkedExample!A1:G62))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E78" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G78" t="str">
+        <f>IF(AND(ISNUMBER(D78),ISNUMBER(E78)),IF(ABS(D78-E78)&lt;=F78,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="29">
+        <f>10</f>
+        <v>10</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Error scan</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>No error values: Checks (rows 1 to 78, above this row)</t>
+        </is>
+      </c>
+      <c r="D79" s="3">
+        <f>SUMPRODUCT(--ISERROR(A1:G78))</f>
+        <v>0.0</v>
+      </c>
+      <c r="E79" s="3">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G79" t="str">
+        <f>IF(AND(ISNUMBER(D79),ISNUMBER(E79)),IF(ABS(D79-E79)&lt;=F79,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
           <t>ALL CHECKS (invariants and error scans)</t>
         </is>
       </c>
-      <c r="D74" s="4" t="str">
-        <f>IF(AND(COUNTIF(G51:G59,"FAIL")+COUNTIF(G63:G72,"FAIL")=0,COUNTIF(G51:G59,"PASS")+COUNTIF(G63:G72,"PASS")=19),"ALL PASS","REVIEW")</f>
+      <c r="D81" s="4" t="str">
+        <f>IF(AND(COUNTIF(G58:G66,"FAIL")+COUNTIF(G70:G79,"FAIL")=0,COUNTIF(G58:G66,"PASS")+COUNTIF(G70:G79,"PASS")=19),"ALL PASS","REVIEW")</f>
         <v>ALL PASS</v>
       </c>
     </row>
-    <row r="75">
-      <c r="C75" s="2" t="inlineStr">
+    <row r="82">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Anchors matching</t>
         </is>
       </c>
-      <c r="D75" s="3">
-        <f>COUNTIF(G5:G47,"PASS")</f>
-        <v>43</v>
-      </c>
-      <c r="E75" t="str">
-        <f>"of "&amp;ROWS(G5:G47)</f>
-        <v>of 43</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="15" t="inlineStr">
+      <c r="D82" s="3">
+        <f>COUNTIF(G5:G54,"PASS")</f>
+        <v>50</v>
+      </c>
+      <c r="E82" t="str">
+        <f>"of "&amp;ROWS(G5:G54)</f>
+        <v>of 50</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Anchor tolerance = half a unit of the spec's shown precision; invariant tolerance 1e-6. Checked outside the workbook by script (spec Audit findings): every calculated cell is a formula; every spec name exists as an absolute defined name and no others; every input cell is yellow and no calculated cell is.</t>
         </is>
@@ -5183,11 +5463,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14">
+      <c r="A4" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <f>INDEX(WL_DAYS,1)/INDEX(WL_PATIENTS,1)</f>
         <v>9.935348310974625</v>
       </c>
@@ -5195,7 +5475,7 @@
         <f>INDEX(WL_PATIENTS,1)*BENCH_DAYS</f>
         <v>86618.0</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="19">
         <f>INDEX(DAYS_PER_PT,1)-BENCH_DAYS</f>
         <v>-4.064651689025375</v>
       </c>
@@ -5211,7 +5491,7 @@
         <f>INDEX(WL_DAYS,1)-INDEX(EXCESS_DAYS,1)</f>
         <v>61470.0</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="20">
         <f>INDEX(EXCESS_DAYS,1)/INDEX(WL_DAYS,1)</f>
         <v>0.0</v>
       </c>
@@ -5219,7 +5499,7 @@
         <f>DATE(INDEX(YEAR,1)+1,1,1)-DATE(INDEX(YEAR,1),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="19">
         <f>INDEX(EXCESS_DAYS,1)/INDEX(DAYS_IN_YEAR,1)</f>
         <v>0.0</v>
       </c>
@@ -5231,31 +5511,31 @@
         <f>INDEX(REASON_NO_BED,1)+INDEX(REASON_BEHAVIOR,1)+INDEX(REASON_SPECIAL_CARE,1)+INDEX(REASON_FINANCIAL,1)+INDEX(REASON_GUARDIANSHIP,1)+INDEX(REASON_PASARR,1)+INDEX(REASON_OTHER,1)</f>
         <v>120.0</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="20">
         <f>INDEX(REASON_NO_BED,1)/INDEX(REASON_SUM,1)</f>
         <v>0.325</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="20">
         <f>INDEX(REASON_BEHAVIOR,1)/INDEX(REASON_SUM,1)</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,1)/INDEX(REASON_SUM,1)</f>
         <v>0.19166666666666668</v>
       </c>
-      <c r="P4" s="19">
+      <c r="P4" s="20">
         <f>INDEX(REASON_FINANCIAL,1)/INDEX(REASON_SUM,1)</f>
         <v>0.15</v>
       </c>
-      <c r="Q4" s="19">
+      <c r="Q4" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,1)/INDEX(REASON_SUM,1)</f>
         <v>0.09166666666666666</v>
       </c>
-      <c r="R4" s="19">
+      <c r="R4" s="20">
         <f>INDEX(REASON_PASARR,1)/INDEX(REASON_SUM,1)</f>
         <v>0.016666666666666666</v>
       </c>
-      <c r="S4" s="19">
+      <c r="S4" s="20">
         <f>INDEX(REASON_OTHER,1)/INDEX(REASON_SUM,1)</f>
         <v>0.09166666666666666</v>
       </c>
@@ -5269,11 +5549,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>INDEX(WL_DAYS,2)/INDEX(WL_PATIENTS,2)</f>
         <v>12.484132980732905</v>
       </c>
@@ -5281,7 +5561,7 @@
         <f>INDEX(WL_PATIENTS,2)*BENCH_DAYS</f>
         <v>74116.0</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>INDEX(DAYS_PER_PT,2)-BENCH_DAYS</f>
         <v>-1.5158670192670947</v>
       </c>
@@ -5297,7 +5577,7 @@
         <f>INDEX(WL_DAYS,2)-INDEX(EXCESS_DAYS,2)</f>
         <v>66091.0</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="20">
         <f>INDEX(EXCESS_DAYS,2)/INDEX(WL_DAYS,2)</f>
         <v>0.0</v>
       </c>
@@ -5305,7 +5585,7 @@
         <f>DATE(INDEX(YEAR,2)+1,1,1)-DATE(INDEX(YEAR,2),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="19">
         <f>INDEX(EXCESS_DAYS,2)/INDEX(DAYS_IN_YEAR,2)</f>
         <v>0.0</v>
       </c>
@@ -5317,31 +5597,31 @@
         <f>INDEX(REASON_NO_BED,2)+INDEX(REASON_BEHAVIOR,2)+INDEX(REASON_SPECIAL_CARE,2)+INDEX(REASON_FINANCIAL,2)+INDEX(REASON_GUARDIANSHIP,2)+INDEX(REASON_PASARR,2)+INDEX(REASON_OTHER,2)</f>
         <v>171.0</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="20">
         <f>INDEX(REASON_NO_BED,2)/INDEX(REASON_SUM,2)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="20">
         <f>INDEX(REASON_BEHAVIOR,2)/INDEX(REASON_SUM,2)</f>
         <v>0.1695906432748538</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,2)/INDEX(REASON_SUM,2)</f>
         <v>0.09941520467836257</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="20">
         <f>INDEX(REASON_FINANCIAL,2)/INDEX(REASON_SUM,2)</f>
         <v>0.18128654970760233</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,2)/INDEX(REASON_SUM,2)</f>
         <v>0.10526315789473684</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="20">
         <f>INDEX(REASON_PASARR,2)/INDEX(REASON_SUM,2)</f>
         <v>0.011695906432748537</v>
       </c>
-      <c r="S5" s="19">
+      <c r="S5" s="20">
         <f>INDEX(REASON_OTHER,2)/INDEX(REASON_SUM,2)</f>
         <v>0.09941520467836257</v>
       </c>
@@ -5355,11 +5635,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>INDEX(WL_DAYS,3)/INDEX(WL_PATIENTS,3)</f>
         <v>16.4741127348643</v>
       </c>
@@ -5367,7 +5647,7 @@
         <f>INDEX(WL_PATIENTS,3)*BENCH_DAYS</f>
         <v>67060.0</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <f>INDEX(DAYS_PER_PT,3)-BENCH_DAYS</f>
         <v>2.474112734864299</v>
       </c>
@@ -5383,7 +5663,7 @@
         <f>INDEX(WL_DAYS,3)-INDEX(EXCESS_DAYS,3)</f>
         <v>67060.0</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <f>INDEX(EXCESS_DAYS,3)/INDEX(WL_DAYS,3)</f>
         <v>0.1501818504391023</v>
       </c>
@@ -5391,7 +5671,7 @@
         <f>DATE(INDEX(YEAR,3)+1,1,1)-DATE(INDEX(YEAR,3),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="19">
         <f>INDEX(EXCESS_DAYS,3)/INDEX(DAYS_IN_YEAR,3)</f>
         <v>32.46849315068493</v>
       </c>
@@ -5403,31 +5683,31 @@
         <f>INDEX(REASON_NO_BED,3)+INDEX(REASON_BEHAVIOR,3)+INDEX(REASON_SPECIAL_CARE,3)+INDEX(REASON_FINANCIAL,3)+INDEX(REASON_GUARDIANSHIP,3)+INDEX(REASON_PASARR,3)+INDEX(REASON_OTHER,3)</f>
         <v>184.0</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="20">
         <f>INDEX(REASON_NO_BED,3)/INDEX(REASON_SUM,3)</f>
         <v>0.391304347826087</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="20">
         <f>INDEX(REASON_BEHAVIOR,3)/INDEX(REASON_SUM,3)</f>
         <v>0.14673913043478262</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,3)/INDEX(REASON_SUM,3)</f>
         <v>0.11413043478260869</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="20">
         <f>INDEX(REASON_FINANCIAL,3)/INDEX(REASON_SUM,3)</f>
         <v>0.17391304347826086</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="Q6" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,3)/INDEX(REASON_SUM,3)</f>
         <v>0.14130434782608695</v>
       </c>
-      <c r="R6" s="19">
+      <c r="R6" s="20">
         <f>INDEX(REASON_PASARR,3)/INDEX(REASON_SUM,3)</f>
         <v>0.0</v>
       </c>
-      <c r="S6" s="19">
+      <c r="S6" s="20">
         <f>INDEX(REASON_OTHER,3)/INDEX(REASON_SUM,3)</f>
         <v>0.03260869565217391</v>
       </c>
@@ -5441,11 +5721,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>INDEX(WL_DAYS,4)/INDEX(WL_PATIENTS,4)</f>
         <v>12.584449813309906</v>
       </c>
@@ -5453,7 +5733,7 @@
         <f>INDEX(WL_PATIENTS,4)*BENCH_DAYS</f>
         <v>63742.0</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>INDEX(DAYS_PER_PT,4)-BENCH_DAYS</f>
         <v>-1.4155501866900941</v>
       </c>
@@ -5469,7 +5749,7 @@
         <f>INDEX(WL_DAYS,4)-INDEX(EXCESS_DAYS,4)</f>
         <v>57297.0</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="20">
         <f>INDEX(EXCESS_DAYS,4)/INDEX(WL_DAYS,4)</f>
         <v>0.0</v>
       </c>
@@ -5477,7 +5757,7 @@
         <f>DATE(INDEX(YEAR,4)+1,1,1)-DATE(INDEX(YEAR,4),1,1)</f>
         <v>366.0</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="19">
         <f>INDEX(EXCESS_DAYS,4)/INDEX(DAYS_IN_YEAR,4)</f>
         <v>0.0</v>
       </c>
@@ -5489,31 +5769,31 @@
         <f>INDEX(REASON_NO_BED,4)+INDEX(REASON_BEHAVIOR,4)+INDEX(REASON_SPECIAL_CARE,4)+INDEX(REASON_FINANCIAL,4)+INDEX(REASON_GUARDIANSHIP,4)+INDEX(REASON_PASARR,4)+INDEX(REASON_OTHER,4)</f>
         <v>144.0</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="20">
         <f>INDEX(REASON_NO_BED,4)/INDEX(REASON_SUM,4)</f>
         <v>0.2847222222222222</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="20">
         <f>INDEX(REASON_BEHAVIOR,4)/INDEX(REASON_SUM,4)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,4)/INDEX(REASON_SUM,4)</f>
         <v>0.1527777777777778</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="20">
         <f>INDEX(REASON_FINANCIAL,4)/INDEX(REASON_SUM,4)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,4)/INDEX(REASON_SUM,4)</f>
         <v>0.10416666666666667</v>
       </c>
-      <c r="R7" s="19">
+      <c r="R7" s="20">
         <f>INDEX(REASON_PASARR,4)/INDEX(REASON_SUM,4)</f>
         <v>0.0</v>
       </c>
-      <c r="S7" s="19">
+      <c r="S7" s="20">
         <f>INDEX(REASON_OTHER,4)/INDEX(REASON_SUM,4)</f>
         <v>0.08333333333333333</v>
       </c>
@@ -5527,11 +5807,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>INDEX(WL_DAYS,5)/INDEX(WL_PATIENTS,5)</f>
         <v>12.187943982139233</v>
       </c>
@@ -5539,7 +5819,7 @@
         <f>INDEX(WL_PATIENTS,5)*BENCH_DAYS</f>
         <v>68978.0</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <f>INDEX(DAYS_PER_PT,5)-BENCH_DAYS</f>
         <v>-1.8120560178607672</v>
       </c>
@@ -5555,7 +5835,7 @@
         <f>INDEX(WL_DAYS,5)-INDEX(EXCESS_DAYS,5)</f>
         <v>60050.0</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="20">
         <f>INDEX(EXCESS_DAYS,5)/INDEX(WL_DAYS,5)</f>
         <v>0.0</v>
       </c>
@@ -5563,7 +5843,7 @@
         <f>DATE(INDEX(YEAR,5)+1,1,1)-DATE(INDEX(YEAR,5),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="19">
         <f>INDEX(EXCESS_DAYS,5)/INDEX(DAYS_IN_YEAR,5)</f>
         <v>0.0</v>
       </c>
@@ -5575,31 +5855,31 @@
         <f>INDEX(REASON_NO_BED,5)+INDEX(REASON_BEHAVIOR,5)+INDEX(REASON_SPECIAL_CARE,5)+INDEX(REASON_FINANCIAL,5)+INDEX(REASON_GUARDIANSHIP,5)+INDEX(REASON_PASARR,5)+INDEX(REASON_OTHER,5)</f>
         <v>189.0</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="20">
         <f>INDEX(REASON_NO_BED,5)/INDEX(REASON_SUM,5)</f>
         <v>0.26455026455026454</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="20">
         <f>INDEX(REASON_BEHAVIOR,5)/INDEX(REASON_SUM,5)</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,5)/INDEX(REASON_SUM,5)</f>
         <v>0.1164021164021164</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="20">
         <f>INDEX(REASON_FINANCIAL,5)/INDEX(REASON_SUM,5)</f>
         <v>0.2275132275132275</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="Q8" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,5)/INDEX(REASON_SUM,5)</f>
         <v>0.10582010582010581</v>
       </c>
-      <c r="R8" s="19">
+      <c r="R8" s="20">
         <f>INDEX(REASON_PASARR,5)/INDEX(REASON_SUM,5)</f>
         <v>0.0</v>
       </c>
-      <c r="S8" s="19">
+      <c r="S8" s="20">
         <f>INDEX(REASON_OTHER,5)/INDEX(REASON_SUM,5)</f>
         <v>0.09523809523809523</v>
       </c>
@@ -5613,11 +5893,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>INDEX(WL_DAYS,6)/INDEX(WL_PATIENTS,6)</f>
         <v>21.34229828850856</v>
       </c>
@@ -5625,7 +5905,7 @@
         <f>INDEX(WL_PATIENTS,6)*BENCH_DAYS</f>
         <v>51534.0</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>INDEX(DAYS_PER_PT,6)-BENCH_DAYS</f>
         <v>7.342298288508559</v>
       </c>
@@ -5641,7 +5921,7 @@
         <f>INDEX(WL_DAYS,6)-INDEX(EXCESS_DAYS,6)</f>
         <v>51534.0</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="20">
         <f>INDEX(EXCESS_DAYS,6)/INDEX(WL_DAYS,6)</f>
         <v>0.3440256615878107</v>
       </c>
@@ -5649,7 +5929,7 @@
         <f>DATE(INDEX(YEAR,6)+1,1,1)-DATE(INDEX(YEAR,6),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="19">
         <f>INDEX(EXCESS_DAYS,6)/INDEX(DAYS_IN_YEAR,6)</f>
         <v>74.04657534246576</v>
       </c>
@@ -5661,31 +5941,31 @@
         <f>INDEX(REASON_NO_BED,6)+INDEX(REASON_BEHAVIOR,6)+INDEX(REASON_SPECIAL_CARE,6)+INDEX(REASON_FINANCIAL,6)+INDEX(REASON_GUARDIANSHIP,6)+INDEX(REASON_PASARR,6)+INDEX(REASON_OTHER,6)</f>
         <v>250.0</v>
       </c>
-      <c r="M9" s="19">
+      <c r="M9" s="20">
         <f>INDEX(REASON_NO_BED,6)/INDEX(REASON_SUM,6)</f>
         <v>0.228</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="20">
         <f>INDEX(REASON_BEHAVIOR,6)/INDEX(REASON_SUM,6)</f>
         <v>0.14</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,6)/INDEX(REASON_SUM,6)</f>
         <v>0.156</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="20">
         <f>INDEX(REASON_FINANCIAL,6)/INDEX(REASON_SUM,6)</f>
         <v>0.3</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="Q9" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,6)/INDEX(REASON_SUM,6)</f>
         <v>0.116</v>
       </c>
-      <c r="R9" s="19">
+      <c r="R9" s="20">
         <f>INDEX(REASON_PASARR,6)/INDEX(REASON_SUM,6)</f>
         <v>0.02</v>
       </c>
-      <c r="S9" s="19">
+      <c r="S9" s="20">
         <f>INDEX(REASON_OTHER,6)/INDEX(REASON_SUM,6)</f>
         <v>0.04</v>
       </c>
@@ -5699,11 +5979,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>INDEX(WL_DAYS,7)/INDEX(WL_PATIENTS,7)</f>
         <v>23.018559556786702</v>
       </c>
@@ -5711,7 +5991,7 @@
         <f>INDEX(WL_PATIENTS,7)*BENCH_DAYS</f>
         <v>50540.0</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>INDEX(DAYS_PER_PT,7)-BENCH_DAYS</f>
         <v>9.018559556786702</v>
       </c>
@@ -5727,7 +6007,7 @@
         <f>INDEX(WL_DAYS,7)-INDEX(EXCESS_DAYS,7)</f>
         <v>50540.0</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="20">
         <f>INDEX(EXCESS_DAYS,7)/INDEX(WL_DAYS,7)</f>
         <v>0.3917951309914919</v>
       </c>
@@ -5735,7 +6015,7 @@
         <f>DATE(INDEX(YEAR,7)+1,1,1)-DATE(INDEX(YEAR,7),1,1)</f>
         <v>365.0</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="19">
         <f>INDEX(EXCESS_DAYS,7)/INDEX(DAYS_IN_YEAR,7)</f>
         <v>89.1972602739726</v>
       </c>
@@ -5747,31 +6027,31 @@
         <f>INDEX(REASON_NO_BED,7)+INDEX(REASON_BEHAVIOR,7)+INDEX(REASON_SPECIAL_CARE,7)+INDEX(REASON_FINANCIAL,7)+INDEX(REASON_GUARDIANSHIP,7)+INDEX(REASON_PASARR,7)+INDEX(REASON_OTHER,7)</f>
         <v>191.0</v>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="20">
         <f>INDEX(REASON_NO_BED,7)/INDEX(REASON_SUM,7)</f>
         <v>0.2198952879581152</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="20">
         <f>INDEX(REASON_BEHAVIOR,7)/INDEX(REASON_SUM,7)</f>
         <v>0.2513089005235602</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,7)/INDEX(REASON_SUM,7)</f>
         <v>0.13612565445026178</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="20">
         <f>INDEX(REASON_FINANCIAL,7)/INDEX(REASON_SUM,7)</f>
         <v>0.2356020942408377</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,7)/INDEX(REASON_SUM,7)</f>
         <v>0.14659685863874344</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="20">
         <f>INDEX(REASON_PASARR,7)/INDEX(REASON_SUM,7)</f>
         <v>0.005235602094240838</v>
       </c>
-      <c r="S10" s="19">
+      <c r="S10" s="20">
         <f>INDEX(REASON_OTHER,7)/INDEX(REASON_SUM,7)</f>
         <v>0.005235602094240838</v>
       </c>
@@ -5785,11 +6065,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>INDEX(WL_DAYS,8)/INDEX(WL_PATIENTS,8)</f>
         <v>19.492795389048993</v>
       </c>
@@ -5797,7 +6077,7 @@
         <f>INDEX(WL_PATIENTS,8)*BENCH_DAYS</f>
         <v>43722.0</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f>INDEX(DAYS_PER_PT,8)-BENCH_DAYS</f>
         <v>5.492795389048993</v>
       </c>
@@ -5813,7 +6093,7 @@
         <f>INDEX(WL_DAYS,8)-INDEX(EXCESS_DAYS,8)</f>
         <v>43722.0</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="20">
         <f>INDEX(EXCESS_DAYS,8)/INDEX(WL_DAYS,8)</f>
         <v>0.281785925487877</v>
       </c>
@@ -5821,7 +6101,7 @@
         <f>DATE(INDEX(YEAR,8)+1,1,1)-DATE(INDEX(YEAR,8),1,1)</f>
         <v>366.0</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="19">
         <f>INDEX(EXCESS_DAYS,8)/INDEX(DAYS_IN_YEAR,8)</f>
         <v>46.868852459016395</v>
       </c>
@@ -5833,31 +6113,31 @@
         <f>INDEX(REASON_NO_BED,8)+INDEX(REASON_BEHAVIOR,8)+INDEX(REASON_SPECIAL_CARE,8)+INDEX(REASON_FINANCIAL,8)+INDEX(REASON_GUARDIANSHIP,8)+INDEX(REASON_PASARR,8)+INDEX(REASON_OTHER,8)</f>
         <v>173.0</v>
       </c>
-      <c r="M11" s="19">
+      <c r="M11" s="20">
         <f>INDEX(REASON_NO_BED,8)/INDEX(REASON_SUM,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="20">
         <f>INDEX(REASON_BEHAVIOR,8)/INDEX(REASON_SUM,8)</f>
         <v>0.1676300578034682</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="20">
         <f>INDEX(REASON_SPECIAL_CARE,8)/INDEX(REASON_SUM,8)</f>
         <v>0.10404624277456648</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="20">
         <f>INDEX(REASON_FINANCIAL,8)/INDEX(REASON_SUM,8)</f>
         <v>0.3468208092485549</v>
       </c>
-      <c r="Q11" s="19">
+      <c r="Q11" s="20">
         <f>INDEX(REASON_GUARDIANSHIP,8)/INDEX(REASON_SUM,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="R11" s="19">
+      <c r="R11" s="20">
         <f>INDEX(REASON_PASARR,8)/INDEX(REASON_SUM,8)</f>
         <v>0.0</v>
       </c>
-      <c r="S11" s="19">
+      <c r="S11" s="20">
         <f>INDEX(REASON_OTHER,8)/INDEX(REASON_SUM,8)</f>
         <v>0.023121387283236993</v>
       </c>
@@ -5887,7 +6167,7 @@
         <f>INDEX(REASON_SUM,1)&lt;INDEX(DEC31_TOTAL,1)</f>
         <v>1</v>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>2017 reasons recorded for 120 of 157 patients on Dec 31; its shares use the recorded reasons only.</t>
         </is>
@@ -5903,7 +6183,7 @@
         <f>INDEX(LTC_UNSTAFFED,8)</f>
         <v>548</v>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Staffing note (reported only)</t>
         </is>
@@ -5921,7 +6201,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Excess days are measured against the average benchmark and are a lower bound on days patients spent beyond 14. All levels of care. Beds use calendar days (366 in 2020 and 2024).</t>
         </is>
@@ -5938,7 +6218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" style="7" min="1" max="1"/>
@@ -5983,7 +6263,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Excess days</t>
         </is>
@@ -6007,7 +6287,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Waitlisted rate, January</t>
         </is>
@@ -6027,7 +6307,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Waitlisted rate, July</t>
         </is>
@@ -6047,7 +6327,7 @@
       </c>
     </row>
     <row r="7" ht="31" customHeight="1" s="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Average waitlisted rate (WL_RATE_AVG); Now = WL_RATE_2026</t>
         </is>
@@ -6071,7 +6351,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Net cost per day, low (NET_COST_LO)</t>
         </is>
@@ -6095,7 +6375,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Net cost per day, high (NET_COST_HI)</t>
         </is>
@@ -6119,7 +6399,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Cost of excess days, low (EXCESS_COST_LO)</t>
         </is>
@@ -6143,7 +6423,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Cost of excess days, high (EXCESS_COST_HI)</t>
         </is>
@@ -6167,7 +6447,7 @@
       </c>
     </row>
     <row r="12" ht="31" customHeight="1" s="7">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Nursing-facility share of Dec 31 waitlist (NF_SHARE_DEC31), reported beside the result only</t>
         </is>
@@ -6177,86 +6457,102 @@
           <t>share</t>
         </is>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <f>INDEX(DEC31_NF,MATCH(2023,YEAR,0))/INDEX(DEC31_TOTAL,MATCH(2023,YEAR,0))</f>
         <v>0.8219895287958116</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>INDEX(DEC31_NF,MATCH(2024,YEAR,0))/INDEX(DEC31_TOTAL,MATCH(2024,YEAR,0))</f>
         <v>0.6936416184971098</v>
       </c>
     </row>
     <row r="13" ht="31" customHeight="1" s="7">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Ceiling per placed patient, low (CEIL_PER_PT_LO): net cost per day now x 2024 days per patient</t>
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Days saved per placed patient (DAYS_SAVED_PER_PT): 2024 days per patient minus the admission window</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="E13" s="24">
+        <f>MAX(0,INDEX(DAYS_PER_PT,MATCH(2024,YEAR,0))-ADMIT_WINDOW_DAYS)</f>
+        <v>5.492795389048993</v>
+      </c>
+    </row>
+    <row r="14" ht="31" customHeight="1" s="7">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Ceiling per placed patient, low (CEIL_PER_PT_LO): net cost per day now x days saved</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>USD per patient</t>
         </is>
       </c>
-      <c r="E13" s="35">
-        <f>NET_COST_LO_NOW*INDEX(DAYS_PER_PT,MATCH(2024,YEAR,0))</f>
-        <v>1232.7243804034586</v>
-      </c>
-    </row>
-    <row r="14" ht="31" customHeight="1" s="7">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>Ceiling per placed patient, high (CEIL_PER_PT_HI): net cost per day now x 2024 days per patient</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="E14" s="35">
+        <f>NET_COST_LO_NOW*DAYS_SAVED_PER_PT</f>
+        <v>347.36438040345837</v>
+      </c>
+    </row>
+    <row r="15" ht="31" customHeight="1" s="7">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Ceiling per placed patient, high (CEIL_PER_PT_HI): net cost per day now x days saved</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>USD per patient</t>
         </is>
       </c>
-      <c r="E14" s="35">
-        <f>NET_COST_HI_NOW*INDEX(DAYS_PER_PT,MATCH(2024,YEAR,0))</f>
-        <v>19166.096138328532</v>
-      </c>
-    </row>
-    <row r="16" ht="31" customHeight="1" s="7">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="E15" s="35">
+        <f>NET_COST_HI_NOW*DAYS_SAVED_PER_PT</f>
+        <v>5400.736138328532</v>
+      </c>
+    </row>
+    <row r="17" ht="31" customHeight="1" s="7">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Change in waitlist days, 2023 to 2024 (WL_DAYS_CHANGE_2024)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="C16" s="19">
+      <c r="C17" s="20">
         <f>INDEX(WL_DAYS,MATCH(2024,YEAR,0))/INDEX(WL_DAYS,MATCH(2023,YEAR,0))-1</f>
         <v>-0.26741037582584204</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Note: Leahi Hospital, Jan 2026 waitlisted rate</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>USD per day</t>
         </is>
       </c>
-      <c r="C17" s="35">
+      <c r="C18" s="35">
         <f>WL_RATE_LEAHI_2026</f>
         <v>480.19</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Reported as a note; the other hospitals are at WL_RATE_2026. Not used in a calculation.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Avoidable cost range AVOID_COST_LO to AVOID_COST_HI per waitlisted day, net of the waitlisted rate. All levels of care.</t>
         </is>
@@ -6313,11 +6609,11 @@
           <t>Financial share, Dec 31 2020</t>
         </is>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2020,YEAR,0))</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>COVID year</t>
         </is>
@@ -6329,11 +6625,11 @@
           <t>Financial share, Dec 31 2021</t>
         </is>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2021,YEAR,0))</f>
         <v>0.2275132275132275</v>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>COVID year</t>
         </is>
@@ -6345,11 +6641,11 @@
           <t>Drop, 2020 to 2021 (T1_DROP_2021; negative = rise)</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2020,YEAR,0))-INDEX(SHARE_FINANCIAL,MATCH(2021,YEAR,0))</f>
         <v>-0.019179894179894158</v>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Shown as a percent of the reasons total, i.e. percentage points</t>
         </is>
@@ -6365,7 +6661,7 @@
         <f>T1_DROP_2021*100&gt;=T1_MIN_DROP_PTS</f>
         <v>0</v>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Unrounded comparison; 2021 comparison is COVID-confounded</t>
         </is>
@@ -6377,7 +6673,7 @@
           <t>Financial share, Dec 31 2023</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2023,YEAR,0))</f>
         <v>0.2356020942408377</v>
       </c>
@@ -6388,7 +6684,7 @@
           <t>Financial share, Dec 31 2024</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2024,YEAR,0))</f>
         <v>0.3468208092485549</v>
       </c>
@@ -6399,11 +6695,11 @@
           <t>Drop, 2023 to 2024 (T1_DROP_2024; negative = rise)</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <f>INDEX(SHARE_FINANCIAL,MATCH(2023,YEAR,0))-INDEX(SHARE_FINANCIAL,MATCH(2024,YEAR,0))</f>
         <v>-0.11121871500771721</v>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Shown as a percent of the reasons total, i.e. percentage points</t>
         </is>
@@ -6419,7 +6715,7 @@
         <f>T1_DROP_2024*100&gt;=T1_MIN_DROP_PTS</f>
         <v>0</v>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Unrounded comparison</t>
         </is>
@@ -6435,7 +6731,7 @@
         <f>IF(AND(NOT(T1_PASS_2021),NOT(T1_PASS_2024)),"Falsified",IF(AND(T1_PASS_2021,NOT(T1_PASS_2024)),"Not falsified; weak (rests on the COVID-confounded 2021 comparison)","Not falsified"))</f>
         <v>Falsified</v>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Fails only if both drops fall short (lenient reading)</t>
         </is>
@@ -6464,11 +6760,11 @@
           <t>Least-squares slope of days per patient, 2017 to 2023 (T2_SLOPE)</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <f>SLOPE(INDEX(DAYS_PER_PT,1):INDEX(DAYS_PER_PT,7),INDEX(YEAR,1):INDEX(YEAR,7))</f>
         <v>1.8814212714379457</v>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>days per patient per year</t>
         </is>
@@ -6484,7 +6780,7 @@
         <f>IF(T2_SLOPE&lt;0,"Met","Not met")</f>
         <v>Not met</v>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Met = the trend slopes down (falling steadily toward 14)</t>
         </is>
@@ -6518,7 +6814,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14">
+      <c r="A19" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
@@ -6540,7 +6836,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
@@ -6562,7 +6858,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14">
+      <c r="A21" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
@@ -6584,7 +6880,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
@@ -6606,7 +6902,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14">
+      <c r="A23" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
@@ -6628,7 +6924,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
@@ -6650,7 +6946,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14">
+      <c r="A25" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
@@ -6672,7 +6968,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
@@ -6703,7 +6999,7 @@
         <f>COUNTIF(LARGEST_REASON,"No bed")</f>
         <v>5</v>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>of 8 years, 2017 to 2024</t>
         </is>
@@ -6719,7 +7015,7 @@
         <f>IF(T3_YEARS&gt;8/2,"Met","Not met")</f>
         <v>Met</v>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Met = more than half of 8 years (5 or more); a tie counts as not largest</t>
         </is>
@@ -6735,14 +7031,14 @@
         <f>FLAG_2017_INCOMPLETE</f>
         <v>1</v>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>2017 is counted on its recorded reasons (120 of 157) and flagged</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>The model reports each test's verdict. It does not rank or cost the options and does not choose between the add-on and the top-up.</t>
         </is>
@@ -6771,11 +7067,11 @@
           <t>Financial count change, Dec 2020 to Dec 2021 (T1_FIN_CHANGE_2021)</t>
         </is>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="25">
         <f>INDEX(REASON_FINANCIAL,MATCH(2021,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2020,YEAR,0))</f>
         <v>13.0</v>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>patients, Dec 31</t>
         </is>
@@ -6787,7 +7083,7 @@
           <t>Other six reasons change, Dec 2020 to Dec 2021 (T1_OTHER_CHANGE_2021)</t>
         </is>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="25">
         <f>(INDEX(REASON_SUM,MATCH(2021,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2021,YEAR,0)))-(INDEX(REASON_SUM,MATCH(2020,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2020,YEAR,0)))</f>
         <v>32.0</v>
       </c>
@@ -6798,7 +7094,7 @@
           <t>Financial count change, Dec 2023 to Dec 2024 (T1_FIN_CHANGE_2024)</t>
         </is>
       </c>
-      <c r="B36" s="23">
+      <c r="B36" s="25">
         <f>INDEX(REASON_FINANCIAL,MATCH(2024,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2023,YEAR,0))</f>
         <v>15.0</v>
       </c>
@@ -6809,13 +7105,13 @@
           <t>Other six reasons change, Dec 2023 to Dec 2024 (T1_OTHER_CHANGE_2024)</t>
         </is>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="25">
         <f>(INDEX(REASON_SUM,MATCH(2024,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2024,YEAR,0)))-(INDEX(REASON_SUM,MATCH(2023,YEAR,0))-INDEX(REASON_FINANCIAL,MATCH(2023,YEAR,0)))</f>
         <v>-33.0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Side diagnostic: not a test; no verdict. Chosen on Sep 29, after the results were known (spec Conventions).</t>
         </is>
@@ -6881,19 +7177,19 @@
         <f>INDEX(COUNTY,1)</f>
         <v>Hawaii</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <f>INDEX(CTY_DAYS,1,1)/INDEX(CTY_PATIENTS,1,1)</f>
         <v>26.711162255466053</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <f>INDEX(CTY_DAYS,1,2)/INDEX(CTY_PATIENTS,1,2)</f>
         <v>27.74965612104539</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="20">
         <f>INDEX(CTY_DAYS,1,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.27933619745598515</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="20">
         <f>INDEX(CTY_DAYS,1,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.33139496681779357</v>
       </c>
@@ -6903,19 +7199,19 @@
         <f>INDEX(COUNTY,2)</f>
         <v>Honolulu</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>INDEX(CTY_DAYS,2,1)/INDEX(CTY_PATIENTS,2,1)</f>
         <v>17.883370288248337</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>INDEX(CTY_DAYS,2,2)/INDEX(CTY_PATIENTS,2,2)</f>
         <v>13.835270338554826</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <f>INDEX(CTY_DAYS,2,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.4853003116839356</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="20">
         <f>INDEX(CTY_DAYS,2,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.4497667389447401</v>
       </c>
@@ -6925,19 +7221,19 @@
         <f>INDEX(COUNTY,3)</f>
         <v>Kauai</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>INDEX(CTY_DAYS,3,1)/INDEX(CTY_PATIENTS,3,1)</f>
         <v>20.0</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>INDEX(CTY_DAYS,3,2)/INDEX(CTY_PATIENTS,3,2)</f>
         <v>30.109375</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <f>INDEX(CTY_DAYS,3,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.02069870151750364</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>INDEX(CTY_DAYS,3,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.031654510808857346</v>
       </c>
@@ -6947,19 +7243,19 @@
         <f>INDEX(COUNTY,4)</f>
         <v>Maui</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>INDEX(CTY_DAYS,4,1)/INDEX(CTY_PATIENTS,4,1)</f>
         <v>44.595</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>INDEX(CTY_DAYS,4,2)/INDEX(CTY_PATIENTS,4,2)</f>
         <v>32.28045325779037</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <f>INDEX(CTY_DAYS,4,1)/INDEX(WL_DAYS,MATCH(2023,YEAR,0))</f>
         <v>0.21466478934257555</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <f>INDEX(CTY_DAYS,4,2)/INDEX(WL_DAYS,MATCH(2024,YEAR,0))</f>
         <v>0.18718378342860897</v>
       </c>
@@ -6970,17 +7266,17 @@
           <t>Total share</t>
         </is>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <f>INDEX(CTY_DAY_SHARE,1,1)+INDEX(CTY_DAY_SHARE,2,1)+INDEX(CTY_DAY_SHARE,3,1)+INDEX(CTY_DAY_SHARE,4,1)</f>
         <v>1.0</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>INDEX(CTY_DAY_SHARE,1,2)+INDEX(CTY_DAY_SHARE,2,2)+INDEX(CTY_DAY_SHARE,3,2)+INDEX(CTY_DAY_SHARE,4,2)</f>
         <v>1.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>County = the county of the reporting hospital (Table 18 hospital rows summed).</t>
         </is>
@@ -7036,11 +7332,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14">
+      <c r="A4" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <f>INDEX(EXCESS_BEDS,1)</f>
         <v>0.0</v>
       </c>
@@ -7054,11 +7350,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>INDEX(EXCESS_BEDS,2)</f>
         <v>0.0</v>
       </c>
@@ -7072,11 +7368,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>INDEX(EXCESS_BEDS,3)</f>
         <v>32.46849315068493</v>
       </c>
@@ -7090,11 +7386,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>INDEX(EXCESS_BEDS,4)</f>
         <v>0.0</v>
       </c>
@@ -7108,11 +7404,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>INDEX(EXCESS_BEDS,5)</f>
         <v>0.0</v>
       </c>
@@ -7126,11 +7422,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>INDEX(EXCESS_BEDS,6)</f>
         <v>74.04657534246576</v>
       </c>
@@ -7144,11 +7440,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>INDEX(EXCESS_BEDS,7)</f>
         <v>89.1972602739726</v>
       </c>
@@ -7162,11 +7458,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>INDEX(EXCESS_BEDS,8)</f>
         <v>46.868852459016395</v>
       </c>
@@ -7202,35 +7498,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Blank where a year has no excess beds (no division by zero).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Limits (spec Conventions, Capacity comparison):</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>(1) Excess beds cover the acute waitlist across all levels of care on an average day; unstaffed beds are long-term-care beds on Dec 31. Not a bed-for-bed match.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>(2) Reopening beds idle for lack of staff is a workforce lever outside the scope; the capacity option is new transitional capacity.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>(3) Excess days are a lower bound, so excess beds are too.</t>
         </is>
@@ -7247,13 +7543,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" style="7" min="1" max="1"/>
-    <col width="14" customWidth="1" style="7" min="2" max="2"/>
+    <col width="88" customWidth="1" style="7" min="1" max="1"/>
+    <col width="16" customWidth="1" style="7" min="2" max="2"/>
     <col width="20" customWidth="1" style="7" min="3" max="3"/>
-    <col width="16" customWidth="1" style="7" min="4" max="4"/>
+    <col width="22" customWidth="1" style="7" min="4" max="4"/>
     <col width="22" customWidth="1" style="7" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -7308,7 +7604,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <f>INDEX(MB_GROSS,1)</f>
         <v>0.03</v>
       </c>
@@ -7323,7 +7619,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>INDEX(MB_GROSS,2)</f>
         <v>0.03</v>
       </c>
@@ -7338,7 +7634,7 @@
           <t>FY2026</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>INDEX(MB_GROSS,3)</f>
         <v>0.033</v>
       </c>
@@ -7350,7 +7646,7 @@
         <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2026,1,1),RATE_DATE,0))</f>
         <v>495.26</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>1-INDEX(RATE_FWD,1)/INDEX(COST_FWD,3)</f>
         <v>0.021380290392819967</v>
       </c>
@@ -7361,7 +7657,7 @@
           <t>FY2027</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>INDEX(MB_GROSS,4)</f>
         <v>0.033</v>
       </c>
@@ -7373,7 +7669,7 @@
         <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2026,1,1),RATE_DATE,0))*(1+RATE_GROWTH_2024_2026)</f>
         <v>502.1147295121337</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>1-INDEX(RATE_FWD,2)/INDEX(COST_FWD,4)</f>
         <v>0.039531015821562265</v>
       </c>
@@ -7384,41 +7680,300 @@
           <t>Post-reset rate pace, Jan 2024 to Jan 2026 (RATE_GROWTH_2024_2026)</t>
         </is>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <f>(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2026,1,1),RATE_DATE,0))/INDEX(NF_RATE_MEDIAN,MATCH(DATE(2024,1,1),RATE_DATE,0)))^(1/2)-1</f>
         <v>0.013840668562237424</v>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>a year, compounded over two years</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Cost above the rate over a median Medicaid stay, FY2026 (STAY_SHORTFALL)</t>
+        </is>
+      </c>
+      <c r="B11" s="35">
+        <f>(INDEX(COST_FWD,3)-INDEX(RATE_FWD,1))*MEDIAN_MCD_LOS</f>
+        <v>5873.496793247295</v>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>USD per stay; a rough comparison (spec Conventions)</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Rate for FY2026 = the January 2026 median; FY2027 carries it forward at the post-reset pace.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Cost is dated July 1 of the fiscal year and the rate January: a half-year mismatch.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>The market basket is a national Medicare index standing in for Hawaii nursing-home cost growth.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Not a forecast; the model does not rank or cost the options (spec Conventions, Condition (a)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Paper figures: the rate against Medicaid-heavy cost, the two rate rises, and the behavior and guardianship share</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1" s="7">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Fiscal year</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>July rate median</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Medicaid-heavy cost</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Gap, 1 - rate / cost (RATE_COST_GAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="B19" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2016,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2016,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2016,7,1),RATE_DATE,0)),"")</f>
+        <v>252.4</v>
+      </c>
+      <c r="C19" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2016,COST_FY,0))</f>
+        <v>344.38</v>
+      </c>
+      <c r="D19" s="26">
+        <f>IF(ISNUMBER(B19),1-B19/C19,"")</f>
+        <v>0.26708868110807826</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="B20" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2017,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2017,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2017,7,1),RATE_DATE,0)),"")</f>
+        <v>261.45</v>
+      </c>
+      <c r="C20" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2017,COST_FY,0))</f>
+        <v>356.1</v>
+      </c>
+      <c r="D20" s="26">
+        <f>IF(ISNUMBER(B20),1-B20/C20,"")</f>
+        <v>0.26579612468407754</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="B21" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2018,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2018,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2018,7,1),RATE_DATE,0)),"")</f>
+        <v>270.66</v>
+      </c>
+      <c r="C21" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2018,COST_FY,0))</f>
+        <v>365.93</v>
+      </c>
+      <c r="D21" s="26">
+        <f>IF(ISNUMBER(B21),1-B21/C21,"")</f>
+        <v>0.2603503402290055</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="str">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2019,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2019,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2019,7,1),RATE_DATE,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2019,COST_FY,0))</f>
+        <v>373.25</v>
+      </c>
+      <c r="D22" s="26" t="str">
+        <f>IF(ISNUMBER(B22),1-B22/C22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="B23" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2020,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2020,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2020,7,1),RATE_DATE,0)),"")</f>
+        <v>282.98</v>
+      </c>
+      <c r="C23" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2020,COST_FY,0))</f>
+        <v>398.33</v>
+      </c>
+      <c r="D23" s="26">
+        <f>IF(ISNUMBER(B23),1-B23/C23,"")</f>
+        <v>0.289584013255341</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="B24" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2021,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2021,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2021,7,1),RATE_DATE,0)),"")</f>
+        <v>334.75</v>
+      </c>
+      <c r="C24" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2021,COST_FY,0))</f>
+        <v>423.44</v>
+      </c>
+      <c r="D24" s="26">
+        <f>IF(ISNUMBER(B24),1-B24/C24,"")</f>
+        <v>0.20945116191195923</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="str">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2022,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2022,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2022,7,1),RATE_DATE,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2022,COST_FY,0))</f>
+        <v>435.63</v>
+      </c>
+      <c r="D25" s="26" t="str">
+        <f>IF(ISNUMBER(B25),1-B25/C25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="B26" s="35">
+        <f>IF(IF(ISNUMBER(MATCH(DATE(2023,7,1),RATE_DATE,0)),ISNUMBER(INDEX(NF_RATE_MEDIAN,MATCH(DATE(2023,7,1),RATE_DATE,0))),FALSE),INDEX(NF_RATE_MEDIAN,MATCH(DATE(2023,7,1),RATE_DATE,0)),"")</f>
+        <v>371.99</v>
+      </c>
+      <c r="C26" s="35">
+        <f>INDEX(NF_COST_MCD_HEAVY,MATCH(2023,COST_FY,0))</f>
+        <v>461.79</v>
+      </c>
+      <c r="D26" s="26">
+        <f>IF(ISNUMBER(B26),1-B26/C26,"")</f>
+        <v>0.19446068559301843</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Smallest gap, FY2016 to FY2023 (RATE_COST_GAP_MIN)</t>
+        </is>
+      </c>
+      <c r="B28" s="26">
+        <f>MIN(D19:D26)</f>
+        <v>0.19446068559301843</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Largest gap, FY2016 to FY2023 (RATE_COST_GAP_MAX)</t>
+        </is>
+      </c>
+      <c r="B29" s="26">
+        <f>MAX(D19:D26)</f>
+        <v>0.289584013255341</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Rate rise, July 2020 to July 2021 (RATE_RISE_2021)</t>
+        </is>
+      </c>
+      <c r="B31" s="20">
+        <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2021,7,1),RATE_DATE,0))/INDEX(NF_RATE_MEDIAN,MATCH(DATE(2020,7,1),RATE_DATE,0))-1</f>
+        <v>0.1829457912219945</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Rate rise, July 2023 to January 2024 (RATE_RISE_2024)</t>
+        </is>
+      </c>
+      <c r="B32" s="20">
+        <f>INDEX(NF_RATE_MEDIAN,MATCH(DATE(2024,1,1),RATE_DATE,0))/INDEX(NF_RATE_MEDIAN,MATCH(DATE(2023,7,1),RATE_DATE,0))-1</f>
+        <v>0.29527675475147164</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Behavior and guardianship share, Dec 31, 2024 (BEH_GUARD_SHARE_2024)</t>
+        </is>
+      </c>
+      <c r="B34" s="20">
+        <f>INDEX(SHARE_BEHAVIOR,MATCH(2024,YEAR,0))+INDEX(SHARE_GUARDIANSHIP,MATCH(2024,YEAR,0))</f>
+        <v>0.3468208092485549</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>The gap pairs each fiscal year's cost with that July's rate memo; years with no July median in the rate series (2019, 2022) are blank. The rate median covers all homes; the cost median covers Medicaid-heavy homes.</t>
         </is>
       </c>
     </row>
@@ -7489,7 +8044,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
@@ -7497,7 +8052,7 @@
         <f>DATE(INDEX(YEAR,1),7,1)</f>
         <v>42917</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>INDEX(DAYS_PER_PT,1)</f>
         <v>9.935348310974625</v>
       </c>
@@ -7511,7 +8066,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
@@ -7519,7 +8074,7 @@
         <f>DATE(INDEX(YEAR,2),7,1)</f>
         <v>43282</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>INDEX(DAYS_PER_PT,2)</f>
         <v>12.484132980732905</v>
       </c>
@@ -7533,7 +8088,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
@@ -7541,7 +8096,7 @@
         <f>DATE(INDEX(YEAR,3),7,1)</f>
         <v>43647</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>INDEX(DAYS_PER_PT,3)</f>
         <v>16.4741127348643</v>
       </c>
@@ -7555,7 +8110,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
@@ -7563,7 +8118,7 @@
         <f>DATE(INDEX(YEAR,4),7,1)</f>
         <v>44013</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>INDEX(DAYS_PER_PT,4)</f>
         <v>12.584449813309906</v>
       </c>
@@ -7577,7 +8132,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
@@ -7585,7 +8140,7 @@
         <f>DATE(INDEX(YEAR,5),7,1)</f>
         <v>44378</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>INDEX(DAYS_PER_PT,5)</f>
         <v>12.187943982139233</v>
       </c>
@@ -7599,7 +8154,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
@@ -7607,7 +8162,7 @@
         <f>DATE(INDEX(YEAR,6),7,1)</f>
         <v>44743</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>INDEX(DAYS_PER_PT,6)</f>
         <v>21.34229828850856</v>
       </c>
@@ -7621,7 +8176,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
@@ -7629,7 +8184,7 @@
         <f>DATE(INDEX(YEAR,7),7,1)</f>
         <v>45108</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <f>INDEX(DAYS_PER_PT,7)</f>
         <v>23.018559556786702</v>
       </c>
@@ -7643,7 +8198,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14">
+      <c r="A12" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
@@ -7651,7 +8206,7 @@
         <f>DATE(INDEX(YEAR,8),7,1)</f>
         <v>45474</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <f>INDEX(DAYS_PER_PT,8)</f>
         <v>19.492795389048993</v>
       </c>
@@ -7760,35 +8315,35 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14">
+      <c r="A21" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>INDEX(SHARE_NO_BED,1)</f>
         <v>0.325</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <f>INDEX(SHARE_BEHAVIOR,1)</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,1)</f>
         <v>0.19166666666666668</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <f>INDEX(SHARE_FINANCIAL,1)</f>
         <v>0.15</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,1)</f>
         <v>0.09166666666666666</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="20">
         <f>INDEX(SHARE_PASARR,1)</f>
         <v>0.016666666666666666</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="20">
         <f>INDEX(SHARE_OTHER,1)</f>
         <v>0.09166666666666666</v>
       </c>
@@ -7798,35 +8353,35 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>INDEX(SHARE_NO_BED,2)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <f>INDEX(SHARE_BEHAVIOR,2)</f>
         <v>0.1695906432748538</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,2)</f>
         <v>0.09941520467836257</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <f>INDEX(SHARE_FINANCIAL,2)</f>
         <v>0.18128654970760233</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,2)</f>
         <v>0.10526315789473684</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="20">
         <f>INDEX(SHARE_PASARR,2)</f>
         <v>0.011695906432748537</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="20">
         <f>INDEX(SHARE_OTHER,2)</f>
         <v>0.09941520467836257</v>
       </c>
@@ -7836,35 +8391,35 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14">
+      <c r="A23" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="20">
         <f>INDEX(SHARE_NO_BED,3)</f>
         <v>0.391304347826087</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="20">
         <f>INDEX(SHARE_BEHAVIOR,3)</f>
         <v>0.14673913043478262</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,3)</f>
         <v>0.11413043478260869</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="20">
         <f>INDEX(SHARE_FINANCIAL,3)</f>
         <v>0.17391304347826086</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,3)</f>
         <v>0.14130434782608695</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="20">
         <f>INDEX(SHARE_PASARR,3)</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="20">
         <f>INDEX(SHARE_OTHER,3)</f>
         <v>0.03260869565217391</v>
       </c>
@@ -7874,35 +8429,35 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <f>INDEX(SHARE_NO_BED,4)</f>
         <v>0.2847222222222222</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <f>INDEX(SHARE_BEHAVIOR,4)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,4)</f>
         <v>0.1527777777777778</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <f>INDEX(SHARE_FINANCIAL,4)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,4)</f>
         <v>0.10416666666666667</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <f>INDEX(SHARE_PASARR,4)</f>
         <v>0.0</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <f>INDEX(SHARE_OTHER,4)</f>
         <v>0.08333333333333333</v>
       </c>
@@ -7912,35 +8467,35 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14">
+      <c r="A25" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="20">
         <f>INDEX(SHARE_NO_BED,5)</f>
         <v>0.26455026455026454</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="20">
         <f>INDEX(SHARE_BEHAVIOR,5)</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,5)</f>
         <v>0.1164021164021164</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="20">
         <f>INDEX(SHARE_FINANCIAL,5)</f>
         <v>0.2275132275132275</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,5)</f>
         <v>0.10582010582010581</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="20">
         <f>INDEX(SHARE_PASARR,5)</f>
         <v>0.0</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="20">
         <f>INDEX(SHARE_OTHER,5)</f>
         <v>0.09523809523809523</v>
       </c>
@@ -7950,35 +8505,35 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="20">
         <f>INDEX(SHARE_NO_BED,6)</f>
         <v>0.228</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <f>INDEX(SHARE_BEHAVIOR,6)</f>
         <v>0.14</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,6)</f>
         <v>0.156</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <f>INDEX(SHARE_FINANCIAL,6)</f>
         <v>0.3</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,6)</f>
         <v>0.116</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <f>INDEX(SHARE_PASARR,6)</f>
         <v>0.02</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="20">
         <f>INDEX(SHARE_OTHER,6)</f>
         <v>0.04</v>
       </c>
@@ -7988,35 +8543,35 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14">
+      <c r="A27" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <f>INDEX(SHARE_NO_BED,7)</f>
         <v>0.2198952879581152</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <f>INDEX(SHARE_BEHAVIOR,7)</f>
         <v>0.2513089005235602</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,7)</f>
         <v>0.13612565445026178</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <f>INDEX(SHARE_FINANCIAL,7)</f>
         <v>0.2356020942408377</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,7)</f>
         <v>0.14659685863874344</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <f>INDEX(SHARE_PASARR,7)</f>
         <v>0.005235602094240838</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="20">
         <f>INDEX(SHARE_OTHER,7)</f>
         <v>0.005235602094240838</v>
       </c>
@@ -8026,35 +8581,35 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14">
+      <c r="A28" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="20">
         <f>INDEX(SHARE_NO_BED,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <f>INDEX(SHARE_BEHAVIOR,8)</f>
         <v>0.1676300578034682</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <f>INDEX(SHARE_SPECIAL_CARE,8)</f>
         <v>0.10404624277456648</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <f>INDEX(SHARE_FINANCIAL,8)</f>
         <v>0.3468208092485549</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="20">
         <f>INDEX(SHARE_GUARDIANSHIP,8)</f>
         <v>0.1791907514450867</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="20">
         <f>INDEX(SHARE_PASARR,8)</f>
         <v>0.0</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="20">
         <f>INDEX(SHARE_OTHER,8)</f>
         <v>0.023121387283236993</v>
       </c>
@@ -8093,11 +8648,11 @@
           <t>Across the 12% adjustment</t>
         </is>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="28">
         <f>YEAR(DATE_ADJ_2021)-1</f>
         <v>2020.0</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="28">
         <f>YEAR(DATE_ADJ_2021)</f>
         <v>2021</v>
       </c>
@@ -8108,11 +8663,11 @@
           <t>Across the reset</t>
         </is>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <f>YEAR(DATE_RESET_2024)-1</f>
         <v>2023.0</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="28">
         <f>YEAR(DATE_RESET_2024)</f>
         <v>2024</v>
       </c>
@@ -8142,7 +8697,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16">
+      <c r="A37" s="17">
         <f>DATE(2016,1,1)</f>
         <v>42370</v>
       </c>
@@ -8156,7 +8711,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16">
+      <c r="A38" s="17">
         <f>DATE(2016,7,1)</f>
         <v>42552</v>
       </c>
@@ -8170,7 +8725,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16">
+      <c r="A39" s="17">
         <f>DATE(2017,1,1)</f>
         <v>42736</v>
       </c>
@@ -8184,7 +8739,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16">
+      <c r="A40" s="17">
         <f>DATE(2017,7,1)</f>
         <v>42917</v>
       </c>
@@ -8198,7 +8753,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16">
+      <c r="A41" s="17">
         <f>DATE(2018,1,1)</f>
         <v>43101</v>
       </c>
@@ -8212,7 +8767,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16">
+      <c r="A42" s="17">
         <f>DATE(2018,7,1)</f>
         <v>43282</v>
       </c>
@@ -8226,7 +8781,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16">
+      <c r="A43" s="17">
         <f>DATE(2019,1,1)</f>
         <v>43466</v>
       </c>
@@ -8240,7 +8795,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16">
+      <c r="A44" s="17">
         <f>DATE(2019,7,1)</f>
         <v>43647</v>
       </c>
@@ -8254,7 +8809,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16">
+      <c r="A45" s="17">
         <f>DATE(2020,1,1)</f>
         <v>43831</v>
       </c>
@@ -8268,7 +8823,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16">
+      <c r="A46" s="17">
         <f>DATE(2020,7,1)</f>
         <v>44013</v>
       </c>
@@ -8282,7 +8837,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16">
+      <c r="A47" s="17">
         <f>DATE(2021,1,1)</f>
         <v>44197</v>
       </c>
@@ -8296,7 +8851,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16">
+      <c r="A48" s="17">
         <f>DATE(2021,7,1)</f>
         <v>44378</v>
       </c>
@@ -8310,7 +8865,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16">
+      <c r="A49" s="17">
         <f>DATE(2022,1,1)</f>
         <v>44562</v>
       </c>
@@ -8324,7 +8879,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16">
+      <c r="A50" s="17">
         <f>DATE(2022,7,1)</f>
         <v>44743</v>
       </c>
@@ -8338,7 +8893,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16">
+      <c r="A51" s="17">
         <f>DATE(2023,1,1)</f>
         <v>44927</v>
       </c>
@@ -8352,7 +8907,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16">
+      <c r="A52" s="17">
         <f>DATE(2023,7,1)</f>
         <v>45108</v>
       </c>
@@ -8366,7 +8921,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16">
+      <c r="A53" s="17">
         <f>DATE(2024,1,1)</f>
         <v>45292</v>
       </c>
@@ -8380,7 +8935,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16">
+      <c r="A54" s="17">
         <f>DATE(2024,7,1)</f>
         <v>45474</v>
       </c>
@@ -8394,7 +8949,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16">
+      <c r="A55" s="17">
         <f>DATE(2025,1,1)</f>
         <v>45658</v>
       </c>
@@ -8408,7 +8963,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="16">
+      <c r="A56" s="17">
         <f>DATE(2025,7,1)</f>
         <v>45839</v>
       </c>
@@ -8422,7 +8977,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16">
+      <c r="A57" s="17">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
       </c>
@@ -8465,7 +9020,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14">
+      <c r="A61" s="15">
         <f>INDEX(COST_FY,1)</f>
         <v>2011</v>
       </c>
@@ -8483,7 +9038,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14">
+      <c r="A62" s="15">
         <f>INDEX(COST_FY,2)</f>
         <v>2012</v>
       </c>
@@ -8501,7 +9056,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="14">
+      <c r="A63" s="15">
         <f>INDEX(COST_FY,3)</f>
         <v>2013</v>
       </c>
@@ -8519,7 +9074,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14">
+      <c r="A64" s="15">
         <f>INDEX(COST_FY,4)</f>
         <v>2014</v>
       </c>
@@ -8537,7 +9092,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14">
+      <c r="A65" s="15">
         <f>INDEX(COST_FY,5)</f>
         <v>2015</v>
       </c>
@@ -8555,7 +9110,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14">
+      <c r="A66" s="15">
         <f>INDEX(COST_FY,6)</f>
         <v>2016</v>
       </c>
@@ -8573,7 +9128,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14">
+      <c r="A67" s="15">
         <f>INDEX(COST_FY,7)</f>
         <v>2017</v>
       </c>
@@ -8591,7 +9146,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="14">
+      <c r="A68" s="15">
         <f>INDEX(COST_FY,8)</f>
         <v>2018</v>
       </c>
@@ -8609,7 +9164,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="14">
+      <c r="A69" s="15">
         <f>INDEX(COST_FY,9)</f>
         <v>2019</v>
       </c>
@@ -8627,7 +9182,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="14">
+      <c r="A70" s="15">
         <f>INDEX(COST_FY,10)</f>
         <v>2020</v>
       </c>
@@ -8645,7 +9200,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="14">
+      <c r="A71" s="15">
         <f>INDEX(COST_FY,11)</f>
         <v>2021</v>
       </c>
@@ -8663,7 +9218,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="14">
+      <c r="A72" s="15">
         <f>INDEX(COST_FY,12)</f>
         <v>2022</v>
       </c>
@@ -8681,7 +9236,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="14">
+      <c r="A73" s="15">
         <f>INDEX(COST_FY,13)</f>
         <v>2023</v>
       </c>
@@ -8728,7 +9283,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="14">
+      <c r="A77" s="15">
         <f>INDEX(YEAR,1)</f>
         <v>2017</v>
       </c>
@@ -8746,7 +9301,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="14">
+      <c r="A78" s="15">
         <f>INDEX(YEAR,2)</f>
         <v>2018</v>
       </c>
@@ -8764,7 +9319,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="14">
+      <c r="A79" s="15">
         <f>INDEX(YEAR,3)</f>
         <v>2019</v>
       </c>
@@ -8782,7 +9337,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="14">
+      <c r="A80" s="15">
         <f>INDEX(YEAR,4)</f>
         <v>2020</v>
       </c>
@@ -8800,7 +9355,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="14">
+      <c r="A81" s="15">
         <f>INDEX(YEAR,5)</f>
         <v>2021</v>
       </c>
@@ -8818,7 +9373,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="14">
+      <c r="A82" s="15">
         <f>INDEX(YEAR,6)</f>
         <v>2022</v>
       </c>
@@ -8836,7 +9391,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="14">
+      <c r="A83" s="15">
         <f>INDEX(YEAR,7)</f>
         <v>2023</v>
       </c>
@@ -8854,7 +9409,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="14">
+      <c r="A84" s="15">
         <f>INDEX(YEAR,8)</f>
         <v>2024</v>
       </c>
@@ -8872,7 +9427,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="15" t="inlineStr">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Figure g: schematic, no data (illustrative, not to scale).</t>
         </is>
@@ -8984,11 +9539,11 @@
       <c r="D8" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>C8/B8</f>
         <v>10.0</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="19">
         <f>D8/B8</f>
         <v>20.0</v>
       </c>
@@ -9006,11 +9561,11 @@
       <c r="D9" s="6" t="n">
         <v>1400</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>C9/B9</f>
         <v>14.0</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>D9/B9</f>
         <v>14.0</v>
       </c>
@@ -9028,11 +9583,11 @@
       <c r="D10" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>C10/B10</f>
         <v>20.0</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>D10/B10</f>
         <v>10.0</v>
       </c>
@@ -9168,10 +9723,10 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="B22" s="28" t="n">
+      <c r="B22" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C22" s="28" t="n">
+      <c r="C22" s="12" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9181,10 +9736,10 @@
           <t>E2</t>
         </is>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C23" s="12" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -9194,10 +9749,10 @@
           <t>E3</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n">
+      <c r="B24" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C24" s="12" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9207,10 +9762,10 @@
           <t>E4</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="12" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -9220,10 +9775,10 @@
           <t>E5</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C26" s="12" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -9966,7 +10521,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>Case E feeds the drops (in points) straight into the verdict formula; the share-to-drop step is covered by the regression anchors on Checks.</t>
         </is>
